--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y178"/>
+  <dimension ref="A1:Y177"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.375" customWidth="1" style="3" min="1" max="2"/>
@@ -2428,17 +2428,15 @@
       <c r="I21" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="J21" s="0" t="n">
+        <v>15</v>
       </c>
       <c r="M21" s="0" t="n">
         <v>1000001</v>
       </c>
       <c r="N21" s="0" t="inlineStr">
         <is>
-          <t>10100008&amp;10200008&amp;10300008&amp;11000006&amp;</t>
+          <t>10100008&amp;10200008&amp;10300008&amp;11020014&amp;</t>
         </is>
       </c>
       <c r="P21" s="0" t="n">
@@ -2457,66 +2455,66 @@
     </row>
     <row r="22" ht="15" customHeight="1" s="3">
       <c r="A22" s="0" t="n">
-        <v>1040020001</v>
+        <v>1041010001</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>104002</v>
+        <v>104101</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G22" s="0" t="n">
+        <v>1000</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I22" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="J22" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="M22" s="0" t="n">
         <v>1000001</v>
       </c>
       <c r="N22" s="0" t="inlineStr">
         <is>
-          <t>10100010&amp;10200010&amp;10300010&amp;11000006&amp;</t>
+          <t>10200009&amp;10300009&amp;11000012&amp;</t>
         </is>
       </c>
       <c r="P22" s="0" t="n">
-        <v>1040020001</v>
-      </c>
-      <c r="S22" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
+        <v>1041010001</v>
+      </c>
+      <c r="S22" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T22" s="0" t="n">
+        <v>100004</v>
       </c>
       <c r="Y22" s="0" t="inlineStr">
         <is>
-          <t>双持战士</t>
+          <t>BOSS-大剑战士</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="0" t="n">
-        <v>1041010001</v>
+        <v>1041020001</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>104101</v>
+        <v>104102</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>1</v>
@@ -2541,94 +2539,132 @@
       <c r="J23" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
       <c r="M23" s="0" t="n">
         <v>1000001</v>
       </c>
       <c r="N23" s="0" t="inlineStr">
         <is>
-          <t>10200009&amp;10300009&amp;11000012&amp;</t>
+          <t>10200009&amp;10300009&amp;11000015&amp;</t>
         </is>
       </c>
       <c r="P23" s="0" t="n">
-        <v>1041010001</v>
+        <v>1041020001</v>
       </c>
       <c r="S23" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="T23" s="0" t="n">
-        <v>100004</v>
+      <c r="T23" s="0" t="inlineStr">
+        <is>
+          <t>100001</t>
+        </is>
       </c>
       <c r="Y23" s="0" t="inlineStr">
         <is>
-          <t>BOSS-大剑战士</t>
+          <t>BOSS-大盾战士</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="3">
-      <c r="A24" s="0" t="n">
-        <v>1041020001</v>
-      </c>
-      <c r="B24" s="0" t="n">
-        <v>104102</v>
-      </c>
-      <c r="C24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="F24" s="0" t="inlineStr">
+      <c r="A24" s="2" t="n">
+        <v>2000000001</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" s="0" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H24" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="I24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="M24" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="N24" s="0" t="inlineStr">
-        <is>
-          <t>10200009&amp;10300009&amp;11020022&amp;</t>
-        </is>
-      </c>
-      <c r="P24" s="0" t="n">
-        <v>1041020001</v>
-      </c>
-      <c r="S24" s="0" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T24" s="0" t="inlineStr">
-        <is>
-          <t>100001</t>
-        </is>
-      </c>
-      <c r="Y24" s="0" t="inlineStr">
-        <is>
-          <t>BOSS-大盾战士</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>10200016&amp;10300016&amp;</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
+        <v>2000000001</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>白剑伟</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
       <c r="A25" s="2" t="n">
-        <v>2000000001</v>
+        <v>2000000002</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2674,7 +2710,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
+          <t>5050011&amp;5070005&amp;</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2684,23 +2720,17 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10200016&amp;10300016&amp;</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr"/>
+          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="n">
-        <v>2000000001</v>
+        <v>2000000002</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>5</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
@@ -2712,105 +2742,105 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>白剑伟</t>
+          <t>宛家伟</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="3">
       <c r="A26" s="2" t="n">
-        <v>2000000002</v>
+        <v>2000000003</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+        <v>99</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>5050011&amp;5070005&amp;</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="L26" s="0" t="inlineStr">
+        <is>
+          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
+        </is>
+      </c>
+      <c r="M26" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
+          <t>40200006&amp;40300003&amp;41000004&amp;</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>2000000002</v>
+        <v>2000000003</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W26" s="2" t="n">
+      <c r="W26" s="0" t="n">
         <v>4</v>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>宛家伟</t>
+          <t>雷神天尊斩</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000004</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2856,7 +2886,7 @@
       </c>
       <c r="L27" s="0" t="inlineStr">
         <is>
-          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
+          <t>1030006&amp;1040002&amp;1050012&amp;1060002&amp;</t>
         </is>
       </c>
       <c r="M27" s="0" t="inlineStr">
@@ -2866,17 +2896,21 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>40200006&amp;40300003&amp;41000004&amp;</t>
-        </is>
-      </c>
+          <t>10300011&amp;10200011&amp;</t>
+        </is>
+      </c>
+      <c r="O27" s="0" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000004</v>
       </c>
       <c r="Q27" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R27" s="2" t="n">
-        <v>3</v>
+      <c r="R27" s="2" t="n"/>
+      <c r="U27" s="0" t="inlineStr">
+        <is>
+          <t>3,255,255,255,255&amp;6,178,38,38,255&amp;</t>
+        </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
@@ -2888,105 +2922,49 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>雷神天尊斩</t>
+          <t>卡米莉娅</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
-      <c r="A28" s="2" t="n">
-        <v>2000000004</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" s="0" t="inlineStr">
-        <is>
-          <t>1030006&amp;1040002&amp;1050012&amp;1060002&amp;</t>
-        </is>
-      </c>
-      <c r="M28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>10300011&amp;10200011&amp;</t>
-        </is>
-      </c>
-      <c r="O28" s="0" t="inlineStr"/>
-      <c r="P28" s="2" t="n">
-        <v>2000000004</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="R28" s="2" t="n"/>
-      <c r="U28" s="0" t="inlineStr">
-        <is>
-          <t>3,255,255,255,255&amp;6,178,38,38,255&amp;</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>cn</t>
-        </is>
+      <c r="A28" s="0" t="n">
+        <v>3000010011</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O28" s="0" t="inlineStr">
+        <is>
+          <t>10000002,N</t>
+        </is>
+      </c>
+      <c r="P28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="W28" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t>卡米莉娅</t>
+        <v>1</v>
+      </c>
+      <c r="Y28" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000010011</v>
+        <v>3000010012</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>1001</v>
@@ -3002,27 +2980,27 @@
       </c>
       <c r="O29" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W29" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y29" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级1</t>
+          <t>议会随机议员-生物1001-评级2</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000010012</v>
+        <v>3000010013</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>1001</v>
@@ -3038,27 +3016,27 @@
       </c>
       <c r="O30" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W30" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y30" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级2</t>
+          <t>议会随机议员-生物1001-评级3</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="3">
       <c r="A31" s="0" t="n">
-        <v>3000010013</v>
+        <v>3000010014</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>1001</v>
@@ -3074,27 +3052,27 @@
       </c>
       <c r="O31" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W31" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级3</t>
+          <t>议会随机议员-生物1001-评级4</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="3">
       <c r="A32" s="0" t="n">
-        <v>3000010014</v>
+        <v>3000010015</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>1001</v>
@@ -3110,30 +3088,31 @@
       </c>
       <c r="O32" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="0" t="n">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="S32" s="0" t="inlineStr"/>
       <c r="W32" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级4</t>
+          <t>议会随机议员-生物1001-评级5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>3000010015</v>
+        <v>3000010021</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>3</v>
@@ -3146,28 +3125,27 @@
       </c>
       <c r="O33" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="S33" s="0" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="W33" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级5</t>
+          <t>议会随机议员-生物1002-评级1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>3000010021</v>
+        <v>3000010022</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>1002</v>
@@ -3183,27 +3161,27 @@
       </c>
       <c r="O34" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W34" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级1</t>
+          <t>议会随机议员-生物1002-评级2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>3000010022</v>
+        <v>3000010023</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>1002</v>
@@ -3219,27 +3197,27 @@
       </c>
       <c r="O35" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P35" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级2</t>
+          <t>议会随机议员-生物1002-评级3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>3000010023</v>
+        <v>3000010024</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1002</v>
@@ -3255,27 +3233,27 @@
       </c>
       <c r="O36" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P36" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W36" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级3</t>
+          <t>议会随机议员-生物1002-评级4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>3000010024</v>
+        <v>3000010025</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>1002</v>
@@ -3291,30 +3269,30 @@
       </c>
       <c r="O37" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W37" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级4</t>
+          <t>议会随机议员-生物1002-评级5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>3000010025</v>
+        <v>3000010031</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>3</v>
@@ -3327,27 +3305,27 @@
       </c>
       <c r="O38" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W38" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级5</t>
+          <t>议会随机议员-生物1003-评级1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>3000010031</v>
+        <v>3000010032</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>1003</v>
@@ -3363,27 +3341,27 @@
       </c>
       <c r="O39" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W39" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级1</t>
+          <t>议会随机议员-生物1003-评级2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>3000010032</v>
+        <v>3000010033</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>1003</v>
@@ -3399,27 +3377,27 @@
       </c>
       <c r="O40" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P40" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W40" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级2</t>
+          <t>议会随机议员-生物1003-评级3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>3000010033</v>
+        <v>3000010034</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>1003</v>
@@ -3435,27 +3413,27 @@
       </c>
       <c r="O41" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W41" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级3</t>
+          <t>议会随机议员-生物1003-评级4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>3000010034</v>
+        <v>3000010035</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>1003</v>
@@ -3471,30 +3449,30 @@
       </c>
       <c r="O42" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W42" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级4</t>
+          <t>议会随机议员-生物1003-评级5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>3000010035</v>
+        <v>3000010041</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>3</v>
@@ -3507,27 +3485,27 @@
       </c>
       <c r="O43" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P43" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W43" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级5</t>
+          <t>议会随机议员-生物1004-评级1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>3000010041</v>
+        <v>3000010042</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>1004</v>
@@ -3543,27 +3521,27 @@
       </c>
       <c r="O44" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P44" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级1</t>
+          <t>议会随机议员-生物1004-评级2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>3000010042</v>
+        <v>3000010043</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>1004</v>
@@ -3579,27 +3557,27 @@
       </c>
       <c r="O45" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P45" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级2</t>
+          <t>议会随机议员-生物1004-评级3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>3000010043</v>
+        <v>3000010044</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>1004</v>
@@ -3615,27 +3593,27 @@
       </c>
       <c r="O46" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P46" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W46" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y46" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级3</t>
+          <t>议会随机议员-生物1004-评级4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>3000010044</v>
+        <v>3000010045</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>1004</v>
@@ -3651,30 +3629,30 @@
       </c>
       <c r="O47" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P47" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W47" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y47" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级4</t>
+          <t>议会随机议员-生物1004-评级5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>3000010045</v>
+        <v>3000020011</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>1004</v>
+        <v>2001</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>3</v>
@@ -3687,27 +3665,27 @@
       </c>
       <c r="O48" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P48" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W48" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y48" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级5</t>
+          <t>议会随机议员-生物2001-评级1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>3000020011</v>
+        <v>3000020012</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>2001</v>
@@ -3723,27 +3701,27 @@
       </c>
       <c r="O49" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P49" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W49" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y49" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级1</t>
+          <t>议会随机议员-生物2001-评级2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>3000020012</v>
+        <v>3000020013</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>2001</v>
@@ -3759,27 +3737,27 @@
       </c>
       <c r="O50" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P50" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W50" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y50" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级2</t>
+          <t>议会随机议员-生物2001-评级3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>3000020013</v>
+        <v>3000020014</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>2001</v>
@@ -3795,27 +3773,27 @@
       </c>
       <c r="O51" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P51" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W51" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y51" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级3</t>
+          <t>议会随机议员-生物2001-评级4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>3000020014</v>
+        <v>3000020015</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>2001</v>
@@ -3831,30 +3809,30 @@
       </c>
       <c r="O52" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P52" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W52" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y52" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级4</t>
+          <t>议会随机议员-生物2001-评级5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>3000020015</v>
+        <v>3000020021</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>3</v>
@@ -3867,27 +3845,27 @@
       </c>
       <c r="O53" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y53" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级5</t>
+          <t>议会随机议员-生物2002-评级1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>3000020021</v>
+        <v>3000020022</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>2002</v>
@@ -3903,27 +3881,27 @@
       </c>
       <c r="O54" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P54" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W54" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级1</t>
+          <t>议会随机议员-生物2002-评级2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>3000020022</v>
+        <v>3000020023</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>2002</v>
@@ -3939,27 +3917,27 @@
       </c>
       <c r="O55" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P55" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级2</t>
+          <t>议会随机议员-生物2002-评级3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>3000020023</v>
+        <v>3000020024</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>2002</v>
@@ -3975,27 +3953,27 @@
       </c>
       <c r="O56" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P56" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W56" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级3</t>
+          <t>议会随机议员-生物2002-评级4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>3000020024</v>
+        <v>3000020025</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>2002</v>
@@ -4011,30 +3989,30 @@
       </c>
       <c r="O57" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P57" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级4</t>
+          <t>议会随机议员-生物2002-评级5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>3000020025</v>
+        <v>3000020031</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>3</v>
@@ -4047,27 +4025,27 @@
       </c>
       <c r="O58" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P58" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W58" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级5</t>
+          <t>议会随机议员-生物2003-评级1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>3000020031</v>
+        <v>3000020032</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>2003</v>
@@ -4083,27 +4061,27 @@
       </c>
       <c r="O59" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P59" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W59" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级1</t>
+          <t>议会随机议员-生物2003-评级2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>3000020032</v>
+        <v>3000020033</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>2003</v>
@@ -4119,27 +4097,27 @@
       </c>
       <c r="O60" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P60" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W60" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级2</t>
+          <t>议会随机议员-生物2003-评级3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3000020033</v>
+        <v>3000020034</v>
       </c>
       <c r="B61" s="0" t="n">
         <v>2003</v>
@@ -4155,27 +4133,27 @@
       </c>
       <c r="O61" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P61" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W61" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级3</t>
+          <t>议会随机议员-生物2003-评级4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3000020034</v>
+        <v>3000020035</v>
       </c>
       <c r="B62" s="0" t="n">
         <v>2003</v>
@@ -4191,30 +4169,30 @@
       </c>
       <c r="O62" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P62" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W62" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级4</t>
+          <t>议会随机议员-生物2003-评级5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>3000020035</v>
+        <v>3000020041</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>3</v>
@@ -4227,27 +4205,27 @@
       </c>
       <c r="O63" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P63" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y63" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级5</t>
+          <t>议会随机议员-生物2004-评级1</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="3">
       <c r="A64" s="0" t="n">
-        <v>3000020041</v>
+        <v>3000020042</v>
       </c>
       <c r="B64" s="0" t="n">
         <v>2004</v>
@@ -4263,27 +4241,27 @@
       </c>
       <c r="O64" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P64" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W64" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级1</t>
+          <t>议会随机议员-生物2004-评级2</t>
         </is>
       </c>
     </row>
     <row r="65" ht="12" customHeight="1" s="3">
       <c r="A65" s="0" t="n">
-        <v>3000020042</v>
+        <v>3000020043</v>
       </c>
       <c r="B65" s="0" t="n">
         <v>2004</v>
@@ -4299,27 +4277,27 @@
       </c>
       <c r="O65" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P65" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级2</t>
+          <t>议会随机议员-生物2004-评级3</t>
         </is>
       </c>
     </row>
     <row r="66" ht="12" customHeight="1" s="3">
       <c r="A66" s="0" t="n">
-        <v>3000020043</v>
+        <v>3000020044</v>
       </c>
       <c r="B66" s="0" t="n">
         <v>2004</v>
@@ -4335,27 +4313,27 @@
       </c>
       <c r="O66" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P66" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W66" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级3</t>
+          <t>议会随机议员-生物2004-评级4</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="3">
       <c r="A67" s="0" t="n">
-        <v>3000020044</v>
+        <v>3000020045</v>
       </c>
       <c r="B67" s="0" t="n">
         <v>2004</v>
@@ -4371,30 +4349,30 @@
       </c>
       <c r="O67" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P67" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级4</t>
+          <t>议会随机议员-生物2004-评级5</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="3">
       <c r="A68" s="0" t="n">
-        <v>3000020045</v>
+        <v>3000030011</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>2004</v>
+        <v>3001</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>3</v>
@@ -4407,27 +4385,27 @@
       </c>
       <c r="O68" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P68" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级5</t>
+          <t>议会随机议员-生物3001-评级1</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>3000030011</v>
+        <v>3000030012</v>
       </c>
       <c r="B69" s="0" t="n">
         <v>3001</v>
@@ -4443,27 +4421,27 @@
       </c>
       <c r="O69" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P69" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W69" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级1</t>
+          <t>议会随机议员-生物3001-评级2</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>3000030012</v>
+        <v>3000030013</v>
       </c>
       <c r="B70" s="0" t="n">
         <v>3001</v>
@@ -4479,27 +4457,27 @@
       </c>
       <c r="O70" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P70" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级2</t>
+          <t>议会随机议员-生物3001-评级3</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>3000030013</v>
+        <v>3000030014</v>
       </c>
       <c r="B71" s="0" t="n">
         <v>3001</v>
@@ -4515,27 +4493,27 @@
       </c>
       <c r="O71" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P71" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W71" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级3</t>
+          <t>议会随机议员-生物3001-评级4</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="3">
       <c r="A72" s="0" t="n">
-        <v>3000030014</v>
+        <v>3000030015</v>
       </c>
       <c r="B72" s="0" t="n">
         <v>3001</v>
@@ -4551,30 +4529,30 @@
       </c>
       <c r="O72" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P72" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级4</t>
+          <t>议会随机议员-生物3001-评级5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>3000030015</v>
+        <v>3000030021</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>3</v>
@@ -4587,27 +4565,27 @@
       </c>
       <c r="O73" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P73" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级5</t>
+          <t>议会随机议员-生物3002-评级1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>3000030021</v>
+        <v>3000030022</v>
       </c>
       <c r="B74" s="0" t="n">
         <v>3002</v>
@@ -4623,27 +4601,27 @@
       </c>
       <c r="O74" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P74" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W74" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级1</t>
+          <t>议会随机议员-生物3002-评级2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>3000030022</v>
+        <v>3000030023</v>
       </c>
       <c r="B75" s="0" t="n">
         <v>3002</v>
@@ -4659,27 +4637,27 @@
       </c>
       <c r="O75" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P75" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级2</t>
+          <t>议会随机议员-生物3002-评级3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>3000030023</v>
+        <v>3000030024</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>3002</v>
@@ -4695,27 +4673,27 @@
       </c>
       <c r="O76" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P76" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W76" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级3</t>
+          <t>议会随机议员-生物3002-评级4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>3000030024</v>
+        <v>3000030025</v>
       </c>
       <c r="B77" s="0" t="n">
         <v>3002</v>
@@ -4731,30 +4709,30 @@
       </c>
       <c r="O77" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P77" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级4</t>
+          <t>议会随机议员-生物3002-评级5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>3000030025</v>
+        <v>3000030031</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>3</v>
@@ -4767,27 +4745,27 @@
       </c>
       <c r="O78" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P78" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级5</t>
+          <t>议会随机议员-生物3003-评级1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>3000030031</v>
+        <v>3000030032</v>
       </c>
       <c r="B79" s="0" t="n">
         <v>3003</v>
@@ -4803,27 +4781,27 @@
       </c>
       <c r="O79" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P79" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级1</t>
+          <t>议会随机议员-生物3003-评级2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>3000030032</v>
+        <v>3000030033</v>
       </c>
       <c r="B80" s="0" t="n">
         <v>3003</v>
@@ -4839,27 +4817,27 @@
       </c>
       <c r="O80" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P80" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级2</t>
+          <t>议会随机议员-生物3003-评级3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>3000030033</v>
+        <v>3000030034</v>
       </c>
       <c r="B81" s="0" t="n">
         <v>3003</v>
@@ -4875,27 +4853,27 @@
       </c>
       <c r="O81" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P81" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q81" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W81" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级3</t>
+          <t>议会随机议员-生物3003-评级4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>3000030034</v>
+        <v>3000030035</v>
       </c>
       <c r="B82" s="0" t="n">
         <v>3003</v>
@@ -4911,30 +4889,30 @@
       </c>
       <c r="O82" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P82" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级4</t>
+          <t>议会随机议员-生物3003-评级5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>3000030035</v>
+        <v>3000030041</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>3</v>
@@ -4947,27 +4925,27 @@
       </c>
       <c r="O83" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P83" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级5</t>
+          <t>议会随机议员-生物3004-评级1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>3000030041</v>
+        <v>3000030042</v>
       </c>
       <c r="B84" s="0" t="n">
         <v>3004</v>
@@ -4983,27 +4961,27 @@
       </c>
       <c r="O84" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P84" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q84" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y84" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级1</t>
+          <t>议会随机议员-生物3004-评级2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>3000030042</v>
+        <v>3000030043</v>
       </c>
       <c r="B85" s="0" t="n">
         <v>3004</v>
@@ -5019,27 +4997,27 @@
       </c>
       <c r="O85" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P85" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q85" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y85" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级2</t>
+          <t>议会随机议员-生物3004-评级3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>3000030043</v>
+        <v>3000030044</v>
       </c>
       <c r="B86" s="0" t="n">
         <v>3004</v>
@@ -5055,27 +5033,27 @@
       </c>
       <c r="O86" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P86" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W86" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y86" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级3</t>
+          <t>议会随机议员-生物3004-评级4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>3000030044</v>
+        <v>3000030045</v>
       </c>
       <c r="B87" s="0" t="n">
         <v>3004</v>
@@ -5091,30 +5069,30 @@
       </c>
       <c r="O87" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P87" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y87" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级4</t>
+          <t>议会随机议员-生物3004-评级5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>3000030045</v>
+        <v>3000040011</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>3004</v>
+        <v>4001</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>3</v>
@@ -5127,27 +5105,27 @@
       </c>
       <c r="O88" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P88" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q88" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y88" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级5</t>
+          <t>议会随机议员-生物4001-评级1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>3000040011</v>
+        <v>3000040012</v>
       </c>
       <c r="B89" s="0" t="n">
         <v>4001</v>
@@ -5163,27 +5141,27 @@
       </c>
       <c r="O89" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P89" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q89" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W89" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y89" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级1</t>
+          <t>议会随机议员-生物4001-评级2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>3000040012</v>
+        <v>3000040013</v>
       </c>
       <c r="B90" s="0" t="n">
         <v>4001</v>
@@ -5199,27 +5177,27 @@
       </c>
       <c r="O90" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P90" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y90" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级2</t>
+          <t>议会随机议员-生物4001-评级3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>3000040013</v>
+        <v>3000040014</v>
       </c>
       <c r="B91" s="0" t="n">
         <v>4001</v>
@@ -5235,27 +5213,27 @@
       </c>
       <c r="O91" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P91" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q91" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W91" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y91" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级3</t>
+          <t>议会随机议员-生物4001-评级4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>3000040014</v>
+        <v>3000040015</v>
       </c>
       <c r="B92" s="0" t="n">
         <v>4001</v>
@@ -5271,30 +5249,30 @@
       </c>
       <c r="O92" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P92" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q92" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y92" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级4</t>
+          <t>议会随机议员-生物4001-评级5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>3000040015</v>
+        <v>3000040021</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>3</v>
@@ -5307,27 +5285,27 @@
       </c>
       <c r="O93" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P93" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q93" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y93" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级5</t>
+          <t>议会随机议员-生物4002-评级1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>3000040021</v>
+        <v>3000040022</v>
       </c>
       <c r="B94" s="0" t="n">
         <v>4002</v>
@@ -5343,27 +5321,27 @@
       </c>
       <c r="O94" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P94" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W94" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y94" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级1</t>
+          <t>议会随机议员-生物4002-评级2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>3000040022</v>
+        <v>3000040023</v>
       </c>
       <c r="B95" s="0" t="n">
         <v>4002</v>
@@ -5379,27 +5357,27 @@
       </c>
       <c r="O95" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P95" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q95" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W95" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y95" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级2</t>
+          <t>议会随机议员-生物4002-评级3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>3000040023</v>
+        <v>3000040024</v>
       </c>
       <c r="B96" s="0" t="n">
         <v>4002</v>
@@ -5415,27 +5393,27 @@
       </c>
       <c r="O96" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P96" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q96" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W96" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y96" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级3</t>
+          <t>议会随机议员-生物4002-评级4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>3000040024</v>
+        <v>3000040025</v>
       </c>
       <c r="B97" s="0" t="n">
         <v>4002</v>
@@ -5451,30 +5429,30 @@
       </c>
       <c r="O97" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P97" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q97" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W97" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y97" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级4</t>
+          <t>议会随机议员-生物4002-评级5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>3000040025</v>
+        <v>3000040031</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>3</v>
@@ -5487,27 +5465,27 @@
       </c>
       <c r="O98" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P98" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q98" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W98" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y98" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级5</t>
+          <t>议会随机议员-生物4003-评级1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>3000040031</v>
+        <v>3000040032</v>
       </c>
       <c r="B99" s="0" t="n">
         <v>4003</v>
@@ -5523,27 +5501,27 @@
       </c>
       <c r="O99" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P99" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q99" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y99" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级1</t>
+          <t>议会随机议员-生物4003-评级2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>3000040032</v>
+        <v>3000040033</v>
       </c>
       <c r="B100" s="0" t="n">
         <v>4003</v>
@@ -5559,27 +5537,27 @@
       </c>
       <c r="O100" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P100" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q100" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W100" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y100" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级2</t>
+          <t>议会随机议员-生物4003-评级3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>3000040033</v>
+        <v>3000040034</v>
       </c>
       <c r="B101" s="0" t="n">
         <v>4003</v>
@@ -5595,27 +5573,27 @@
       </c>
       <c r="O101" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P101" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q101" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W101" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y101" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级3</t>
+          <t>议会随机议员-生物4003-评级4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>3000040034</v>
+        <v>3000040035</v>
       </c>
       <c r="B102" s="0" t="n">
         <v>4003</v>
@@ -5631,30 +5609,30 @@
       </c>
       <c r="O102" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P102" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q102" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y102" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级4</t>
+          <t>议会随机议员-生物4003-评级5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>3000040035</v>
+        <v>3000040041</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>3</v>
@@ -5667,27 +5645,27 @@
       </c>
       <c r="O103" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P103" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q103" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y103" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级5</t>
+          <t>议会随机议员-生物4004-评级1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>3000040041</v>
+        <v>3000040042</v>
       </c>
       <c r="B104" s="0" t="n">
         <v>4004</v>
@@ -5703,27 +5681,27 @@
       </c>
       <c r="O104" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P104" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q104" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W104" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y104" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级1</t>
+          <t>议会随机议员-生物4004-评级2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>3000040042</v>
+        <v>3000040043</v>
       </c>
       <c r="B105" s="0" t="n">
         <v>4004</v>
@@ -5739,27 +5717,27 @@
       </c>
       <c r="O105" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P105" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q105" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y105" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级2</t>
+          <t>议会随机议员-生物4004-评级3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>3000040043</v>
+        <v>3000040044</v>
       </c>
       <c r="B106" s="0" t="n">
         <v>4004</v>
@@ -5775,27 +5753,27 @@
       </c>
       <c r="O106" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P106" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q106" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W106" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y106" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级3</t>
+          <t>议会随机议员-生物4004-评级4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>3000040044</v>
+        <v>3000040045</v>
       </c>
       <c r="B107" s="0" t="n">
         <v>4004</v>
@@ -5811,30 +5789,30 @@
       </c>
       <c r="O107" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P107" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q107" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y107" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级4</t>
+          <t>议会随机议员-生物4004-评级5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>3000040045</v>
+        <v>3000040051</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>3</v>
@@ -5847,27 +5825,27 @@
       </c>
       <c r="O108" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P108" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y108" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级5</t>
+          <t>议会随机议员-生物4005-评级1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>3000040051</v>
+        <v>3000040052</v>
       </c>
       <c r="B109" s="0" t="n">
         <v>4005</v>
@@ -5883,27 +5861,27 @@
       </c>
       <c r="O109" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P109" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q109" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W109" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y109" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级1</t>
+          <t>议会随机议员-生物4005-评级2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>3000040052</v>
+        <v>3000040053</v>
       </c>
       <c r="B110" s="0" t="n">
         <v>4005</v>
@@ -5919,27 +5897,27 @@
       </c>
       <c r="O110" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P110" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q110" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W110" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y110" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级2</t>
+          <t>议会随机议员-生物4005-评级3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>3000040053</v>
+        <v>3000040054</v>
       </c>
       <c r="B111" s="0" t="n">
         <v>4005</v>
@@ -5955,27 +5933,27 @@
       </c>
       <c r="O111" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P111" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q111" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W111" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y111" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级3</t>
+          <t>议会随机议员-生物4005-评级4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>3000040054</v>
+        <v>3000040055</v>
       </c>
       <c r="B112" s="0" t="n">
         <v>4005</v>
@@ -5991,30 +5969,30 @@
       </c>
       <c r="O112" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P112" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W112" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y112" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级4</t>
+          <t>议会随机议员-生物4005-评级5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>3000040055</v>
+        <v>3000050011</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>4005</v>
+        <v>5001</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>3</v>
@@ -6027,27 +6005,27 @@
       </c>
       <c r="O113" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P113" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q113" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y113" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级5</t>
+          <t>议会随机议员-生物5001-评级1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>3000050011</v>
+        <v>3000050012</v>
       </c>
       <c r="B114" s="0" t="n">
         <v>5001</v>
@@ -6063,27 +6041,27 @@
       </c>
       <c r="O114" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P114" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q114" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W114" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y114" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级1</t>
+          <t>议会随机议员-生物5001-评级2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>3000050012</v>
+        <v>3000050013</v>
       </c>
       <c r="B115" s="0" t="n">
         <v>5001</v>
@@ -6099,27 +6077,27 @@
       </c>
       <c r="O115" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P115" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W115" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y115" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级2</t>
+          <t>议会随机议员-生物5001-评级3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>3000050013</v>
+        <v>3000050014</v>
       </c>
       <c r="B116" s="0" t="n">
         <v>5001</v>
@@ -6135,27 +6113,27 @@
       </c>
       <c r="O116" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P116" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q116" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W116" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y116" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级3</t>
+          <t>议会随机议员-生物5001-评级4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>3000050014</v>
+        <v>3000050015</v>
       </c>
       <c r="B117" s="0" t="n">
         <v>5001</v>
@@ -6171,30 +6149,30 @@
       </c>
       <c r="O117" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P117" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q117" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W117" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y117" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级4</t>
+          <t>议会随机议员-生物5001-评级5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>3000050015</v>
+        <v>3000050021</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>3</v>
@@ -6207,27 +6185,27 @@
       </c>
       <c r="O118" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P118" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q118" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y118" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级5</t>
+          <t>议会随机议员-生物5002-评级1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>3000050021</v>
+        <v>3000050022</v>
       </c>
       <c r="B119" s="0" t="n">
         <v>5002</v>
@@ -6243,27 +6221,27 @@
       </c>
       <c r="O119" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P119" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q119" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W119" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y119" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级1</t>
+          <t>议会随机议员-生物5002-评级2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>3000050022</v>
+        <v>3000050023</v>
       </c>
       <c r="B120" s="0" t="n">
         <v>5002</v>
@@ -6279,27 +6257,27 @@
       </c>
       <c r="O120" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P120" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q120" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W120" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y120" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级2</t>
+          <t>议会随机议员-生物5002-评级3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>3000050023</v>
+        <v>3000050024</v>
       </c>
       <c r="B121" s="0" t="n">
         <v>5002</v>
@@ -6315,27 +6293,27 @@
       </c>
       <c r="O121" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P121" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W121" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y121" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级3</t>
+          <t>议会随机议员-生物5002-评级4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>3000050024</v>
+        <v>3000050025</v>
       </c>
       <c r="B122" s="0" t="n">
         <v>5002</v>
@@ -6351,30 +6329,30 @@
       </c>
       <c r="O122" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P122" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q122" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W122" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y122" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级4</t>
+          <t>议会随机议员-生物5002-评级5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>3000050025</v>
+        <v>3000050031</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>3</v>
@@ -6387,27 +6365,27 @@
       </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P123" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q123" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y123" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级5</t>
+          <t>议会随机议员-生物5003-评级1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>3000050031</v>
+        <v>3000050032</v>
       </c>
       <c r="B124" s="0" t="n">
         <v>5003</v>
@@ -6423,27 +6401,27 @@
       </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P124" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q124" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W124" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级1</t>
+          <t>议会随机议员-生物5003-评级2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>3000050032</v>
+        <v>3000050033</v>
       </c>
       <c r="B125" s="0" t="n">
         <v>5003</v>
@@ -6459,27 +6437,27 @@
       </c>
       <c r="O125" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P125" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q125" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级2</t>
+          <t>议会随机议员-生物5003-评级3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>3000050033</v>
+        <v>3000050034</v>
       </c>
       <c r="B126" s="0" t="n">
         <v>5003</v>
@@ -6495,27 +6473,27 @@
       </c>
       <c r="O126" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P126" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q126" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W126" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级3</t>
+          <t>议会随机议员-生物5003-评级4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>3000050034</v>
+        <v>3000050035</v>
       </c>
       <c r="B127" s="0" t="n">
         <v>5003</v>
@@ -6531,30 +6509,30 @@
       </c>
       <c r="O127" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P127" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q127" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W127" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级4</t>
+          <t>议会随机议员-生物5003-评级5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>3000050035</v>
+        <v>3000050041</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>3</v>
@@ -6567,27 +6545,27 @@
       </c>
       <c r="O128" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P128" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q128" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级5</t>
+          <t>议会随机议员-生物5004-评级1</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000050041</v>
+        <v>3000050042</v>
       </c>
       <c r="B129" s="0" t="n">
         <v>5004</v>
@@ -6603,27 +6581,27 @@
       </c>
       <c r="O129" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P129" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q129" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W129" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级1</t>
+          <t>议会随机议员-生物5004-评级2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000050042</v>
+        <v>3000050043</v>
       </c>
       <c r="B130" s="0" t="n">
         <v>5004</v>
@@ -6639,27 +6617,27 @@
       </c>
       <c r="O130" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P130" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q130" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W130" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级2</t>
+          <t>议会随机议员-生物5004-评级3</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000050043</v>
+        <v>3000050044</v>
       </c>
       <c r="B131" s="0" t="n">
         <v>5004</v>
@@ -6675,27 +6653,27 @@
       </c>
       <c r="O131" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P131" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q131" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W131" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y131" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级3</t>
+          <t>议会随机议员-生物5004-评级4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000050044</v>
+        <v>3000050045</v>
       </c>
       <c r="B132" s="0" t="n">
         <v>5004</v>
@@ -6711,30 +6689,30 @@
       </c>
       <c r="O132" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P132" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q132" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W132" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y132" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级4</t>
+          <t>议会随机议员-生物5004-评级5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000050045</v>
+        <v>3000060011</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>3</v>
@@ -6747,27 +6725,27 @@
       </c>
       <c r="O133" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P133" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q133" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W133" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级5</t>
+          <t>议会随机议员-生物6001-评级1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000060011</v>
+        <v>3000060012</v>
       </c>
       <c r="B134" s="0" t="n">
         <v>6001</v>
@@ -6783,27 +6761,27 @@
       </c>
       <c r="O134" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P134" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q134" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W134" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y134" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级1</t>
+          <t>议会随机议员-生物6001-评级2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000060012</v>
+        <v>3000060013</v>
       </c>
       <c r="B135" s="0" t="n">
         <v>6001</v>
@@ -6819,27 +6797,27 @@
       </c>
       <c r="O135" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P135" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q135" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W135" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y135" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级2</t>
+          <t>议会随机议员-生物6001-评级3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000060013</v>
+        <v>3000060014</v>
       </c>
       <c r="B136" s="0" t="n">
         <v>6001</v>
@@ -6855,27 +6833,27 @@
       </c>
       <c r="O136" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P136" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q136" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W136" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y136" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级3</t>
+          <t>议会随机议员-生物6001-评级4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000060014</v>
+        <v>3000060015</v>
       </c>
       <c r="B137" s="0" t="n">
         <v>6001</v>
@@ -6891,30 +6869,30 @@
       </c>
       <c r="O137" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P137" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q137" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W137" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y137" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级4</t>
+          <t>议会随机议员-生物6001-评级5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000060015</v>
+        <v>3000060021</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="C138" s="0" t="n">
         <v>3</v>
@@ -6927,27 +6905,27 @@
       </c>
       <c r="O138" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P138" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q138" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W138" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y138" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级5</t>
+          <t>议会随机议员-生物6002-评级1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>3000060021</v>
+        <v>3000060022</v>
       </c>
       <c r="B139" s="0" t="n">
         <v>6002</v>
@@ -6963,27 +6941,27 @@
       </c>
       <c r="O139" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P139" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q139" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W139" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y139" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级1</t>
+          <t>议会随机议员-生物6002-评级2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>3000060022</v>
+        <v>3000060023</v>
       </c>
       <c r="B140" s="0" t="n">
         <v>6002</v>
@@ -6999,27 +6977,27 @@
       </c>
       <c r="O140" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P140" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q140" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W140" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y140" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级2</t>
+          <t>议会随机议员-生物6002-评级3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>3000060023</v>
+        <v>3000060024</v>
       </c>
       <c r="B141" s="0" t="n">
         <v>6002</v>
@@ -7035,27 +7013,27 @@
       </c>
       <c r="O141" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P141" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q141" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W141" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y141" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级3</t>
+          <t>议会随机议员-生物6002-评级4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>3000060024</v>
+        <v>3000060025</v>
       </c>
       <c r="B142" s="0" t="n">
         <v>6002</v>
@@ -7071,30 +7049,30 @@
       </c>
       <c r="O142" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P142" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q142" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W142" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y142" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级4</t>
+          <t>议会随机议员-生物6002-评级5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>3000060025</v>
+        <v>3000060031</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>3</v>
@@ -7107,27 +7085,27 @@
       </c>
       <c r="O143" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P143" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q143" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W143" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y143" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级5</t>
+          <t>议会随机议员-生物6003-评级1</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>3000060031</v>
+        <v>3000060032</v>
       </c>
       <c r="B144" s="0" t="n">
         <v>6003</v>
@@ -7143,27 +7121,27 @@
       </c>
       <c r="O144" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P144" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q144" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W144" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y144" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级1</t>
+          <t>议会随机议员-生物6003-评级2</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>3000060032</v>
+        <v>3000060033</v>
       </c>
       <c r="B145" s="0" t="n">
         <v>6003</v>
@@ -7179,27 +7157,27 @@
       </c>
       <c r="O145" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P145" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q145" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W145" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y145" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级2</t>
+          <t>议会随机议员-生物6003-评级3</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>3000060033</v>
+        <v>3000060034</v>
       </c>
       <c r="B146" s="0" t="n">
         <v>6003</v>
@@ -7215,27 +7193,27 @@
       </c>
       <c r="O146" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P146" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q146" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W146" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y146" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级3</t>
+          <t>议会随机议员-生物6003-评级4</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>3000060034</v>
+        <v>3000060035</v>
       </c>
       <c r="B147" s="0" t="n">
         <v>6003</v>
@@ -7251,30 +7229,30 @@
       </c>
       <c r="O147" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P147" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q147" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W147" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y147" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级4</t>
+          <t>议会随机议员-生物6003-评级5</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>3000060035</v>
+        <v>3000060041</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="C148" s="0" t="n">
         <v>3</v>
@@ -7287,27 +7265,27 @@
       </c>
       <c r="O148" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P148" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q148" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W148" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y148" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级5</t>
+          <t>议会随机议员-生物6004-评级1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>3000060041</v>
+        <v>3000060042</v>
       </c>
       <c r="B149" s="0" t="n">
         <v>6004</v>
@@ -7323,27 +7301,27 @@
       </c>
       <c r="O149" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P149" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q149" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W149" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y149" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级1</t>
+          <t>议会随机议员-生物6004-评级2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>3000060042</v>
+        <v>3000060043</v>
       </c>
       <c r="B150" s="0" t="n">
         <v>6004</v>
@@ -7359,27 +7337,27 @@
       </c>
       <c r="O150" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P150" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q150" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W150" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y150" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级2</t>
+          <t>议会随机议员-生物6004-评级3</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>3000060043</v>
+        <v>3000060044</v>
       </c>
       <c r="B151" s="0" t="n">
         <v>6004</v>
@@ -7395,27 +7373,27 @@
       </c>
       <c r="O151" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P151" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q151" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W151" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y151" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级3</t>
+          <t>议会随机议员-生物6004-评级4</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>3000060044</v>
+        <v>3000060045</v>
       </c>
       <c r="B152" s="0" t="n">
         <v>6004</v>
@@ -7431,30 +7409,30 @@
       </c>
       <c r="O152" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P152" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q152" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W152" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y152" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级4</t>
+          <t>议会随机议员-生物6004-评级5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>3000060045</v>
+        <v>3000060051</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="C153" s="0" t="n">
         <v>3</v>
@@ -7467,27 +7445,27 @@
       </c>
       <c r="O153" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P153" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q153" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W153" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y153" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级5</t>
+          <t>议会随机议员-生物6005-评级1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>3000060051</v>
+        <v>3000060052</v>
       </c>
       <c r="B154" s="0" t="n">
         <v>6005</v>
@@ -7503,27 +7481,27 @@
       </c>
       <c r="O154" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P154" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q154" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W154" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y154" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级1</t>
+          <t>议会随机议员-生物6005-评级2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>3000060052</v>
+        <v>3000060053</v>
       </c>
       <c r="B155" s="0" t="n">
         <v>6005</v>
@@ -7539,27 +7517,27 @@
       </c>
       <c r="O155" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P155" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q155" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W155" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y155" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级2</t>
+          <t>议会随机议员-生物6005-评级3</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>3000060053</v>
+        <v>3000060054</v>
       </c>
       <c r="B156" s="0" t="n">
         <v>6005</v>
@@ -7575,27 +7553,27 @@
       </c>
       <c r="O156" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P156" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q156" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W156" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y156" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级3</t>
+          <t>议会随机议员-生物6005-评级4</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>3000060054</v>
+        <v>3000060055</v>
       </c>
       <c r="B157" s="0" t="n">
         <v>6005</v>
@@ -7611,30 +7589,30 @@
       </c>
       <c r="O157" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P157" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q157" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W157" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y157" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级4</t>
+          <t>议会随机议员-生物6005-评级5</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>3000060055</v>
+        <v>3000070011</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>6005</v>
+        <v>7001</v>
       </c>
       <c r="C158" s="0" t="n">
         <v>3</v>
@@ -7647,27 +7625,27 @@
       </c>
       <c r="O158" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P158" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q158" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W158" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y158" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级5</t>
+          <t>议会随机议员-生物7001-评级1</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>3000070011</v>
+        <v>3000070012</v>
       </c>
       <c r="B159" s="0" t="n">
         <v>7001</v>
@@ -7683,27 +7661,27 @@
       </c>
       <c r="O159" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P159" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q159" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W159" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y159" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级1</t>
+          <t>议会随机议员-生物7001-评级2</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>3000070012</v>
+        <v>3000070013</v>
       </c>
       <c r="B160" s="0" t="n">
         <v>7001</v>
@@ -7719,27 +7697,27 @@
       </c>
       <c r="O160" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P160" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q160" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W160" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y160" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级2</t>
+          <t>议会随机议员-生物7001-评级3</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>3000070013</v>
+        <v>3000070014</v>
       </c>
       <c r="B161" s="0" t="n">
         <v>7001</v>
@@ -7755,27 +7733,27 @@
       </c>
       <c r="O161" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P161" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q161" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W161" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y161" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级3</t>
+          <t>议会随机议员-生物7001-评级4</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>3000070014</v>
+        <v>3000070015</v>
       </c>
       <c r="B162" s="0" t="n">
         <v>7001</v>
@@ -7791,30 +7769,30 @@
       </c>
       <c r="O162" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P162" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q162" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W162" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y162" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级4</t>
+          <t>议会随机议员-生物7001-评级5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>3000070015</v>
+        <v>3000070021</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="C163" s="0" t="n">
         <v>3</v>
@@ -7827,27 +7805,27 @@
       </c>
       <c r="O163" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P163" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q163" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W163" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y163" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级5</t>
+          <t>议会随机议员-生物7002-评级1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000070021</v>
+        <v>3000070022</v>
       </c>
       <c r="B164" s="0" t="n">
         <v>7002</v>
@@ -7863,27 +7841,27 @@
       </c>
       <c r="O164" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P164" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q164" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W164" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y164" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级1</t>
+          <t>议会随机议员-生物7002-评级2</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000070022</v>
+        <v>3000070023</v>
       </c>
       <c r="B165" s="0" t="n">
         <v>7002</v>
@@ -7899,27 +7877,27 @@
       </c>
       <c r="O165" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P165" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q165" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W165" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y165" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级2</t>
+          <t>议会随机议员-生物7002-评级3</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000070023</v>
+        <v>3000070024</v>
       </c>
       <c r="B166" s="0" t="n">
         <v>7002</v>
@@ -7935,27 +7913,27 @@
       </c>
       <c r="O166" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P166" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q166" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W166" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y166" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级3</t>
+          <t>议会随机议员-生物7002-评级4</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000070024</v>
+        <v>3000070025</v>
       </c>
       <c r="B167" s="0" t="n">
         <v>7002</v>
@@ -7971,30 +7949,30 @@
       </c>
       <c r="O167" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P167" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q167" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W167" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y167" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级4</t>
+          <t>议会随机议员-生物7002-评级5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000070025</v>
+        <v>3000070031</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="C168" s="0" t="n">
         <v>3</v>
@@ -8007,27 +7985,27 @@
       </c>
       <c r="O168" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P168" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q168" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W168" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y168" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级5</t>
+          <t>议会随机议员-生物7003-评级1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000070031</v>
+        <v>3000070032</v>
       </c>
       <c r="B169" s="0" t="n">
         <v>7003</v>
@@ -8043,27 +8021,27 @@
       </c>
       <c r="O169" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P169" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q169" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W169" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y169" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级1</t>
+          <t>议会随机议员-生物7003-评级2</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>3000070032</v>
+        <v>3000070033</v>
       </c>
       <c r="B170" s="0" t="n">
         <v>7003</v>
@@ -8079,27 +8057,27 @@
       </c>
       <c r="O170" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P170" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q170" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W170" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y170" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级2</t>
+          <t>议会随机议员-生物7003-评级3</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000070033</v>
+        <v>3000070034</v>
       </c>
       <c r="B171" s="0" t="n">
         <v>7003</v>
@@ -8115,27 +8093,27 @@
       </c>
       <c r="O171" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P171" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q171" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W171" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y171" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级3</t>
+          <t>议会随机议员-生物7003-评级4</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>3000070034</v>
+        <v>3000070035</v>
       </c>
       <c r="B172" s="0" t="n">
         <v>7003</v>
@@ -8151,30 +8129,30 @@
       </c>
       <c r="O172" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P172" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q172" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W172" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y172" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级4</t>
+          <t>议会随机议员-生物7003-评级5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>3000070035</v>
+        <v>3000070041</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="C173" s="0" t="n">
         <v>3</v>
@@ -8187,27 +8165,27 @@
       </c>
       <c r="O173" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P173" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q173" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W173" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y173" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级5</t>
+          <t>议会随机议员-生物7004-评级1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>3000070041</v>
+        <v>3000070042</v>
       </c>
       <c r="B174" s="0" t="n">
         <v>7004</v>
@@ -8223,27 +8201,27 @@
       </c>
       <c r="O174" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P174" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q174" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W174" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y174" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级1</t>
+          <t>议会随机议员-生物7004-评级2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>3000070042</v>
+        <v>3000070043</v>
       </c>
       <c r="B175" s="0" t="n">
         <v>7004</v>
@@ -8259,27 +8237,27 @@
       </c>
       <c r="O175" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P175" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q175" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W175" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y175" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级2</t>
+          <t>议会随机议员-生物7004-评级3</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>3000070043</v>
+        <v>3000070044</v>
       </c>
       <c r="B176" s="0" t="n">
         <v>7004</v>
@@ -8295,27 +8273,27 @@
       </c>
       <c r="O176" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P176" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q176" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W176" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y176" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级3</t>
+          <t>议会随机议员-生物7004-评级4</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>3000070044</v>
+        <v>3000070045</v>
       </c>
       <c r="B177" s="0" t="n">
         <v>7004</v>
@@ -8331,55 +8309,19 @@
       </c>
       <c r="O177" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P177" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q177" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W177" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y177" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7004-评级4</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="0" t="n">
-        <v>3000070045</v>
-      </c>
-      <c r="B178" s="0" t="n">
-        <v>7004</v>
-      </c>
-      <c r="C178" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D178" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M178" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O178" s="0" t="inlineStr">
-        <is>
-          <t>70000002,SR,SSR</t>
-        </is>
-      </c>
-      <c r="P178" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q178" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W178" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y178" s="0" t="inlineStr">
         <is>
           <t>议会随机议员-生物7004-评级5</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -2553,11 +2553,7 @@
       <c r="S23" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="T23" s="0" t="inlineStr">
-        <is>
-          <t>100001</t>
-        </is>
-      </c>
+      <c r="T23" s="0" t="n"/>
       <c r="Y23" s="0" t="inlineStr">
         <is>
           <t>BOSS-大盾战士</t>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y177"/>
+  <dimension ref="A1:Y178"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.375" customWidth="1" style="3" min="1" max="2"/>
@@ -2393,24 +2393,29 @@
       <c r="S20" s="1" t="n">
         <v>1.2</v>
       </c>
+      <c r="T20" s="0" t="n">
+        <v>100006</v>
+      </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>人类-大魔法师（冰）</t>
+          <t>人类-大魔法师（冰）-BOSS</t>
         </is>
       </c>
     </row>
     <row r="21" customFormat="1" s="2">
       <c r="A21" s="0" t="n">
-        <v>1040010001</v>
+        <v>1031040001</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>104001</v>
+        <v>103104</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="0" t="n">
-        <v>100</v>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -2422,99 +2427,105 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="0" t="n">
-        <v>15</v>
-      </c>
       <c r="M21" s="0" t="n">
         <v>1000001</v>
       </c>
       <c r="N21" s="0" t="inlineStr">
         <is>
-          <t>10100008&amp;10200008&amp;10300008&amp;11020014&amp;</t>
+          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
         </is>
       </c>
       <c r="P21" s="0" t="n">
-        <v>1040010001</v>
-      </c>
-      <c r="S21" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
+        <v>1031010004</v>
+      </c>
+      <c r="S21" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T21" s="0" t="n">
+        <v>100007</v>
       </c>
       <c r="Y21" s="0" t="inlineStr">
         <is>
-          <t>盗贼</t>
+          <t>人类-大魔法师（雷）-BOSS</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="3">
       <c r="A22" s="0" t="n">
-        <v>1041010001</v>
+        <v>1040010001</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>104101</v>
+        <v>104001</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" s="0" t="n">
-        <v>1000</v>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H22" s="0" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I22" s="0" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="K22" s="0" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M22" s="0" t="n">
         <v>1000001</v>
       </c>
       <c r="N22" s="0" t="inlineStr">
         <is>
-          <t>10200009&amp;10300009&amp;11000012&amp;</t>
+          <t>10100008&amp;10200008&amp;10300008&amp;11020014&amp;</t>
         </is>
       </c>
       <c r="P22" s="0" t="n">
-        <v>1041010001</v>
-      </c>
-      <c r="S22" s="0" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T22" s="0" t="n">
-        <v>100004</v>
+        <v>1040010001</v>
+      </c>
+      <c r="S22" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
       </c>
       <c r="Y22" s="0" t="inlineStr">
         <is>
-          <t>BOSS-大剑战士</t>
+          <t>盗贼</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="0" t="n">
-        <v>1041020001</v>
+        <v>1041010001</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>104102</v>
+        <v>104101</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>1</v>
@@ -2539,128 +2550,90 @@
       <c r="J23" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="K23" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="M23" s="0" t="n">
         <v>1000001</v>
       </c>
       <c r="N23" s="0" t="inlineStr">
         <is>
-          <t>10200009&amp;10300009&amp;11000015&amp;</t>
+          <t>10200009&amp;10300009&amp;11000012&amp;</t>
         </is>
       </c>
       <c r="P23" s="0" t="n">
-        <v>1041020001</v>
+        <v>1041010001</v>
       </c>
       <c r="S23" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="T23" s="0" t="n"/>
+      <c r="T23" s="0" t="n">
+        <v>100004</v>
+      </c>
       <c r="Y23" s="0" t="inlineStr">
         <is>
+          <t>BOSS-大剑战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="3">
+      <c r="A24" s="0" t="n">
+        <v>1041020001</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>104102</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N24" s="0" t="inlineStr">
+        <is>
+          <t>10200009&amp;10300009&amp;11000015&amp;</t>
+        </is>
+      </c>
+      <c r="P24" s="0" t="n">
+        <v>1041020001</v>
+      </c>
+      <c r="S24" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T24" s="0" t="inlineStr"/>
+      <c r="Y24" s="0" t="inlineStr">
+        <is>
           <t>BOSS-大盾战士</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="3">
-      <c r="A24" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>10200016&amp;10300016&amp;</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>cn</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t>白剑伟</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
       <c r="A25" s="2" t="n">
-        <v>2000000002</v>
+        <v>2000000001</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2706,7 +2679,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5050011&amp;5070005&amp;</t>
+          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2716,17 +2689,23 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
-        </is>
-      </c>
+          <t>10200016&amp;10300016&amp;</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="n">
-        <v>2000000002</v>
+        <v>2000000001</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>5</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
+        </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
@@ -2738,105 +2717,105 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>宛家伟</t>
+          <t>白剑伟</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="3">
       <c r="A26" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000002</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="0" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="0" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="0" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I26" s="0" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J26" s="0" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="0" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L26" s="0" t="inlineStr">
-        <is>
-          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
-        </is>
-      </c>
-      <c r="M26" s="0" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>5050011&amp;5070005&amp;</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>40200006&amp;40300003&amp;41000004&amp;</t>
+          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000002</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W26" s="0" t="n">
+      <c r="W26" s="2" t="n">
         <v>4</v>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>雷神天尊斩</t>
+          <t>宛家伟</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="2" t="n">
-        <v>2000000004</v>
+        <v>2000000003</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2882,7 +2861,7 @@
       </c>
       <c r="L27" s="0" t="inlineStr">
         <is>
-          <t>1030006&amp;1040002&amp;1050012&amp;1060002&amp;</t>
+          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
         </is>
       </c>
       <c r="M27" s="0" t="inlineStr">
@@ -2892,21 +2871,17 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10300011&amp;10200011&amp;</t>
-        </is>
-      </c>
-      <c r="O27" s="0" t="inlineStr"/>
+          <t>40200006&amp;40300003&amp;41000004&amp;</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="n">
-        <v>2000000004</v>
+        <v>2000000003</v>
       </c>
       <c r="Q27" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R27" s="2" t="n"/>
-      <c r="U27" s="0" t="inlineStr">
-        <is>
-          <t>3,255,255,255,255&amp;6,178,38,38,255&amp;</t>
-        </is>
+      <c r="R27" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
@@ -2918,49 +2893,105 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
+          <t>雷神天尊斩</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="3">
+      <c r="A28" s="2" t="n">
+        <v>2000000004</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="0" t="inlineStr">
+        <is>
+          <t>1030006&amp;1040002&amp;1050012&amp;1060002&amp;</t>
+        </is>
+      </c>
+      <c r="M28" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>10300011&amp;10200011&amp;</t>
+        </is>
+      </c>
+      <c r="O28" s="0" t="inlineStr"/>
+      <c r="P28" s="2" t="n">
+        <v>2000000004</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R28" s="2" t="n"/>
+      <c r="U28" s="0" t="inlineStr">
+        <is>
+          <t>3,255,255,255,255&amp;6,178,38,38,255&amp;</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="W28" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
           <t>卡米莉娅</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="3">
-      <c r="A28" s="0" t="n">
-        <v>3000010011</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C28" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O28" s="0" t="inlineStr">
-        <is>
-          <t>10000002,N</t>
-        </is>
-      </c>
-      <c r="P28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000010012</v>
+        <v>3000010011</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>1001</v>
@@ -2976,27 +3007,27 @@
       </c>
       <c r="O29" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W29" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y29" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级2</t>
+          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000010013</v>
+        <v>3000010012</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>1001</v>
@@ -3012,27 +3043,27 @@
       </c>
       <c r="O30" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W30" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y30" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级3</t>
+          <t>议会随机议员-生物1001-评级2</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="3">
       <c r="A31" s="0" t="n">
-        <v>3000010014</v>
+        <v>3000010013</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>1001</v>
@@ -3048,27 +3079,27 @@
       </c>
       <c r="O31" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W31" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级4</t>
+          <t>议会随机议员-生物1001-评级3</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="3">
       <c r="A32" s="0" t="n">
-        <v>3000010015</v>
+        <v>3000010014</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>1001</v>
@@ -3084,31 +3115,30 @@
       </c>
       <c r="O32" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="S32" s="0" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="W32" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级5</t>
+          <t>议会随机议员-生物1001-评级4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>3000010021</v>
+        <v>3000010015</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>3</v>
@@ -3121,27 +3151,28 @@
       </c>
       <c r="O33" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="0" t="n">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="S33" s="0" t="inlineStr"/>
       <c r="W33" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级1</t>
+          <t>议会随机议员-生物1001-评级5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>3000010022</v>
+        <v>3000010021</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>1002</v>
@@ -3157,27 +3188,27 @@
       </c>
       <c r="O34" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W34" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级2</t>
+          <t>议会随机议员-生物1002-评级1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>3000010023</v>
+        <v>3000010022</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>1002</v>
@@ -3193,27 +3224,27 @@
       </c>
       <c r="O35" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P35" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W35" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级3</t>
+          <t>议会随机议员-生物1002-评级2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>3000010024</v>
+        <v>3000010023</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1002</v>
@@ -3229,27 +3260,27 @@
       </c>
       <c r="O36" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P36" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W36" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级4</t>
+          <t>议会随机议员-生物1002-评级3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>3000010025</v>
+        <v>3000010024</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>1002</v>
@@ -3265,30 +3296,30 @@
       </c>
       <c r="O37" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W37" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级5</t>
+          <t>议会随机议员-生物1002-评级4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>3000010031</v>
+        <v>3000010025</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>3</v>
@@ -3301,27 +3332,27 @@
       </c>
       <c r="O38" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W38" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级1</t>
+          <t>议会随机议员-生物1002-评级5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>3000010032</v>
+        <v>3000010031</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>1003</v>
@@ -3337,27 +3368,27 @@
       </c>
       <c r="O39" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W39" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级2</t>
+          <t>议会随机议员-生物1003-评级1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>3000010033</v>
+        <v>3000010032</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>1003</v>
@@ -3373,27 +3404,27 @@
       </c>
       <c r="O40" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P40" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W40" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级3</t>
+          <t>议会随机议员-生物1003-评级2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>3000010034</v>
+        <v>3000010033</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>1003</v>
@@ -3409,27 +3440,27 @@
       </c>
       <c r="O41" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W41" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级4</t>
+          <t>议会随机议员-生物1003-评级3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>3000010035</v>
+        <v>3000010034</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>1003</v>
@@ -3445,30 +3476,30 @@
       </c>
       <c r="O42" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W42" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级5</t>
+          <t>议会随机议员-生物1003-评级4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>3000010041</v>
+        <v>3000010035</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>3</v>
@@ -3481,27 +3512,27 @@
       </c>
       <c r="O43" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P43" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W43" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级1</t>
+          <t>议会随机议员-生物1003-评级5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>3000010042</v>
+        <v>3000010041</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>1004</v>
@@ -3517,27 +3548,27 @@
       </c>
       <c r="O44" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P44" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W44" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级2</t>
+          <t>议会随机议员-生物1004-评级1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>3000010043</v>
+        <v>3000010042</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>1004</v>
@@ -3553,27 +3584,27 @@
       </c>
       <c r="O45" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P45" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W45" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级3</t>
+          <t>议会随机议员-生物1004-评级2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>3000010044</v>
+        <v>3000010043</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>1004</v>
@@ -3589,27 +3620,27 @@
       </c>
       <c r="O46" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P46" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W46" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y46" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级4</t>
+          <t>议会随机议员-生物1004-评级3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>3000010045</v>
+        <v>3000010044</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>1004</v>
@@ -3625,30 +3656,30 @@
       </c>
       <c r="O47" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P47" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W47" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y47" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级5</t>
+          <t>议会随机议员-生物1004-评级4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>3000020011</v>
+        <v>3000010045</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>3</v>
@@ -3661,27 +3692,27 @@
       </c>
       <c r="O48" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P48" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W48" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y48" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级1</t>
+          <t>议会随机议员-生物1004-评级5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>3000020012</v>
+        <v>3000020011</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>2001</v>
@@ -3697,27 +3728,27 @@
       </c>
       <c r="O49" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P49" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W49" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y49" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级2</t>
+          <t>议会随机议员-生物2001-评级1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>3000020013</v>
+        <v>3000020012</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>2001</v>
@@ -3733,27 +3764,27 @@
       </c>
       <c r="O50" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P50" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W50" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y50" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级3</t>
+          <t>议会随机议员-生物2001-评级2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>3000020014</v>
+        <v>3000020013</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>2001</v>
@@ -3769,27 +3800,27 @@
       </c>
       <c r="O51" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P51" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W51" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y51" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级4</t>
+          <t>议会随机议员-生物2001-评级3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>3000020015</v>
+        <v>3000020014</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>2001</v>
@@ -3805,30 +3836,30 @@
       </c>
       <c r="O52" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P52" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W52" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y52" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级5</t>
+          <t>议会随机议员-生物2001-评级4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>3000020021</v>
+        <v>3000020015</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>3</v>
@@ -3841,27 +3872,27 @@
       </c>
       <c r="O53" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y53" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级1</t>
+          <t>议会随机议员-生物2001-评级5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>3000020022</v>
+        <v>3000020021</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>2002</v>
@@ -3877,27 +3908,27 @@
       </c>
       <c r="O54" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P54" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W54" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级2</t>
+          <t>议会随机议员-生物2002-评级1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>3000020023</v>
+        <v>3000020022</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>2002</v>
@@ -3913,27 +3944,27 @@
       </c>
       <c r="O55" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P55" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级3</t>
+          <t>议会随机议员-生物2002-评级2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>3000020024</v>
+        <v>3000020023</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>2002</v>
@@ -3949,27 +3980,27 @@
       </c>
       <c r="O56" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P56" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W56" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级4</t>
+          <t>议会随机议员-生物2002-评级3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>3000020025</v>
+        <v>3000020024</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>2002</v>
@@ -3985,30 +4016,30 @@
       </c>
       <c r="O57" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P57" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级5</t>
+          <t>议会随机议员-生物2002-评级4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>3000020031</v>
+        <v>3000020025</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>3</v>
@@ -4021,27 +4052,27 @@
       </c>
       <c r="O58" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P58" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W58" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级1</t>
+          <t>议会随机议员-生物2002-评级5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>3000020032</v>
+        <v>3000020031</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>2003</v>
@@ -4057,27 +4088,27 @@
       </c>
       <c r="O59" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P59" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W59" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级2</t>
+          <t>议会随机议员-生物2003-评级1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>3000020033</v>
+        <v>3000020032</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>2003</v>
@@ -4093,27 +4124,27 @@
       </c>
       <c r="O60" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P60" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W60" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级3</t>
+          <t>议会随机议员-生物2003-评级2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3000020034</v>
+        <v>3000020033</v>
       </c>
       <c r="B61" s="0" t="n">
         <v>2003</v>
@@ -4129,27 +4160,27 @@
       </c>
       <c r="O61" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P61" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W61" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级4</t>
+          <t>议会随机议员-生物2003-评级3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3000020035</v>
+        <v>3000020034</v>
       </c>
       <c r="B62" s="0" t="n">
         <v>2003</v>
@@ -4165,30 +4196,30 @@
       </c>
       <c r="O62" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P62" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W62" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级5</t>
+          <t>议会随机议员-生物2003-评级4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>3000020041</v>
+        <v>3000020035</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>3</v>
@@ -4201,27 +4232,27 @@
       </c>
       <c r="O63" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P63" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y63" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级1</t>
+          <t>议会随机议员-生物2003-评级5</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="3">
       <c r="A64" s="0" t="n">
-        <v>3000020042</v>
+        <v>3000020041</v>
       </c>
       <c r="B64" s="0" t="n">
         <v>2004</v>
@@ -4237,27 +4268,27 @@
       </c>
       <c r="O64" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P64" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W64" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级2</t>
+          <t>议会随机议员-生物2004-评级1</t>
         </is>
       </c>
     </row>
     <row r="65" ht="12" customHeight="1" s="3">
       <c r="A65" s="0" t="n">
-        <v>3000020043</v>
+        <v>3000020042</v>
       </c>
       <c r="B65" s="0" t="n">
         <v>2004</v>
@@ -4273,27 +4304,27 @@
       </c>
       <c r="O65" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P65" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级3</t>
+          <t>议会随机议员-生物2004-评级2</t>
         </is>
       </c>
     </row>
     <row r="66" ht="12" customHeight="1" s="3">
       <c r="A66" s="0" t="n">
-        <v>3000020044</v>
+        <v>3000020043</v>
       </c>
       <c r="B66" s="0" t="n">
         <v>2004</v>
@@ -4309,27 +4340,27 @@
       </c>
       <c r="O66" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P66" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W66" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级4</t>
+          <t>议会随机议员-生物2004-评级3</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="3">
       <c r="A67" s="0" t="n">
-        <v>3000020045</v>
+        <v>3000020044</v>
       </c>
       <c r="B67" s="0" t="n">
         <v>2004</v>
@@ -4345,30 +4376,30 @@
       </c>
       <c r="O67" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P67" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级5</t>
+          <t>议会随机议员-生物2004-评级4</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="3">
       <c r="A68" s="0" t="n">
-        <v>3000030011</v>
+        <v>3000020045</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>3</v>
@@ -4381,27 +4412,27 @@
       </c>
       <c r="O68" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P68" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级1</t>
+          <t>议会随机议员-生物2004-评级5</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>3000030012</v>
+        <v>3000030011</v>
       </c>
       <c r="B69" s="0" t="n">
         <v>3001</v>
@@ -4417,27 +4448,27 @@
       </c>
       <c r="O69" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P69" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W69" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级2</t>
+          <t>议会随机议员-生物3001-评级1</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>3000030013</v>
+        <v>3000030012</v>
       </c>
       <c r="B70" s="0" t="n">
         <v>3001</v>
@@ -4453,27 +4484,27 @@
       </c>
       <c r="O70" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P70" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级3</t>
+          <t>议会随机议员-生物3001-评级2</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>3000030014</v>
+        <v>3000030013</v>
       </c>
       <c r="B71" s="0" t="n">
         <v>3001</v>
@@ -4489,27 +4520,27 @@
       </c>
       <c r="O71" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P71" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W71" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级4</t>
+          <t>议会随机议员-生物3001-评级3</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="3">
       <c r="A72" s="0" t="n">
-        <v>3000030015</v>
+        <v>3000030014</v>
       </c>
       <c r="B72" s="0" t="n">
         <v>3001</v>
@@ -4525,30 +4556,30 @@
       </c>
       <c r="O72" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P72" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级5</t>
+          <t>议会随机议员-生物3001-评级4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>3000030021</v>
+        <v>3000030015</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>3</v>
@@ -4561,27 +4592,27 @@
       </c>
       <c r="O73" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P73" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级1</t>
+          <t>议会随机议员-生物3001-评级5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>3000030022</v>
+        <v>3000030021</v>
       </c>
       <c r="B74" s="0" t="n">
         <v>3002</v>
@@ -4597,27 +4628,27 @@
       </c>
       <c r="O74" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P74" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W74" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级2</t>
+          <t>议会随机议员-生物3002-评级1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>3000030023</v>
+        <v>3000030022</v>
       </c>
       <c r="B75" s="0" t="n">
         <v>3002</v>
@@ -4633,27 +4664,27 @@
       </c>
       <c r="O75" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P75" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级3</t>
+          <t>议会随机议员-生物3002-评级2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>3000030024</v>
+        <v>3000030023</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>3002</v>
@@ -4669,27 +4700,27 @@
       </c>
       <c r="O76" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P76" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W76" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级4</t>
+          <t>议会随机议员-生物3002-评级3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>3000030025</v>
+        <v>3000030024</v>
       </c>
       <c r="B77" s="0" t="n">
         <v>3002</v>
@@ -4705,30 +4736,30 @@
       </c>
       <c r="O77" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P77" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级5</t>
+          <t>议会随机议员-生物3002-评级4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>3000030031</v>
+        <v>3000030025</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>3</v>
@@ -4741,27 +4772,27 @@
       </c>
       <c r="O78" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P78" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级1</t>
+          <t>议会随机议员-生物3002-评级5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>3000030032</v>
+        <v>3000030031</v>
       </c>
       <c r="B79" s="0" t="n">
         <v>3003</v>
@@ -4777,27 +4808,27 @@
       </c>
       <c r="O79" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P79" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W79" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级2</t>
+          <t>议会随机议员-生物3003-评级1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>3000030033</v>
+        <v>3000030032</v>
       </c>
       <c r="B80" s="0" t="n">
         <v>3003</v>
@@ -4813,27 +4844,27 @@
       </c>
       <c r="O80" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P80" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级3</t>
+          <t>议会随机议员-生物3003-评级2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>3000030034</v>
+        <v>3000030033</v>
       </c>
       <c r="B81" s="0" t="n">
         <v>3003</v>
@@ -4849,27 +4880,27 @@
       </c>
       <c r="O81" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P81" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q81" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W81" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级4</t>
+          <t>议会随机议员-生物3003-评级3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>3000030035</v>
+        <v>3000030034</v>
       </c>
       <c r="B82" s="0" t="n">
         <v>3003</v>
@@ -4885,30 +4916,30 @@
       </c>
       <c r="O82" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P82" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级5</t>
+          <t>议会随机议员-生物3003-评级4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>3000030041</v>
+        <v>3000030035</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>3</v>
@@ -4921,27 +4952,27 @@
       </c>
       <c r="O83" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P83" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级1</t>
+          <t>议会随机议员-生物3003-评级5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>3000030042</v>
+        <v>3000030041</v>
       </c>
       <c r="B84" s="0" t="n">
         <v>3004</v>
@@ -4957,27 +4988,27 @@
       </c>
       <c r="O84" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P84" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q84" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W84" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y84" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级2</t>
+          <t>议会随机议员-生物3004-评级1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>3000030043</v>
+        <v>3000030042</v>
       </c>
       <c r="B85" s="0" t="n">
         <v>3004</v>
@@ -4993,27 +5024,27 @@
       </c>
       <c r="O85" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P85" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q85" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y85" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级3</t>
+          <t>议会随机议员-生物3004-评级2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>3000030044</v>
+        <v>3000030043</v>
       </c>
       <c r="B86" s="0" t="n">
         <v>3004</v>
@@ -5029,27 +5060,27 @@
       </c>
       <c r="O86" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P86" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W86" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y86" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级4</t>
+          <t>议会随机议员-生物3004-评级3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>3000030045</v>
+        <v>3000030044</v>
       </c>
       <c r="B87" s="0" t="n">
         <v>3004</v>
@@ -5065,30 +5096,30 @@
       </c>
       <c r="O87" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P87" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y87" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级5</t>
+          <t>议会随机议员-生物3004-评级4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>3000040011</v>
+        <v>3000030045</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>3</v>
@@ -5101,27 +5132,27 @@
       </c>
       <c r="O88" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P88" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q88" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y88" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级1</t>
+          <t>议会随机议员-生物3004-评级5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>3000040012</v>
+        <v>3000040011</v>
       </c>
       <c r="B89" s="0" t="n">
         <v>4001</v>
@@ -5137,27 +5168,27 @@
       </c>
       <c r="O89" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P89" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q89" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W89" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y89" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级2</t>
+          <t>议会随机议员-生物4001-评级1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>3000040013</v>
+        <v>3000040012</v>
       </c>
       <c r="B90" s="0" t="n">
         <v>4001</v>
@@ -5173,27 +5204,27 @@
       </c>
       <c r="O90" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P90" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y90" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级3</t>
+          <t>议会随机议员-生物4001-评级2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>3000040014</v>
+        <v>3000040013</v>
       </c>
       <c r="B91" s="0" t="n">
         <v>4001</v>
@@ -5209,27 +5240,27 @@
       </c>
       <c r="O91" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P91" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q91" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W91" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y91" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级4</t>
+          <t>议会随机议员-生物4001-评级3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>3000040015</v>
+        <v>3000040014</v>
       </c>
       <c r="B92" s="0" t="n">
         <v>4001</v>
@@ -5245,30 +5276,30 @@
       </c>
       <c r="O92" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P92" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q92" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y92" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级5</t>
+          <t>议会随机议员-生物4001-评级4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>3000040021</v>
+        <v>3000040015</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>3</v>
@@ -5281,27 +5312,27 @@
       </c>
       <c r="O93" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P93" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q93" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y93" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级1</t>
+          <t>议会随机议员-生物4001-评级5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>3000040022</v>
+        <v>3000040021</v>
       </c>
       <c r="B94" s="0" t="n">
         <v>4002</v>
@@ -5317,27 +5348,27 @@
       </c>
       <c r="O94" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P94" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W94" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y94" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级2</t>
+          <t>议会随机议员-生物4002-评级1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>3000040023</v>
+        <v>3000040022</v>
       </c>
       <c r="B95" s="0" t="n">
         <v>4002</v>
@@ -5353,27 +5384,27 @@
       </c>
       <c r="O95" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P95" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q95" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W95" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y95" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级3</t>
+          <t>议会随机议员-生物4002-评级2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>3000040024</v>
+        <v>3000040023</v>
       </c>
       <c r="B96" s="0" t="n">
         <v>4002</v>
@@ -5389,27 +5420,27 @@
       </c>
       <c r="O96" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P96" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q96" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W96" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y96" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级4</t>
+          <t>议会随机议员-生物4002-评级3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>3000040025</v>
+        <v>3000040024</v>
       </c>
       <c r="B97" s="0" t="n">
         <v>4002</v>
@@ -5425,30 +5456,30 @@
       </c>
       <c r="O97" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P97" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q97" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W97" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y97" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级5</t>
+          <t>议会随机议员-生物4002-评级4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>3000040031</v>
+        <v>3000040025</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>3</v>
@@ -5461,27 +5492,27 @@
       </c>
       <c r="O98" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P98" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q98" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W98" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y98" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级1</t>
+          <t>议会随机议员-生物4002-评级5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>3000040032</v>
+        <v>3000040031</v>
       </c>
       <c r="B99" s="0" t="n">
         <v>4003</v>
@@ -5497,27 +5528,27 @@
       </c>
       <c r="O99" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P99" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q99" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W99" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y99" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级2</t>
+          <t>议会随机议员-生物4003-评级1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>3000040033</v>
+        <v>3000040032</v>
       </c>
       <c r="B100" s="0" t="n">
         <v>4003</v>
@@ -5533,27 +5564,27 @@
       </c>
       <c r="O100" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P100" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q100" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W100" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y100" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级3</t>
+          <t>议会随机议员-生物4003-评级2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>3000040034</v>
+        <v>3000040033</v>
       </c>
       <c r="B101" s="0" t="n">
         <v>4003</v>
@@ -5569,27 +5600,27 @@
       </c>
       <c r="O101" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P101" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q101" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W101" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y101" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级4</t>
+          <t>议会随机议员-生物4003-评级3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>3000040035</v>
+        <v>3000040034</v>
       </c>
       <c r="B102" s="0" t="n">
         <v>4003</v>
@@ -5605,30 +5636,30 @@
       </c>
       <c r="O102" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P102" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q102" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y102" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级5</t>
+          <t>议会随机议员-生物4003-评级4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>3000040041</v>
+        <v>3000040035</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>3</v>
@@ -5641,27 +5672,27 @@
       </c>
       <c r="O103" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P103" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q103" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y103" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级1</t>
+          <t>议会随机议员-生物4003-评级5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>3000040042</v>
+        <v>3000040041</v>
       </c>
       <c r="B104" s="0" t="n">
         <v>4004</v>
@@ -5677,27 +5708,27 @@
       </c>
       <c r="O104" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P104" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q104" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W104" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y104" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级2</t>
+          <t>议会随机议员-生物4004-评级1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>3000040043</v>
+        <v>3000040042</v>
       </c>
       <c r="B105" s="0" t="n">
         <v>4004</v>
@@ -5713,27 +5744,27 @@
       </c>
       <c r="O105" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P105" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q105" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y105" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级3</t>
+          <t>议会随机议员-生物4004-评级2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>3000040044</v>
+        <v>3000040043</v>
       </c>
       <c r="B106" s="0" t="n">
         <v>4004</v>
@@ -5749,27 +5780,27 @@
       </c>
       <c r="O106" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P106" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q106" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W106" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y106" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级4</t>
+          <t>议会随机议员-生物4004-评级3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>3000040045</v>
+        <v>3000040044</v>
       </c>
       <c r="B107" s="0" t="n">
         <v>4004</v>
@@ -5785,30 +5816,30 @@
       </c>
       <c r="O107" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P107" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q107" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y107" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级5</t>
+          <t>议会随机议员-生物4004-评级4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>3000040051</v>
+        <v>3000040045</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>3</v>
@@ -5821,27 +5852,27 @@
       </c>
       <c r="O108" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P108" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y108" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级1</t>
+          <t>议会随机议员-生物4004-评级5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>3000040052</v>
+        <v>3000040051</v>
       </c>
       <c r="B109" s="0" t="n">
         <v>4005</v>
@@ -5857,27 +5888,27 @@
       </c>
       <c r="O109" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P109" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q109" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W109" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y109" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级2</t>
+          <t>议会随机议员-生物4005-评级1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>3000040053</v>
+        <v>3000040052</v>
       </c>
       <c r="B110" s="0" t="n">
         <v>4005</v>
@@ -5893,27 +5924,27 @@
       </c>
       <c r="O110" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P110" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q110" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W110" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y110" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级3</t>
+          <t>议会随机议员-生物4005-评级2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>3000040054</v>
+        <v>3000040053</v>
       </c>
       <c r="B111" s="0" t="n">
         <v>4005</v>
@@ -5929,27 +5960,27 @@
       </c>
       <c r="O111" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P111" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q111" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W111" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y111" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级4</t>
+          <t>议会随机议员-生物4005-评级3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>3000040055</v>
+        <v>3000040054</v>
       </c>
       <c r="B112" s="0" t="n">
         <v>4005</v>
@@ -5965,30 +5996,30 @@
       </c>
       <c r="O112" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P112" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W112" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y112" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级5</t>
+          <t>议会随机议员-生物4005-评级4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>3000050011</v>
+        <v>3000040055</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>3</v>
@@ -6001,27 +6032,27 @@
       </c>
       <c r="O113" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P113" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q113" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y113" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级1</t>
+          <t>议会随机议员-生物4005-评级5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>3000050012</v>
+        <v>3000050011</v>
       </c>
       <c r="B114" s="0" t="n">
         <v>5001</v>
@@ -6037,27 +6068,27 @@
       </c>
       <c r="O114" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P114" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q114" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W114" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y114" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级2</t>
+          <t>议会随机议员-生物5001-评级1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>3000050013</v>
+        <v>3000050012</v>
       </c>
       <c r="B115" s="0" t="n">
         <v>5001</v>
@@ -6073,27 +6104,27 @@
       </c>
       <c r="O115" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P115" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W115" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y115" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级3</t>
+          <t>议会随机议员-生物5001-评级2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>3000050014</v>
+        <v>3000050013</v>
       </c>
       <c r="B116" s="0" t="n">
         <v>5001</v>
@@ -6109,27 +6140,27 @@
       </c>
       <c r="O116" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P116" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q116" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W116" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y116" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级4</t>
+          <t>议会随机议员-生物5001-评级3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>3000050015</v>
+        <v>3000050014</v>
       </c>
       <c r="B117" s="0" t="n">
         <v>5001</v>
@@ -6145,30 +6176,30 @@
       </c>
       <c r="O117" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P117" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q117" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W117" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y117" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级5</t>
+          <t>议会随机议员-生物5001-评级4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>3000050021</v>
+        <v>3000050015</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>3</v>
@@ -6181,27 +6212,27 @@
       </c>
       <c r="O118" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P118" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q118" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y118" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级1</t>
+          <t>议会随机议员-生物5001-评级5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>3000050022</v>
+        <v>3000050021</v>
       </c>
       <c r="B119" s="0" t="n">
         <v>5002</v>
@@ -6217,27 +6248,27 @@
       </c>
       <c r="O119" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P119" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q119" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W119" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y119" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级2</t>
+          <t>议会随机议员-生物5002-评级1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>3000050023</v>
+        <v>3000050022</v>
       </c>
       <c r="B120" s="0" t="n">
         <v>5002</v>
@@ -6253,27 +6284,27 @@
       </c>
       <c r="O120" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P120" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q120" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W120" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y120" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级3</t>
+          <t>议会随机议员-生物5002-评级2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>3000050024</v>
+        <v>3000050023</v>
       </c>
       <c r="B121" s="0" t="n">
         <v>5002</v>
@@ -6289,27 +6320,27 @@
       </c>
       <c r="O121" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P121" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W121" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y121" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级4</t>
+          <t>议会随机议员-生物5002-评级3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>3000050025</v>
+        <v>3000050024</v>
       </c>
       <c r="B122" s="0" t="n">
         <v>5002</v>
@@ -6325,30 +6356,30 @@
       </c>
       <c r="O122" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P122" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q122" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W122" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y122" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级5</t>
+          <t>议会随机议员-生物5002-评级4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>3000050031</v>
+        <v>3000050025</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>3</v>
@@ -6361,27 +6392,27 @@
       </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P123" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q123" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y123" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级1</t>
+          <t>议会随机议员-生物5002-评级5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>3000050032</v>
+        <v>3000050031</v>
       </c>
       <c r="B124" s="0" t="n">
         <v>5003</v>
@@ -6397,27 +6428,27 @@
       </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P124" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q124" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W124" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级2</t>
+          <t>议会随机议员-生物5003-评级1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>3000050033</v>
+        <v>3000050032</v>
       </c>
       <c r="B125" s="0" t="n">
         <v>5003</v>
@@ -6433,27 +6464,27 @@
       </c>
       <c r="O125" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P125" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q125" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级3</t>
+          <t>议会随机议员-生物5003-评级2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>3000050034</v>
+        <v>3000050033</v>
       </c>
       <c r="B126" s="0" t="n">
         <v>5003</v>
@@ -6469,27 +6500,27 @@
       </c>
       <c r="O126" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P126" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q126" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W126" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级4</t>
+          <t>议会随机议员-生物5003-评级3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>3000050035</v>
+        <v>3000050034</v>
       </c>
       <c r="B127" s="0" t="n">
         <v>5003</v>
@@ -6505,30 +6536,30 @@
       </c>
       <c r="O127" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P127" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q127" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W127" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级5</t>
+          <t>议会随机议员-生物5003-评级4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>3000050041</v>
+        <v>3000050035</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>3</v>
@@ -6541,27 +6572,27 @@
       </c>
       <c r="O128" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P128" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q128" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级1</t>
+          <t>议会随机议员-生物5003-评级5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000050042</v>
+        <v>3000050041</v>
       </c>
       <c r="B129" s="0" t="n">
         <v>5004</v>
@@ -6577,27 +6608,27 @@
       </c>
       <c r="O129" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P129" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q129" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W129" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级2</t>
+          <t>议会随机议员-生物5004-评级1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000050043</v>
+        <v>3000050042</v>
       </c>
       <c r="B130" s="0" t="n">
         <v>5004</v>
@@ -6613,27 +6644,27 @@
       </c>
       <c r="O130" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P130" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q130" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W130" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级3</t>
+          <t>议会随机议员-生物5004-评级2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000050044</v>
+        <v>3000050043</v>
       </c>
       <c r="B131" s="0" t="n">
         <v>5004</v>
@@ -6649,27 +6680,27 @@
       </c>
       <c r="O131" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P131" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q131" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W131" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y131" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级4</t>
+          <t>议会随机议员-生物5004-评级3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000050045</v>
+        <v>3000050044</v>
       </c>
       <c r="B132" s="0" t="n">
         <v>5004</v>
@@ -6685,30 +6716,30 @@
       </c>
       <c r="O132" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P132" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q132" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W132" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y132" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级5</t>
+          <t>议会随机议员-生物5004-评级4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000060011</v>
+        <v>3000050045</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>3</v>
@@ -6721,27 +6752,27 @@
       </c>
       <c r="O133" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P133" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q133" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W133" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级1</t>
+          <t>议会随机议员-生物5004-评级5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000060012</v>
+        <v>3000060011</v>
       </c>
       <c r="B134" s="0" t="n">
         <v>6001</v>
@@ -6757,27 +6788,27 @@
       </c>
       <c r="O134" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P134" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q134" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W134" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y134" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级2</t>
+          <t>议会随机议员-生物6001-评级1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000060013</v>
+        <v>3000060012</v>
       </c>
       <c r="B135" s="0" t="n">
         <v>6001</v>
@@ -6793,27 +6824,27 @@
       </c>
       <c r="O135" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P135" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q135" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W135" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y135" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级3</t>
+          <t>议会随机议员-生物6001-评级2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000060014</v>
+        <v>3000060013</v>
       </c>
       <c r="B136" s="0" t="n">
         <v>6001</v>
@@ -6829,27 +6860,27 @@
       </c>
       <c r="O136" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P136" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q136" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W136" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y136" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级4</t>
+          <t>议会随机议员-生物6001-评级3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000060015</v>
+        <v>3000060014</v>
       </c>
       <c r="B137" s="0" t="n">
         <v>6001</v>
@@ -6865,30 +6896,30 @@
       </c>
       <c r="O137" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P137" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q137" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W137" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y137" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级5</t>
+          <t>议会随机议员-生物6001-评级4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000060021</v>
+        <v>3000060015</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C138" s="0" t="n">
         <v>3</v>
@@ -6901,27 +6932,27 @@
       </c>
       <c r="O138" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P138" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q138" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W138" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y138" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级1</t>
+          <t>议会随机议员-生物6001-评级5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>3000060022</v>
+        <v>3000060021</v>
       </c>
       <c r="B139" s="0" t="n">
         <v>6002</v>
@@ -6937,27 +6968,27 @@
       </c>
       <c r="O139" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P139" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q139" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W139" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y139" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级2</t>
+          <t>议会随机议员-生物6002-评级1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>3000060023</v>
+        <v>3000060022</v>
       </c>
       <c r="B140" s="0" t="n">
         <v>6002</v>
@@ -6973,27 +7004,27 @@
       </c>
       <c r="O140" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P140" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q140" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W140" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y140" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级3</t>
+          <t>议会随机议员-生物6002-评级2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>3000060024</v>
+        <v>3000060023</v>
       </c>
       <c r="B141" s="0" t="n">
         <v>6002</v>
@@ -7009,27 +7040,27 @@
       </c>
       <c r="O141" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P141" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q141" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W141" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y141" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级4</t>
+          <t>议会随机议员-生物6002-评级3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>3000060025</v>
+        <v>3000060024</v>
       </c>
       <c r="B142" s="0" t="n">
         <v>6002</v>
@@ -7045,30 +7076,30 @@
       </c>
       <c r="O142" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P142" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q142" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W142" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y142" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级5</t>
+          <t>议会随机议员-生物6002-评级4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>3000060031</v>
+        <v>3000060025</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>3</v>
@@ -7081,27 +7112,27 @@
       </c>
       <c r="O143" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P143" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q143" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W143" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y143" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级1</t>
+          <t>议会随机议员-生物6002-评级5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>3000060032</v>
+        <v>3000060031</v>
       </c>
       <c r="B144" s="0" t="n">
         <v>6003</v>
@@ -7117,27 +7148,27 @@
       </c>
       <c r="O144" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P144" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q144" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W144" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y144" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级2</t>
+          <t>议会随机议员-生物6003-评级1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>3000060033</v>
+        <v>3000060032</v>
       </c>
       <c r="B145" s="0" t="n">
         <v>6003</v>
@@ -7153,27 +7184,27 @@
       </c>
       <c r="O145" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P145" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q145" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W145" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y145" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级3</t>
+          <t>议会随机议员-生物6003-评级2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>3000060034</v>
+        <v>3000060033</v>
       </c>
       <c r="B146" s="0" t="n">
         <v>6003</v>
@@ -7189,27 +7220,27 @@
       </c>
       <c r="O146" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P146" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q146" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W146" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y146" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级4</t>
+          <t>议会随机议员-生物6003-评级3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>3000060035</v>
+        <v>3000060034</v>
       </c>
       <c r="B147" s="0" t="n">
         <v>6003</v>
@@ -7225,30 +7256,30 @@
       </c>
       <c r="O147" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P147" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q147" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W147" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y147" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级5</t>
+          <t>议会随机议员-生物6003-评级4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>3000060041</v>
+        <v>3000060035</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C148" s="0" t="n">
         <v>3</v>
@@ -7261,27 +7292,27 @@
       </c>
       <c r="O148" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P148" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q148" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W148" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y148" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级1</t>
+          <t>议会随机议员-生物6003-评级5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>3000060042</v>
+        <v>3000060041</v>
       </c>
       <c r="B149" s="0" t="n">
         <v>6004</v>
@@ -7297,27 +7328,27 @@
       </c>
       <c r="O149" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P149" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q149" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W149" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y149" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级2</t>
+          <t>议会随机议员-生物6004-评级1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>3000060043</v>
+        <v>3000060042</v>
       </c>
       <c r="B150" s="0" t="n">
         <v>6004</v>
@@ -7333,27 +7364,27 @@
       </c>
       <c r="O150" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P150" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q150" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W150" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y150" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级3</t>
+          <t>议会随机议员-生物6004-评级2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>3000060044</v>
+        <v>3000060043</v>
       </c>
       <c r="B151" s="0" t="n">
         <v>6004</v>
@@ -7369,27 +7400,27 @@
       </c>
       <c r="O151" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P151" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q151" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W151" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y151" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级4</t>
+          <t>议会随机议员-生物6004-评级3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>3000060045</v>
+        <v>3000060044</v>
       </c>
       <c r="B152" s="0" t="n">
         <v>6004</v>
@@ -7405,30 +7436,30 @@
       </c>
       <c r="O152" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P152" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q152" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W152" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y152" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级5</t>
+          <t>议会随机议员-生物6004-评级4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>3000060051</v>
+        <v>3000060045</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C153" s="0" t="n">
         <v>3</v>
@@ -7441,27 +7472,27 @@
       </c>
       <c r="O153" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P153" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q153" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W153" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y153" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级1</t>
+          <t>议会随机议员-生物6004-评级5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>3000060052</v>
+        <v>3000060051</v>
       </c>
       <c r="B154" s="0" t="n">
         <v>6005</v>
@@ -7477,27 +7508,27 @@
       </c>
       <c r="O154" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P154" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q154" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W154" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y154" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级2</t>
+          <t>议会随机议员-生物6005-评级1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>3000060053</v>
+        <v>3000060052</v>
       </c>
       <c r="B155" s="0" t="n">
         <v>6005</v>
@@ -7513,27 +7544,27 @@
       </c>
       <c r="O155" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P155" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q155" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W155" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y155" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级3</t>
+          <t>议会随机议员-生物6005-评级2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>3000060054</v>
+        <v>3000060053</v>
       </c>
       <c r="B156" s="0" t="n">
         <v>6005</v>
@@ -7549,27 +7580,27 @@
       </c>
       <c r="O156" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P156" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q156" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W156" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y156" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级4</t>
+          <t>议会随机议员-生物6005-评级3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>3000060055</v>
+        <v>3000060054</v>
       </c>
       <c r="B157" s="0" t="n">
         <v>6005</v>
@@ -7585,30 +7616,30 @@
       </c>
       <c r="O157" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P157" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q157" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W157" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y157" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级5</t>
+          <t>议会随机议员-生物6005-评级4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>3000070011</v>
+        <v>3000060055</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C158" s="0" t="n">
         <v>3</v>
@@ -7621,27 +7652,27 @@
       </c>
       <c r="O158" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P158" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q158" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W158" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y158" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级1</t>
+          <t>议会随机议员-生物6005-评级5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>3000070012</v>
+        <v>3000070011</v>
       </c>
       <c r="B159" s="0" t="n">
         <v>7001</v>
@@ -7657,27 +7688,27 @@
       </c>
       <c r="O159" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P159" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q159" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W159" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y159" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级2</t>
+          <t>议会随机议员-生物7001-评级1</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>3000070013</v>
+        <v>3000070012</v>
       </c>
       <c r="B160" s="0" t="n">
         <v>7001</v>
@@ -7693,27 +7724,27 @@
       </c>
       <c r="O160" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P160" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q160" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W160" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y160" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级3</t>
+          <t>议会随机议员-生物7001-评级2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>3000070014</v>
+        <v>3000070013</v>
       </c>
       <c r="B161" s="0" t="n">
         <v>7001</v>
@@ -7729,27 +7760,27 @@
       </c>
       <c r="O161" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P161" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q161" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W161" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y161" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级4</t>
+          <t>议会随机议员-生物7001-评级3</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>3000070015</v>
+        <v>3000070014</v>
       </c>
       <c r="B162" s="0" t="n">
         <v>7001</v>
@@ -7765,30 +7796,30 @@
       </c>
       <c r="O162" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P162" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q162" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W162" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y162" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级5</t>
+          <t>议会随机议员-生物7001-评级4</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>3000070021</v>
+        <v>3000070015</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C163" s="0" t="n">
         <v>3</v>
@@ -7801,27 +7832,27 @@
       </c>
       <c r="O163" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P163" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q163" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W163" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y163" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级1</t>
+          <t>议会随机议员-生物7001-评级5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000070022</v>
+        <v>3000070021</v>
       </c>
       <c r="B164" s="0" t="n">
         <v>7002</v>
@@ -7837,27 +7868,27 @@
       </c>
       <c r="O164" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P164" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q164" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W164" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y164" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级2</t>
+          <t>议会随机议员-生物7002-评级1</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000070023</v>
+        <v>3000070022</v>
       </c>
       <c r="B165" s="0" t="n">
         <v>7002</v>
@@ -7873,27 +7904,27 @@
       </c>
       <c r="O165" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P165" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q165" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W165" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y165" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级3</t>
+          <t>议会随机议员-生物7002-评级2</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000070024</v>
+        <v>3000070023</v>
       </c>
       <c r="B166" s="0" t="n">
         <v>7002</v>
@@ -7909,27 +7940,27 @@
       </c>
       <c r="O166" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P166" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q166" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W166" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y166" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级4</t>
+          <t>议会随机议员-生物7002-评级3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000070025</v>
+        <v>3000070024</v>
       </c>
       <c r="B167" s="0" t="n">
         <v>7002</v>
@@ -7945,30 +7976,30 @@
       </c>
       <c r="O167" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P167" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q167" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W167" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y167" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级5</t>
+          <t>议会随机议员-生物7002-评级4</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000070031</v>
+        <v>3000070025</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C168" s="0" t="n">
         <v>3</v>
@@ -7981,27 +8012,27 @@
       </c>
       <c r="O168" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P168" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q168" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W168" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y168" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级1</t>
+          <t>议会随机议员-生物7002-评级5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000070032</v>
+        <v>3000070031</v>
       </c>
       <c r="B169" s="0" t="n">
         <v>7003</v>
@@ -8017,27 +8048,27 @@
       </c>
       <c r="O169" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P169" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q169" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W169" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y169" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级2</t>
+          <t>议会随机议员-生物7003-评级1</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>3000070033</v>
+        <v>3000070032</v>
       </c>
       <c r="B170" s="0" t="n">
         <v>7003</v>
@@ -8053,27 +8084,27 @@
       </c>
       <c r="O170" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P170" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q170" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W170" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y170" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级3</t>
+          <t>议会随机议员-生物7003-评级2</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000070034</v>
+        <v>3000070033</v>
       </c>
       <c r="B171" s="0" t="n">
         <v>7003</v>
@@ -8089,27 +8120,27 @@
       </c>
       <c r="O171" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P171" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q171" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W171" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y171" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级4</t>
+          <t>议会随机议员-生物7003-评级3</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>3000070035</v>
+        <v>3000070034</v>
       </c>
       <c r="B172" s="0" t="n">
         <v>7003</v>
@@ -8125,30 +8156,30 @@
       </c>
       <c r="O172" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P172" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q172" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W172" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y172" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级5</t>
+          <t>议会随机议员-生物7003-评级4</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>3000070041</v>
+        <v>3000070035</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C173" s="0" t="n">
         <v>3</v>
@@ -8161,27 +8192,27 @@
       </c>
       <c r="O173" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P173" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q173" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W173" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y173" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级1</t>
+          <t>议会随机议员-生物7003-评级5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>3000070042</v>
+        <v>3000070041</v>
       </c>
       <c r="B174" s="0" t="n">
         <v>7004</v>
@@ -8197,27 +8228,27 @@
       </c>
       <c r="O174" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P174" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q174" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W174" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y174" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级2</t>
+          <t>议会随机议员-生物7004-评级1</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>3000070043</v>
+        <v>3000070042</v>
       </c>
       <c r="B175" s="0" t="n">
         <v>7004</v>
@@ -8233,27 +8264,27 @@
       </c>
       <c r="O175" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P175" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q175" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W175" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y175" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级3</t>
+          <t>议会随机议员-生物7004-评级2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>3000070044</v>
+        <v>3000070043</v>
       </c>
       <c r="B176" s="0" t="n">
         <v>7004</v>
@@ -8269,27 +8300,27 @@
       </c>
       <c r="O176" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P176" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q176" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W176" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y176" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级4</t>
+          <t>议会随机议员-生物7004-评级3</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>3000070045</v>
+        <v>3000070044</v>
       </c>
       <c r="B177" s="0" t="n">
         <v>7004</v>
@@ -8305,19 +8336,55 @@
       </c>
       <c r="O177" s="0" t="inlineStr">
         <is>
+          <t>70000002,R,SR</t>
+        </is>
+      </c>
+      <c r="P177" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y177" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级4</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="n">
+        <v>3000070045</v>
+      </c>
+      <c r="B178" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D178" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O178" s="0" t="inlineStr">
+        <is>
           <t>70000002,SR,SSR</t>
         </is>
       </c>
-      <c r="P177" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q177" s="0" t="n">
+      <c r="P178" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="W177" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y177" s="0" t="inlineStr">
+      <c r="W178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y178" s="0" t="inlineStr">
         <is>
           <t>议会随机议员-生物7004-评级5</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z178"/>
+  <dimension ref="A1:Z180"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.375" customWidth="1" style="3" min="1" max="2"/>
@@ -1203,7 +1203,7 @@
           <t>icon_res</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="0" t="inlineStr">
         <is>
           <t>ai_param</t>
         </is>
@@ -1335,7 +1335,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1467,7 +1467,7 @@
           <t>头像图片-UI图集sprite名(支持「名,图集」后缀;空=用spine形象展示;无spine资源的NPC(如仅对话使用)配置此字段)</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" s="0" t="inlineStr">
         <is>
           <t>AI参数(&amp;分隔多项,每项 类型:参数1:参数2,空=无)。skill_update:技能extId:间隔秒=注册Update事件,每隔N秒触发指定attack_mode_ext技能(该技能 trigger_scene 须配1=释放技能意图;触发间隔以本参数为准,ext的trigger_interval对scene1无效)。如 skill_update:100005:10</t>
         </is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13" customFormat="1" s="1">
       <c r="A13" s="4" t="n">
-        <v>1020030001</v>
+        <v>1020020002</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>102003</v>
+        <v>102002</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1</v>
@@ -1898,18 +1898,14 @@
       <c r="E13" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="H13" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>25</v>
@@ -1928,11 +1924,11 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>10200005&amp;10300005&amp;10100007&amp;11010003&amp;</t>
+          <t>10200006&amp;10300006&amp;11010002&amp;</t>
         </is>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1020030001</v>
+        <v>1020020001</v>
       </c>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
@@ -1941,35 +1937,31 @@
       </c>
       <c r="Z13" s="4" t="inlineStr">
         <is>
-          <t>连射手-Boss</t>
+          <t>强弓手</t>
         </is>
       </c>
     </row>
     <row r="14" customFormat="1" s="1">
       <c r="A14" s="4" t="n">
-        <v>1030010001</v>
+        <v>1020030001</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>103001</v>
+        <v>102003</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E14" s="4" t="n">
+        <v>200</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G14" s="4" t="n">
+        <v>200</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1977,7 +1969,7 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1985,7 +1977,7 @@
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n">
@@ -1993,66 +1985,58 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>10200007&amp;10300007&amp;11000003&amp;10100007&amp;</t>
+          <t>10200005&amp;10300005&amp;10100007&amp;11010003&amp;</t>
         </is>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1030010001</v>
+        <v>1020030001</v>
       </c>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
-      <c r="S14" s="1" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
+      <c r="S14" s="1" t="n">
+        <v>1.2</v>
       </c>
       <c r="Z14" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（火）</t>
+          <t>连射手-Boss</t>
         </is>
       </c>
     </row>
     <row r="15" customFormat="1" s="1">
       <c r="A15" s="4" t="n">
-        <v>1030020001</v>
+        <v>1020030002</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>103002</v>
+        <v>102003</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E15" s="4" t="n">
+        <v>200</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K15" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n">
@@ -2060,31 +2044,29 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>10100007&amp;10200007&amp;10300007&amp;11000004&amp;</t>
+          <t>10200005&amp;10300005&amp;10100007&amp;11010003&amp;</t>
         </is>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1030020001</v>
+        <v>1020030001</v>
       </c>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
-      <c r="S15" s="1" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
+      <c r="S15" s="1" t="n">
+        <v>1.2</v>
       </c>
       <c r="Z15" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（水）</t>
+          <t>连射手</t>
         </is>
       </c>
     </row>
     <row r="16" customFormat="1" s="1">
       <c r="A16" s="4" t="n">
-        <v>1030030001</v>
+        <v>1030010001</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>103003</v>
+        <v>103001</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1</v>
@@ -2119,7 +2101,7 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n">
@@ -2127,11 +2109,11 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>10200007&amp;10100007&amp;10300007&amp;11000010&amp;</t>
+          <t>10200007&amp;10300007&amp;11000003&amp;10100007&amp;</t>
         </is>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1030030001</v>
+        <v>1030010001</v>
       </c>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
@@ -2142,16 +2124,16 @@
       </c>
       <c r="Z16" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（冰）</t>
+          <t>人类-魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="17" customFormat="1" s="1">
       <c r="A17" s="4" t="n">
-        <v>1030040001</v>
+        <v>1030020001</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>103004</v>
+        <v>103002</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1</v>
@@ -2186,7 +2168,7 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n">
@@ -2194,11 +2176,11 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>10200005&amp;10300005&amp;10100007&amp;11000011&amp;</t>
+          <t>10100007&amp;10200007&amp;10300007&amp;11000004&amp;</t>
         </is>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1030040001</v>
+        <v>1030020001</v>
       </c>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
@@ -2209,16 +2191,16 @@
       </c>
       <c r="Z17" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（雷）</t>
+          <t>人类-魔法师（水）</t>
         </is>
       </c>
     </row>
     <row r="18" customFormat="1" s="1">
       <c r="A18" s="4" t="n">
-        <v>1031010001</v>
+        <v>1030030001</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>103101</v>
+        <v>103003</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1</v>
@@ -2261,32 +2243,31 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
+          <t>10200007&amp;10100007&amp;10300007&amp;11000010&amp;</t>
         </is>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1031010001</v>
+        <v>1030030001</v>
       </c>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
-      <c r="S18" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T18" s="1" t="n">
-        <v>100002</v>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
       </c>
       <c r="Z18" s="4" t="inlineStr">
         <is>
-          <t>人类-大魔法师（火）</t>
+          <t>人类-魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="19" customFormat="1" s="2">
       <c r="A19" s="4" t="n">
-        <v>1031020001</v>
+        <v>1030040001</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>103102</v>
+        <v>103004</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1</v>
@@ -2329,32 +2310,31 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
+          <t>10200005&amp;10300005&amp;10100007&amp;11000011&amp;</t>
         </is>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1031010002</v>
+        <v>1030040001</v>
       </c>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
-      <c r="S19" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>100003</v>
+      <c r="S19" s="1" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
       </c>
       <c r="Z19" s="4" t="inlineStr">
         <is>
-          <t>人类-大魔法师（水）</t>
+          <t>人类-魔法师（雷）</t>
         </is>
       </c>
     </row>
     <row r="20" customFormat="1" s="2">
       <c r="A20" s="4" t="n">
-        <v>1031030001</v>
+        <v>1031010001</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>103103</v>
+        <v>103101</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1</v>
@@ -2401,216 +2381,244 @@
         </is>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1031010003</v>
+        <v>1031010001</v>
       </c>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="T20" s="0" t="n">
+      <c r="T20" s="1" t="n">
+        <v>100002</v>
+      </c>
+      <c r="Z20" s="4" t="inlineStr">
+        <is>
+          <t>人类-大魔法师（火）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="1" s="2">
+      <c r="A21" s="4" t="n">
+        <v>1031020001</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>103102</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>1031010002</v>
+      </c>
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n"/>
+      <c r="S21" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>100003</v>
+      </c>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>人类-大魔法师（水）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="3">
+      <c r="A22" s="4" t="n">
+        <v>1031030001</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>103103</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>1031010003</v>
+      </c>
+      <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="4" t="n"/>
+      <c r="S22" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T22" s="0" t="n">
         <v>100006</v>
       </c>
-      <c r="Z20" s="4" t="inlineStr">
+      <c r="Z22" s="4" t="inlineStr">
         <is>
           <t>人类-大魔法师（冰）-BOSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" customFormat="1" s="2">
-      <c r="A21" s="0" t="n">
-        <v>1031040001</v>
-      </c>
-      <c r="B21" s="0" t="n">
-        <v>103104</v>
-      </c>
-      <c r="C21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K21" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="N21" s="0" t="inlineStr">
-        <is>
-          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
-        </is>
-      </c>
-      <c r="P21" s="0" t="n">
-        <v>1031010004</v>
-      </c>
-      <c r="S21" s="0" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T21" s="0" t="n">
-        <v>100007</v>
-      </c>
-      <c r="Z21" s="0" t="inlineStr">
-        <is>
-          <t>人类-大魔法师（雷）-BOSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="3">
-      <c r="A22" s="0" t="n">
-        <v>1040010001</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>104001</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="I22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="M22" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="N22" s="0" t="inlineStr">
-        <is>
-          <t>10100008&amp;10200008&amp;10300008&amp;11020014&amp;</t>
-        </is>
-      </c>
-      <c r="P22" s="0" t="n">
-        <v>1040010001</v>
-      </c>
-      <c r="S22" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="Z22" s="0" t="inlineStr">
-        <is>
-          <t>盗贼</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="0" t="n">
-        <v>1041010001</v>
+        <v>1031040001</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>104101</v>
+        <v>103104</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="0" t="n">
-        <v>500</v>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="0" t="n">
-        <v>20</v>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="I23" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="0" t="n">
-        <v>8</v>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K23" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M23" s="0" t="n">
         <v>1000001</v>
       </c>
       <c r="N23" s="0" t="inlineStr">
         <is>
-          <t>10200009&amp;10300009&amp;11000012&amp;</t>
+          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
         </is>
       </c>
       <c r="P23" s="0" t="n">
-        <v>1041010001</v>
+        <v>1031010004</v>
       </c>
       <c r="S23" s="0" t="n">
         <v>1.2</v>
       </c>
       <c r="T23" s="0" t="n">
-        <v>100004</v>
+        <v>100007</v>
       </c>
       <c r="Z23" s="0" t="inlineStr">
         <is>
-          <t>BOSS-大剑战士</t>
+          <t>人类-大魔法师（雷）-BOSS</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="3">
       <c r="A24" s="0" t="n">
-        <v>1041020001</v>
+        <v>1040010001</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>104102</v>
+        <v>104001</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" s="0" t="n">
-        <v>10000</v>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H24" s="0" t="n">
         <v>5</v>
@@ -2619,475 +2627,511 @@
         <v>0</v>
       </c>
       <c r="J24" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N24" s="0" t="inlineStr">
+        <is>
+          <t>10100008&amp;10200008&amp;10300008&amp;11020014&amp;</t>
+        </is>
+      </c>
+      <c r="P24" s="0" t="n">
+        <v>1040010001</v>
+      </c>
+      <c r="S24" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="Z24" s="0" t="inlineStr">
+        <is>
+          <t>盗贼</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="3">
+      <c r="A25" s="0" t="n">
+        <v>1041010001</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>104101</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="M24" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="N24" s="0" t="inlineStr">
+      <c r="K25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N25" s="0" t="inlineStr">
+        <is>
+          <t>10200009&amp;10300009&amp;11000012&amp;</t>
+        </is>
+      </c>
+      <c r="P25" s="0" t="n">
+        <v>1041010001</v>
+      </c>
+      <c r="S25" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T25" s="0" t="n">
+        <v>100004</v>
+      </c>
+      <c r="Z25" s="0" t="inlineStr">
+        <is>
+          <t>BOSS-大剑战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="3">
+      <c r="A26" s="0" t="n">
+        <v>1041020001</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>104102</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="M26" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N26" s="0" t="inlineStr">
         <is>
           <t>10200009&amp;10300009&amp;11000015&amp;</t>
         </is>
       </c>
-      <c r="P24" s="0" t="n">
+      <c r="P26" s="0" t="n">
         <v>1041020001</v>
       </c>
-      <c r="S24" s="0" t="n">
+      <c r="S26" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="T24" s="0" t="inlineStr">
+      <c r="T26" s="0" t="inlineStr">
         <is>
           <t>100005</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y26" s="0" t="inlineStr">
         <is>
           <t>skill_update:100005:10</t>
         </is>
       </c>
-      <c r="Z24" s="0" t="inlineStr">
+      <c r="Z26" s="0" t="inlineStr">
         <is>
           <t>BOSS-大盾战士</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="3">
-      <c r="A25" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>10200016&amp;10300016&amp;</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="Q25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>cn</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t>白剑伟</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="3">
-      <c r="A26" s="2" t="n">
-        <v>2000000002</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>5050011&amp;5070005&amp;</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>2000000002</v>
-      </c>
-      <c r="Q26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>cn</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t>宛家伟</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000001</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="0" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G27" s="0" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H27" s="0" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I27" s="0" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J27" s="0" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K27" s="0" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L27" s="0" t="inlineStr">
-        <is>
-          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
-        </is>
-      </c>
-      <c r="M27" s="0" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>40200006&amp;40300003&amp;41000004&amp;</t>
-        </is>
-      </c>
+          <t>10200016&amp;10300016&amp;</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000001</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
+        </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W27" s="0" t="n">
+      <c r="W27" s="2" t="n">
         <v>4</v>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>雷神天尊斩</t>
+          <t>白剑伟</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
       <c r="A28" s="2" t="n">
+        <v>2000000002</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>5050011&amp;5070005&amp;</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>2000000002</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>宛家伟</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="3">
+      <c r="A29" s="2" t="n">
+        <v>2000000003</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="0" t="inlineStr">
+        <is>
+          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
+        </is>
+      </c>
+      <c r="M29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>40200006&amp;40300003&amp;41000004&amp;</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>2000000003</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="W29" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>雷神天尊斩</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="3">
+      <c r="A30" s="2" t="n">
         <v>2000000004</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" s="2" t="n">
+      <c r="C30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="0" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G28" s="0" t="inlineStr">
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H28" s="0" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I28" s="0" t="inlineStr">
+      <c r="I30" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J28" s="0" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="0" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" s="0" t="inlineStr">
+      <c r="L30" s="0" t="inlineStr">
         <is>
           <t>1030006&amp;1040002&amp;1050012&amp;1060002&amp;</t>
         </is>
       </c>
-      <c r="M28" s="0" t="inlineStr">
+      <c r="M30" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>10300011&amp;10200011&amp;</t>
         </is>
       </c>
-      <c r="O28" s="0" t="inlineStr"/>
-      <c r="P28" s="2" t="n">
+      <c r="O30" s="0" t="inlineStr"/>
+      <c r="P30" s="2" t="n">
         <v>2000000004</v>
       </c>
-      <c r="Q28" s="2" t="n">
+      <c r="Q30" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="2" t="n"/>
-      <c r="U28" s="0" t="inlineStr">
+      <c r="R30" s="2" t="n"/>
+      <c r="U30" s="0" t="inlineStr">
         <is>
           <t>3,255,255,255,255&amp;6,178,38,38,255&amp;</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W28" s="0" t="n">
+      <c r="W30" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>卡米莉娅</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="3">
-      <c r="A29" s="0" t="n">
-        <v>3000010011</v>
-      </c>
-      <c r="B29" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C29" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O29" s="0" t="inlineStr">
-        <is>
-          <t>10000002,N</t>
-        </is>
-      </c>
-      <c r="P29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="3">
-      <c r="A30" s="0" t="n">
-        <v>3000010012</v>
-      </c>
-      <c r="B30" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C30" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O30" s="0" t="inlineStr">
-        <is>
-          <t>10000002,N,R</t>
-        </is>
-      </c>
-      <c r="P30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W30" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级2</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="3">
       <c r="A31" s="0" t="n">
-        <v>3000010013</v>
+        <v>3000010011</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>1001</v>
@@ -3103,27 +3147,27 @@
       </c>
       <c r="O31" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W31" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z31" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级3</t>
+          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="3">
       <c r="A32" s="0" t="n">
-        <v>3000010014</v>
+        <v>3000010012</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>1001</v>
@@ -3139,27 +3183,27 @@
       </c>
       <c r="O32" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W32" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级4</t>
+          <t>议会随机议员-生物1001-评级2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>3000010015</v>
+        <v>3000010013</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>1001</v>
@@ -3175,31 +3219,30 @@
       </c>
       <c r="O33" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="S33" s="0" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="W33" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z33" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级5</t>
+          <t>议会随机议员-生物1001-评级3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>3000010021</v>
+        <v>3000010014</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>3</v>
@@ -3212,30 +3255,30 @@
       </c>
       <c r="O34" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W34" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z34" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级1</t>
+          <t>议会随机议员-生物1001-评级4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>3000010022</v>
+        <v>3000010015</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>3</v>
@@ -3248,27 +3291,28 @@
       </c>
       <c r="O35" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P35" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="0" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="S35" s="0" t="inlineStr"/>
       <c r="W35" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z35" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级2</t>
+          <t>议会随机议员-生物1001-评级5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>3000010023</v>
+        <v>3000010021</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1002</v>
@@ -3284,27 +3328,27 @@
       </c>
       <c r="O36" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P36" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W36" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z36" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级3</t>
+          <t>议会随机议员-生物1002-评级1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>3000010024</v>
+        <v>3000010022</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>1002</v>
@@ -3320,27 +3364,27 @@
       </c>
       <c r="O37" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W37" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z37" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级4</t>
+          <t>议会随机议员-生物1002-评级2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>3000010025</v>
+        <v>3000010023</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>1002</v>
@@ -3356,30 +3400,30 @@
       </c>
       <c r="O38" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W38" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z38" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级5</t>
+          <t>议会随机议员-生物1002-评级3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>3000010031</v>
+        <v>3000010024</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>3</v>
@@ -3392,30 +3436,30 @@
       </c>
       <c r="O39" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W39" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z39" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级1</t>
+          <t>议会随机议员-生物1002-评级4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>3000010032</v>
+        <v>3000010025</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>3</v>
@@ -3428,27 +3472,27 @@
       </c>
       <c r="O40" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P40" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W40" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z40" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级2</t>
+          <t>议会随机议员-生物1002-评级5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>3000010033</v>
+        <v>3000010031</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>1003</v>
@@ -3464,27 +3508,27 @@
       </c>
       <c r="O41" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W41" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级3</t>
+          <t>议会随机议员-生物1003-评级1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>3000010034</v>
+        <v>3000010032</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>1003</v>
@@ -3500,27 +3544,27 @@
       </c>
       <c r="O42" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W42" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级4</t>
+          <t>议会随机议员-生物1003-评级2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>3000010035</v>
+        <v>3000010033</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>1003</v>
@@ -3536,30 +3580,30 @@
       </c>
       <c r="O43" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P43" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W43" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级5</t>
+          <t>议会随机议员-生物1003-评级3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>3000010041</v>
+        <v>3000010034</v>
       </c>
       <c r="B44" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>3</v>
@@ -3572,30 +3616,30 @@
       </c>
       <c r="O44" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P44" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W44" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z44" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级1</t>
+          <t>议会随机议员-生物1003-评级4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>3000010042</v>
+        <v>3000010035</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>3</v>
@@ -3608,27 +3652,27 @@
       </c>
       <c r="O45" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P45" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W45" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z45" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级2</t>
+          <t>议会随机议员-生物1003-评级5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>3000010043</v>
+        <v>3000010041</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>1004</v>
@@ -3644,27 +3688,27 @@
       </c>
       <c r="O46" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P46" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W46" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z46" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级3</t>
+          <t>议会随机议员-生物1004-评级1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>3000010044</v>
+        <v>3000010042</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>1004</v>
@@ -3680,27 +3724,27 @@
       </c>
       <c r="O47" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P47" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W47" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z47" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级4</t>
+          <t>议会随机议员-生物1004-评级2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>3000010045</v>
+        <v>3000010043</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>1004</v>
@@ -3716,30 +3760,30 @@
       </c>
       <c r="O48" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P48" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W48" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z48" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级5</t>
+          <t>议会随机议员-生物1004-评级3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>3000020011</v>
+        <v>3000010044</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C49" s="0" t="n">
         <v>3</v>
@@ -3752,30 +3796,30 @@
       </c>
       <c r="O49" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P49" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W49" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z49" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级1</t>
+          <t>议会随机议员-生物1004-评级4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>3000020012</v>
+        <v>3000010045</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>3</v>
@@ -3788,27 +3832,27 @@
       </c>
       <c r="O50" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P50" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W50" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z50" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级2</t>
+          <t>议会随机议员-生物1004-评级5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>3000020013</v>
+        <v>3000020011</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>2001</v>
@@ -3824,27 +3868,27 @@
       </c>
       <c r="O51" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P51" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W51" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z51" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级3</t>
+          <t>议会随机议员-生物2001-评级1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>3000020014</v>
+        <v>3000020012</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>2001</v>
@@ -3860,27 +3904,27 @@
       </c>
       <c r="O52" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P52" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W52" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z52" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级4</t>
+          <t>议会随机议员-生物2001-评级2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>3000020015</v>
+        <v>3000020013</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>2001</v>
@@ -3896,30 +3940,30 @@
       </c>
       <c r="O53" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z53" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级5</t>
+          <t>议会随机议员-生物2001-评级3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>3000020021</v>
+        <v>3000020014</v>
       </c>
       <c r="B54" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>3</v>
@@ -3932,30 +3976,30 @@
       </c>
       <c r="O54" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P54" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z54" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级1</t>
+          <t>议会随机议员-生物2001-评级4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>3000020022</v>
+        <v>3000020015</v>
       </c>
       <c r="B55" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>3</v>
@@ -3968,27 +4012,27 @@
       </c>
       <c r="O55" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P55" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z55" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级2</t>
+          <t>议会随机议员-生物2001-评级5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>3000020023</v>
+        <v>3000020021</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>2002</v>
@@ -4004,27 +4048,27 @@
       </c>
       <c r="O56" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P56" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W56" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z56" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级3</t>
+          <t>议会随机议员-生物2002-评级1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>3000020024</v>
+        <v>3000020022</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>2002</v>
@@ -4040,27 +4084,27 @@
       </c>
       <c r="O57" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P57" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z57" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级4</t>
+          <t>议会随机议员-生物2002-评级2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>3000020025</v>
+        <v>3000020023</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>2002</v>
@@ -4076,30 +4120,30 @@
       </c>
       <c r="O58" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P58" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W58" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z58" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级5</t>
+          <t>议会随机议员-生物2002-评级3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>3000020031</v>
+        <v>3000020024</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C59" s="0" t="n">
         <v>3</v>
@@ -4112,30 +4156,30 @@
       </c>
       <c r="O59" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P59" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W59" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z59" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级1</t>
+          <t>议会随机议员-生物2002-评级4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>3000020032</v>
+        <v>3000020025</v>
       </c>
       <c r="B60" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C60" s="0" t="n">
         <v>3</v>
@@ -4148,27 +4192,27 @@
       </c>
       <c r="O60" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P60" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W60" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z60" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级2</t>
+          <t>议会随机议员-生物2002-评级5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3000020033</v>
+        <v>3000020031</v>
       </c>
       <c r="B61" s="0" t="n">
         <v>2003</v>
@@ -4184,27 +4228,27 @@
       </c>
       <c r="O61" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P61" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W61" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z61" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级3</t>
+          <t>议会随机议员-生物2003-评级1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3000020034</v>
+        <v>3000020032</v>
       </c>
       <c r="B62" s="0" t="n">
         <v>2003</v>
@@ -4220,27 +4264,27 @@
       </c>
       <c r="O62" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P62" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W62" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z62" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级4</t>
+          <t>议会随机议员-生物2003-评级2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>3000020035</v>
+        <v>3000020033</v>
       </c>
       <c r="B63" s="0" t="n">
         <v>2003</v>
@@ -4256,30 +4300,30 @@
       </c>
       <c r="O63" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P63" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z63" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级5</t>
+          <t>议会随机议员-生物2003-评级3</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="3">
       <c r="A64" s="0" t="n">
-        <v>3000020041</v>
+        <v>3000020034</v>
       </c>
       <c r="B64" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>3</v>
@@ -4292,30 +4336,30 @@
       </c>
       <c r="O64" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P64" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W64" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z64" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级1</t>
+          <t>议会随机议员-生物2003-评级4</t>
         </is>
       </c>
     </row>
     <row r="65" ht="12" customHeight="1" s="3">
       <c r="A65" s="0" t="n">
-        <v>3000020042</v>
+        <v>3000020035</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>3</v>
@@ -4328,27 +4372,27 @@
       </c>
       <c r="O65" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P65" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z65" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级2</t>
+          <t>议会随机议员-生物2003-评级5</t>
         </is>
       </c>
     </row>
     <row r="66" ht="12" customHeight="1" s="3">
       <c r="A66" s="0" t="n">
-        <v>3000020043</v>
+        <v>3000020041</v>
       </c>
       <c r="B66" s="0" t="n">
         <v>2004</v>
@@ -4364,27 +4408,27 @@
       </c>
       <c r="O66" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P66" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z66" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级3</t>
+          <t>议会随机议员-生物2004-评级1</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="3">
       <c r="A67" s="0" t="n">
-        <v>3000020044</v>
+        <v>3000020042</v>
       </c>
       <c r="B67" s="0" t="n">
         <v>2004</v>
@@ -4400,27 +4444,27 @@
       </c>
       <c r="O67" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P67" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z67" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级4</t>
+          <t>议会随机议员-生物2004-评级2</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="3">
       <c r="A68" s="0" t="n">
-        <v>3000020045</v>
+        <v>3000020043</v>
       </c>
       <c r="B68" s="0" t="n">
         <v>2004</v>
@@ -4436,30 +4480,30 @@
       </c>
       <c r="O68" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P68" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z68" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级5</t>
+          <t>议会随机议员-生物2004-评级3</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>3000030011</v>
+        <v>3000020044</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>3</v>
@@ -4472,30 +4516,30 @@
       </c>
       <c r="O69" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P69" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z69" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级1</t>
+          <t>议会随机议员-生物2004-评级4</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>3000030012</v>
+        <v>3000020045</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>3</v>
@@ -4508,27 +4552,27 @@
       </c>
       <c r="O70" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P70" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z70" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级2</t>
+          <t>议会随机议员-生物2004-评级5</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>3000030013</v>
+        <v>3000030011</v>
       </c>
       <c r="B71" s="0" t="n">
         <v>3001</v>
@@ -4544,27 +4588,27 @@
       </c>
       <c r="O71" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P71" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z71" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级3</t>
+          <t>议会随机议员-生物3001-评级1</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="3">
       <c r="A72" s="0" t="n">
-        <v>3000030014</v>
+        <v>3000030012</v>
       </c>
       <c r="B72" s="0" t="n">
         <v>3001</v>
@@ -4580,27 +4624,27 @@
       </c>
       <c r="O72" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P72" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z72" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级4</t>
+          <t>议会随机议员-生物3001-评级2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>3000030015</v>
+        <v>3000030013</v>
       </c>
       <c r="B73" s="0" t="n">
         <v>3001</v>
@@ -4616,30 +4660,30 @@
       </c>
       <c r="O73" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P73" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z73" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级5</t>
+          <t>议会随机议员-生物3001-评级3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>3000030021</v>
+        <v>3000030014</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>3</v>
@@ -4652,30 +4696,30 @@
       </c>
       <c r="O74" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P74" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z74" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级1</t>
+          <t>议会随机议员-生物3001-评级4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>3000030022</v>
+        <v>3000030015</v>
       </c>
       <c r="B75" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>3</v>
@@ -4688,27 +4732,27 @@
       </c>
       <c r="O75" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P75" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z75" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级2</t>
+          <t>议会随机议员-生物3001-评级5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>3000030023</v>
+        <v>3000030021</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>3002</v>
@@ -4724,27 +4768,27 @@
       </c>
       <c r="O76" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P76" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z76" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级3</t>
+          <t>议会随机议员-生物3002-评级1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>3000030024</v>
+        <v>3000030022</v>
       </c>
       <c r="B77" s="0" t="n">
         <v>3002</v>
@@ -4760,27 +4804,27 @@
       </c>
       <c r="O77" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P77" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z77" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级4</t>
+          <t>议会随机议员-生物3002-评级2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>3000030025</v>
+        <v>3000030023</v>
       </c>
       <c r="B78" s="0" t="n">
         <v>3002</v>
@@ -4796,30 +4840,30 @@
       </c>
       <c r="O78" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P78" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z78" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级5</t>
+          <t>议会随机议员-生物3002-评级3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>3000030031</v>
+        <v>3000030024</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>3</v>
@@ -4832,30 +4876,30 @@
       </c>
       <c r="O79" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P79" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z79" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级1</t>
+          <t>议会随机议员-生物3002-评级4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>3000030032</v>
+        <v>3000030025</v>
       </c>
       <c r="B80" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C80" s="0" t="n">
         <v>3</v>
@@ -4868,27 +4912,27 @@
       </c>
       <c r="O80" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P80" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z80" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级2</t>
+          <t>议会随机议员-生物3002-评级5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>3000030033</v>
+        <v>3000030031</v>
       </c>
       <c r="B81" s="0" t="n">
         <v>3003</v>
@@ -4904,27 +4948,27 @@
       </c>
       <c r="O81" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P81" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q81" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z81" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级3</t>
+          <t>议会随机议员-生物3003-评级1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>3000030034</v>
+        <v>3000030032</v>
       </c>
       <c r="B82" s="0" t="n">
         <v>3003</v>
@@ -4940,27 +4984,27 @@
       </c>
       <c r="O82" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P82" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z82" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级4</t>
+          <t>议会随机议员-生物3003-评级2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>3000030035</v>
+        <v>3000030033</v>
       </c>
       <c r="B83" s="0" t="n">
         <v>3003</v>
@@ -4976,30 +5020,30 @@
       </c>
       <c r="O83" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P83" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z83" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级5</t>
+          <t>议会随机议员-生物3003-评级3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>3000030041</v>
+        <v>3000030034</v>
       </c>
       <c r="B84" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C84" s="0" t="n">
         <v>3</v>
@@ -5012,30 +5056,30 @@
       </c>
       <c r="O84" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P84" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q84" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W84" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z84" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级1</t>
+          <t>议会随机议员-生物3003-评级4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>3000030042</v>
+        <v>3000030035</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C85" s="0" t="n">
         <v>3</v>
@@ -5048,27 +5092,27 @@
       </c>
       <c r="O85" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P85" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q85" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z85" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级2</t>
+          <t>议会随机议员-生物3003-评级5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>3000030043</v>
+        <v>3000030041</v>
       </c>
       <c r="B86" s="0" t="n">
         <v>3004</v>
@@ -5084,27 +5128,27 @@
       </c>
       <c r="O86" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P86" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W86" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z86" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级3</t>
+          <t>议会随机议员-生物3004-评级1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>3000030044</v>
+        <v>3000030042</v>
       </c>
       <c r="B87" s="0" t="n">
         <v>3004</v>
@@ -5120,27 +5164,27 @@
       </c>
       <c r="O87" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P87" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z87" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级4</t>
+          <t>议会随机议员-生物3004-评级2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>3000030045</v>
+        <v>3000030043</v>
       </c>
       <c r="B88" s="0" t="n">
         <v>3004</v>
@@ -5156,30 +5200,30 @@
       </c>
       <c r="O88" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P88" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q88" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z88" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级5</t>
+          <t>议会随机议员-生物3004-评级3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>3000040011</v>
+        <v>3000030044</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C89" s="0" t="n">
         <v>3</v>
@@ -5192,30 +5236,30 @@
       </c>
       <c r="O89" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P89" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q89" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W89" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z89" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级1</t>
+          <t>议会随机议员-生物3004-评级4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>3000040012</v>
+        <v>3000030045</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C90" s="0" t="n">
         <v>3</v>
@@ -5228,27 +5272,27 @@
       </c>
       <c r="O90" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P90" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z90" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级2</t>
+          <t>议会随机议员-生物3004-评级5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>3000040013</v>
+        <v>3000040011</v>
       </c>
       <c r="B91" s="0" t="n">
         <v>4001</v>
@@ -5264,27 +5308,27 @@
       </c>
       <c r="O91" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P91" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q91" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W91" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z91" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级3</t>
+          <t>议会随机议员-生物4001-评级1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>3000040014</v>
+        <v>3000040012</v>
       </c>
       <c r="B92" s="0" t="n">
         <v>4001</v>
@@ -5300,27 +5344,27 @@
       </c>
       <c r="O92" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P92" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q92" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z92" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级4</t>
+          <t>议会随机议员-生物4001-评级2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>3000040015</v>
+        <v>3000040013</v>
       </c>
       <c r="B93" s="0" t="n">
         <v>4001</v>
@@ -5336,30 +5380,30 @@
       </c>
       <c r="O93" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P93" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q93" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z93" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级5</t>
+          <t>议会随机议员-生物4001-评级3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>3000040021</v>
+        <v>3000040014</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C94" s="0" t="n">
         <v>3</v>
@@ -5372,30 +5416,30 @@
       </c>
       <c r="O94" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P94" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W94" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z94" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级1</t>
+          <t>议会随机议员-生物4001-评级4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>3000040022</v>
+        <v>3000040015</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C95" s="0" t="n">
         <v>3</v>
@@ -5408,27 +5452,27 @@
       </c>
       <c r="O95" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P95" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q95" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W95" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z95" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级2</t>
+          <t>议会随机议员-生物4001-评级5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>3000040023</v>
+        <v>3000040021</v>
       </c>
       <c r="B96" s="0" t="n">
         <v>4002</v>
@@ -5444,27 +5488,27 @@
       </c>
       <c r="O96" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P96" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q96" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W96" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z96" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级3</t>
+          <t>议会随机议员-生物4002-评级1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>3000040024</v>
+        <v>3000040022</v>
       </c>
       <c r="B97" s="0" t="n">
         <v>4002</v>
@@ -5480,27 +5524,27 @@
       </c>
       <c r="O97" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P97" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q97" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W97" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z97" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级4</t>
+          <t>议会随机议员-生物4002-评级2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>3000040025</v>
+        <v>3000040023</v>
       </c>
       <c r="B98" s="0" t="n">
         <v>4002</v>
@@ -5516,30 +5560,30 @@
       </c>
       <c r="O98" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P98" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q98" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W98" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z98" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级5</t>
+          <t>议会随机议员-生物4002-评级3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>3000040031</v>
+        <v>3000040024</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C99" s="0" t="n">
         <v>3</v>
@@ -5552,30 +5596,30 @@
       </c>
       <c r="O99" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P99" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q99" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W99" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z99" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级1</t>
+          <t>议会随机议员-生物4002-评级4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>3000040032</v>
+        <v>3000040025</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>3</v>
@@ -5588,27 +5632,27 @@
       </c>
       <c r="O100" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P100" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q100" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W100" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z100" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级2</t>
+          <t>议会随机议员-生物4002-评级5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>3000040033</v>
+        <v>3000040031</v>
       </c>
       <c r="B101" s="0" t="n">
         <v>4003</v>
@@ -5624,27 +5668,27 @@
       </c>
       <c r="O101" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P101" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q101" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W101" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z101" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级3</t>
+          <t>议会随机议员-生物4003-评级1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>3000040034</v>
+        <v>3000040032</v>
       </c>
       <c r="B102" s="0" t="n">
         <v>4003</v>
@@ -5660,27 +5704,27 @@
       </c>
       <c r="O102" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P102" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q102" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z102" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级4</t>
+          <t>议会随机议员-生物4003-评级2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>3000040035</v>
+        <v>3000040033</v>
       </c>
       <c r="B103" s="0" t="n">
         <v>4003</v>
@@ -5696,30 +5740,30 @@
       </c>
       <c r="O103" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P103" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q103" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z103" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级5</t>
+          <t>议会随机议员-生物4003-评级3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>3000040041</v>
+        <v>3000040034</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C104" s="0" t="n">
         <v>3</v>
@@ -5732,30 +5776,30 @@
       </c>
       <c r="O104" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P104" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q104" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W104" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z104" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级1</t>
+          <t>议会随机议员-生物4003-评级4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>3000040042</v>
+        <v>3000040035</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C105" s="0" t="n">
         <v>3</v>
@@ -5768,27 +5812,27 @@
       </c>
       <c r="O105" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P105" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q105" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z105" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级2</t>
+          <t>议会随机议员-生物4003-评级5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>3000040043</v>
+        <v>3000040041</v>
       </c>
       <c r="B106" s="0" t="n">
         <v>4004</v>
@@ -5804,27 +5848,27 @@
       </c>
       <c r="O106" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P106" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q106" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W106" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z106" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级3</t>
+          <t>议会随机议员-生物4004-评级1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>3000040044</v>
+        <v>3000040042</v>
       </c>
       <c r="B107" s="0" t="n">
         <v>4004</v>
@@ -5840,27 +5884,27 @@
       </c>
       <c r="O107" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P107" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q107" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z107" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级4</t>
+          <t>议会随机议员-生物4004-评级2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>3000040045</v>
+        <v>3000040043</v>
       </c>
       <c r="B108" s="0" t="n">
         <v>4004</v>
@@ -5876,30 +5920,30 @@
       </c>
       <c r="O108" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P108" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z108" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级5</t>
+          <t>议会随机议员-生物4004-评级3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>3000040051</v>
+        <v>3000040044</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>3</v>
@@ -5912,30 +5956,30 @@
       </c>
       <c r="O109" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P109" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q109" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W109" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z109" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级1</t>
+          <t>议会随机议员-生物4004-评级4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>3000040052</v>
+        <v>3000040045</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C110" s="0" t="n">
         <v>3</v>
@@ -5948,27 +5992,27 @@
       </c>
       <c r="O110" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P110" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q110" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W110" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z110" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级2</t>
+          <t>议会随机议员-生物4004-评级5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>3000040053</v>
+        <v>3000040051</v>
       </c>
       <c r="B111" s="0" t="n">
         <v>4005</v>
@@ -5984,27 +6028,27 @@
       </c>
       <c r="O111" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P111" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q111" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W111" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z111" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级3</t>
+          <t>议会随机议员-生物4005-评级1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>3000040054</v>
+        <v>3000040052</v>
       </c>
       <c r="B112" s="0" t="n">
         <v>4005</v>
@@ -6020,27 +6064,27 @@
       </c>
       <c r="O112" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P112" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W112" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z112" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级4</t>
+          <t>议会随机议员-生物4005-评级2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>3000040055</v>
+        <v>3000040053</v>
       </c>
       <c r="B113" s="0" t="n">
         <v>4005</v>
@@ -6056,30 +6100,30 @@
       </c>
       <c r="O113" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P113" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q113" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z113" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级5</t>
+          <t>议会随机议员-生物4005-评级3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>3000050011</v>
+        <v>3000040054</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C114" s="0" t="n">
         <v>3</v>
@@ -6092,30 +6136,30 @@
       </c>
       <c r="O114" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P114" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q114" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W114" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z114" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级1</t>
+          <t>议会随机议员-生物4005-评级4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>3000050012</v>
+        <v>3000040055</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C115" s="0" t="n">
         <v>3</v>
@@ -6128,27 +6172,27 @@
       </c>
       <c r="O115" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P115" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W115" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z115" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级2</t>
+          <t>议会随机议员-生物4005-评级5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>3000050013</v>
+        <v>3000050011</v>
       </c>
       <c r="B116" s="0" t="n">
         <v>5001</v>
@@ -6164,27 +6208,27 @@
       </c>
       <c r="O116" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P116" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q116" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W116" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z116" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级3</t>
+          <t>议会随机议员-生物5001-评级1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>3000050014</v>
+        <v>3000050012</v>
       </c>
       <c r="B117" s="0" t="n">
         <v>5001</v>
@@ -6200,27 +6244,27 @@
       </c>
       <c r="O117" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P117" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q117" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W117" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z117" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级4</t>
+          <t>议会随机议员-生物5001-评级2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>3000050015</v>
+        <v>3000050013</v>
       </c>
       <c r="B118" s="0" t="n">
         <v>5001</v>
@@ -6236,30 +6280,30 @@
       </c>
       <c r="O118" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P118" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q118" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z118" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级5</t>
+          <t>议会随机议员-生物5001-评级3</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>3000050021</v>
+        <v>3000050014</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C119" s="0" t="n">
         <v>3</v>
@@ -6272,30 +6316,30 @@
       </c>
       <c r="O119" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P119" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q119" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W119" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z119" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级1</t>
+          <t>议会随机议员-生物5001-评级4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>3000050022</v>
+        <v>3000050015</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C120" s="0" t="n">
         <v>3</v>
@@ -6308,27 +6352,27 @@
       </c>
       <c r="O120" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P120" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q120" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W120" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z120" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级2</t>
+          <t>议会随机议员-生物5001-评级5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>3000050023</v>
+        <v>3000050021</v>
       </c>
       <c r="B121" s="0" t="n">
         <v>5002</v>
@@ -6344,27 +6388,27 @@
       </c>
       <c r="O121" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P121" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W121" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z121" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级3</t>
+          <t>议会随机议员-生物5002-评级1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>3000050024</v>
+        <v>3000050022</v>
       </c>
       <c r="B122" s="0" t="n">
         <v>5002</v>
@@ -6380,27 +6424,27 @@
       </c>
       <c r="O122" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P122" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q122" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W122" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z122" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级4</t>
+          <t>议会随机议员-生物5002-评级2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>3000050025</v>
+        <v>3000050023</v>
       </c>
       <c r="B123" s="0" t="n">
         <v>5002</v>
@@ -6416,30 +6460,30 @@
       </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P123" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q123" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z123" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级5</t>
+          <t>议会随机议员-生物5002-评级3</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>3000050031</v>
+        <v>3000050024</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>3</v>
@@ -6452,30 +6496,30 @@
       </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P124" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q124" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W124" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z124" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级1</t>
+          <t>议会随机议员-生物5002-评级4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>3000050032</v>
+        <v>3000050025</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>3</v>
@@ -6488,27 +6532,27 @@
       </c>
       <c r="O125" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P125" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q125" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z125" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级2</t>
+          <t>议会随机议员-生物5002-评级5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>3000050033</v>
+        <v>3000050031</v>
       </c>
       <c r="B126" s="0" t="n">
         <v>5003</v>
@@ -6524,27 +6568,27 @@
       </c>
       <c r="O126" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P126" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q126" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W126" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z126" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级3</t>
+          <t>议会随机议员-生物5003-评级1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>3000050034</v>
+        <v>3000050032</v>
       </c>
       <c r="B127" s="0" t="n">
         <v>5003</v>
@@ -6560,27 +6604,27 @@
       </c>
       <c r="O127" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P127" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q127" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W127" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z127" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级4</t>
+          <t>议会随机议员-生物5003-评级2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>3000050035</v>
+        <v>3000050033</v>
       </c>
       <c r="B128" s="0" t="n">
         <v>5003</v>
@@ -6596,30 +6640,30 @@
       </c>
       <c r="O128" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P128" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q128" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z128" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级5</t>
+          <t>议会随机议员-生物5003-评级3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000050041</v>
+        <v>3000050034</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C129" s="0" t="n">
         <v>3</v>
@@ -6632,30 +6676,30 @@
       </c>
       <c r="O129" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P129" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q129" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W129" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z129" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级1</t>
+          <t>议会随机议员-生物5003-评级4</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000050042</v>
+        <v>3000050035</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C130" s="0" t="n">
         <v>3</v>
@@ -6668,27 +6712,27 @@
       </c>
       <c r="O130" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P130" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q130" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W130" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z130" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级2</t>
+          <t>议会随机议员-生物5003-评级5</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000050043</v>
+        <v>3000050041</v>
       </c>
       <c r="B131" s="0" t="n">
         <v>5004</v>
@@ -6704,27 +6748,27 @@
       </c>
       <c r="O131" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P131" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q131" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W131" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z131" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级3</t>
+          <t>议会随机议员-生物5004-评级1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000050044</v>
+        <v>3000050042</v>
       </c>
       <c r="B132" s="0" t="n">
         <v>5004</v>
@@ -6740,27 +6784,27 @@
       </c>
       <c r="O132" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P132" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q132" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W132" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z132" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级4</t>
+          <t>议会随机议员-生物5004-评级2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000050045</v>
+        <v>3000050043</v>
       </c>
       <c r="B133" s="0" t="n">
         <v>5004</v>
@@ -6776,30 +6820,30 @@
       </c>
       <c r="O133" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P133" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q133" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W133" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z133" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级5</t>
+          <t>议会随机议员-生物5004-评级3</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000060011</v>
+        <v>3000050044</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C134" s="0" t="n">
         <v>3</v>
@@ -6812,30 +6856,30 @@
       </c>
       <c r="O134" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P134" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q134" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W134" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z134" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级1</t>
+          <t>议会随机议员-生物5004-评级4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000060012</v>
+        <v>3000050045</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C135" s="0" t="n">
         <v>3</v>
@@ -6848,27 +6892,27 @@
       </c>
       <c r="O135" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P135" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q135" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W135" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z135" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级2</t>
+          <t>议会随机议员-生物5004-评级5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000060013</v>
+        <v>3000060011</v>
       </c>
       <c r="B136" s="0" t="n">
         <v>6001</v>
@@ -6884,27 +6928,27 @@
       </c>
       <c r="O136" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P136" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q136" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W136" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z136" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级3</t>
+          <t>议会随机议员-生物6001-评级1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000060014</v>
+        <v>3000060012</v>
       </c>
       <c r="B137" s="0" t="n">
         <v>6001</v>
@@ -6920,27 +6964,27 @@
       </c>
       <c r="O137" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P137" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q137" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W137" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z137" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级4</t>
+          <t>议会随机议员-生物6001-评级2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000060015</v>
+        <v>3000060013</v>
       </c>
       <c r="B138" s="0" t="n">
         <v>6001</v>
@@ -6956,30 +7000,30 @@
       </c>
       <c r="O138" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P138" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q138" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W138" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z138" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级5</t>
+          <t>议会随机议员-生物6001-评级3</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>3000060021</v>
+        <v>3000060014</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C139" s="0" t="n">
         <v>3</v>
@@ -6992,30 +7036,30 @@
       </c>
       <c r="O139" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P139" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q139" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W139" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z139" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级1</t>
+          <t>议会随机议员-生物6001-评级4</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>3000060022</v>
+        <v>3000060015</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C140" s="0" t="n">
         <v>3</v>
@@ -7028,27 +7072,27 @@
       </c>
       <c r="O140" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P140" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q140" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W140" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z140" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级2</t>
+          <t>议会随机议员-生物6001-评级5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>3000060023</v>
+        <v>3000060021</v>
       </c>
       <c r="B141" s="0" t="n">
         <v>6002</v>
@@ -7064,27 +7108,27 @@
       </c>
       <c r="O141" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P141" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q141" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W141" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z141" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级3</t>
+          <t>议会随机议员-生物6002-评级1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>3000060024</v>
+        <v>3000060022</v>
       </c>
       <c r="B142" s="0" t="n">
         <v>6002</v>
@@ -7100,27 +7144,27 @@
       </c>
       <c r="O142" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P142" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q142" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W142" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z142" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级4</t>
+          <t>议会随机议员-生物6002-评级2</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>3000060025</v>
+        <v>3000060023</v>
       </c>
       <c r="B143" s="0" t="n">
         <v>6002</v>
@@ -7136,30 +7180,30 @@
       </c>
       <c r="O143" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P143" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q143" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W143" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z143" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级5</t>
+          <t>议会随机议员-生物6002-评级3</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>3000060031</v>
+        <v>3000060024</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C144" s="0" t="n">
         <v>3</v>
@@ -7172,30 +7216,30 @@
       </c>
       <c r="O144" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P144" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q144" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W144" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z144" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级1</t>
+          <t>议会随机议员-生物6002-评级4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>3000060032</v>
+        <v>3000060025</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C145" s="0" t="n">
         <v>3</v>
@@ -7208,27 +7252,27 @@
       </c>
       <c r="O145" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P145" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q145" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W145" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z145" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级2</t>
+          <t>议会随机议员-生物6002-评级5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>3000060033</v>
+        <v>3000060031</v>
       </c>
       <c r="B146" s="0" t="n">
         <v>6003</v>
@@ -7244,27 +7288,27 @@
       </c>
       <c r="O146" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P146" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q146" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W146" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z146" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级3</t>
+          <t>议会随机议员-生物6003-评级1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>3000060034</v>
+        <v>3000060032</v>
       </c>
       <c r="B147" s="0" t="n">
         <v>6003</v>
@@ -7280,27 +7324,27 @@
       </c>
       <c r="O147" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P147" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q147" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W147" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z147" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级4</t>
+          <t>议会随机议员-生物6003-评级2</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>3000060035</v>
+        <v>3000060033</v>
       </c>
       <c r="B148" s="0" t="n">
         <v>6003</v>
@@ -7316,30 +7360,30 @@
       </c>
       <c r="O148" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P148" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q148" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W148" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z148" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级5</t>
+          <t>议会随机议员-生物6003-评级3</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>3000060041</v>
+        <v>3000060034</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C149" s="0" t="n">
         <v>3</v>
@@ -7352,30 +7396,30 @@
       </c>
       <c r="O149" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P149" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q149" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W149" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z149" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级1</t>
+          <t>议会随机议员-生物6003-评级4</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>3000060042</v>
+        <v>3000060035</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C150" s="0" t="n">
         <v>3</v>
@@ -7388,27 +7432,27 @@
       </c>
       <c r="O150" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P150" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q150" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W150" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z150" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级2</t>
+          <t>议会随机议员-生物6003-评级5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>3000060043</v>
+        <v>3000060041</v>
       </c>
       <c r="B151" s="0" t="n">
         <v>6004</v>
@@ -7424,27 +7468,27 @@
       </c>
       <c r="O151" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P151" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q151" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W151" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z151" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级3</t>
+          <t>议会随机议员-生物6004-评级1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>3000060044</v>
+        <v>3000060042</v>
       </c>
       <c r="B152" s="0" t="n">
         <v>6004</v>
@@ -7460,27 +7504,27 @@
       </c>
       <c r="O152" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P152" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q152" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W152" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z152" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级4</t>
+          <t>议会随机议员-生物6004-评级2</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>3000060045</v>
+        <v>3000060043</v>
       </c>
       <c r="B153" s="0" t="n">
         <v>6004</v>
@@ -7496,30 +7540,30 @@
       </c>
       <c r="O153" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P153" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q153" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W153" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z153" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级5</t>
+          <t>议会随机议员-生物6004-评级3</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>3000060051</v>
+        <v>3000060044</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C154" s="0" t="n">
         <v>3</v>
@@ -7532,30 +7576,30 @@
       </c>
       <c r="O154" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P154" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q154" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W154" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z154" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级1</t>
+          <t>议会随机议员-生物6004-评级4</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>3000060052</v>
+        <v>3000060045</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C155" s="0" t="n">
         <v>3</v>
@@ -7568,27 +7612,27 @@
       </c>
       <c r="O155" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P155" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q155" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W155" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z155" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级2</t>
+          <t>议会随机议员-生物6004-评级5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>3000060053</v>
+        <v>3000060051</v>
       </c>
       <c r="B156" s="0" t="n">
         <v>6005</v>
@@ -7604,27 +7648,27 @@
       </c>
       <c r="O156" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P156" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q156" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W156" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z156" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级3</t>
+          <t>议会随机议员-生物6005-评级1</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>3000060054</v>
+        <v>3000060052</v>
       </c>
       <c r="B157" s="0" t="n">
         <v>6005</v>
@@ -7640,27 +7684,27 @@
       </c>
       <c r="O157" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P157" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q157" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W157" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z157" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级4</t>
+          <t>议会随机议员-生物6005-评级2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>3000060055</v>
+        <v>3000060053</v>
       </c>
       <c r="B158" s="0" t="n">
         <v>6005</v>
@@ -7676,30 +7720,30 @@
       </c>
       <c r="O158" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P158" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q158" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W158" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z158" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级5</t>
+          <t>议会随机议员-生物6005-评级3</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>3000070011</v>
+        <v>3000060054</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C159" s="0" t="n">
         <v>3</v>
@@ -7712,30 +7756,30 @@
       </c>
       <c r="O159" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P159" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q159" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W159" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z159" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级1</t>
+          <t>议会随机议员-生物6005-评级4</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>3000070012</v>
+        <v>3000060055</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C160" s="0" t="n">
         <v>3</v>
@@ -7748,27 +7792,27 @@
       </c>
       <c r="O160" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P160" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q160" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W160" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z160" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级2</t>
+          <t>议会随机议员-生物6005-评级5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>3000070013</v>
+        <v>3000070011</v>
       </c>
       <c r="B161" s="0" t="n">
         <v>7001</v>
@@ -7784,27 +7828,27 @@
       </c>
       <c r="O161" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P161" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q161" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W161" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z161" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级3</t>
+          <t>议会随机议员-生物7001-评级1</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>3000070014</v>
+        <v>3000070012</v>
       </c>
       <c r="B162" s="0" t="n">
         <v>7001</v>
@@ -7820,27 +7864,27 @@
       </c>
       <c r="O162" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P162" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q162" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W162" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z162" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级4</t>
+          <t>议会随机议员-生物7001-评级2</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>3000070015</v>
+        <v>3000070013</v>
       </c>
       <c r="B163" s="0" t="n">
         <v>7001</v>
@@ -7856,30 +7900,30 @@
       </c>
       <c r="O163" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P163" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q163" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W163" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z163" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级5</t>
+          <t>议会随机议员-生物7001-评级3</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000070021</v>
+        <v>3000070014</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C164" s="0" t="n">
         <v>3</v>
@@ -7892,30 +7936,30 @@
       </c>
       <c r="O164" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P164" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q164" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W164" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z164" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级1</t>
+          <t>议会随机议员-生物7001-评级4</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000070022</v>
+        <v>3000070015</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C165" s="0" t="n">
         <v>3</v>
@@ -7928,27 +7972,27 @@
       </c>
       <c r="O165" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P165" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q165" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W165" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z165" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级2</t>
+          <t>议会随机议员-生物7001-评级5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000070023</v>
+        <v>3000070021</v>
       </c>
       <c r="B166" s="0" t="n">
         <v>7002</v>
@@ -7964,27 +8008,27 @@
       </c>
       <c r="O166" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P166" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q166" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W166" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z166" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级3</t>
+          <t>议会随机议员-生物7002-评级1</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000070024</v>
+        <v>3000070022</v>
       </c>
       <c r="B167" s="0" t="n">
         <v>7002</v>
@@ -8000,27 +8044,27 @@
       </c>
       <c r="O167" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P167" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q167" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W167" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z167" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级4</t>
+          <t>议会随机议员-生物7002-评级2</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000070025</v>
+        <v>3000070023</v>
       </c>
       <c r="B168" s="0" t="n">
         <v>7002</v>
@@ -8036,30 +8080,30 @@
       </c>
       <c r="O168" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P168" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q168" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W168" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z168" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级5</t>
+          <t>议会随机议员-生物7002-评级3</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000070031</v>
+        <v>3000070024</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C169" s="0" t="n">
         <v>3</v>
@@ -8072,30 +8116,30 @@
       </c>
       <c r="O169" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P169" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q169" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W169" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z169" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级1</t>
+          <t>议会随机议员-生物7002-评级4</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>3000070032</v>
+        <v>3000070025</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C170" s="0" t="n">
         <v>3</v>
@@ -8108,27 +8152,27 @@
       </c>
       <c r="O170" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P170" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q170" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W170" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z170" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级2</t>
+          <t>议会随机议员-生物7002-评级5</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000070033</v>
+        <v>3000070031</v>
       </c>
       <c r="B171" s="0" t="n">
         <v>7003</v>
@@ -8144,27 +8188,27 @@
       </c>
       <c r="O171" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P171" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q171" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W171" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z171" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级3</t>
+          <t>议会随机议员-生物7003-评级1</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>3000070034</v>
+        <v>3000070032</v>
       </c>
       <c r="B172" s="0" t="n">
         <v>7003</v>
@@ -8180,27 +8224,27 @@
       </c>
       <c r="O172" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P172" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q172" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W172" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z172" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级4</t>
+          <t>议会随机议员-生物7003-评级2</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>3000070035</v>
+        <v>3000070033</v>
       </c>
       <c r="B173" s="0" t="n">
         <v>7003</v>
@@ -8216,30 +8260,30 @@
       </c>
       <c r="O173" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P173" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q173" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W173" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z173" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级5</t>
+          <t>议会随机议员-生物7003-评级3</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>3000070041</v>
+        <v>3000070034</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C174" s="0" t="n">
         <v>3</v>
@@ -8252,30 +8296,30 @@
       </c>
       <c r="O174" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P174" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q174" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W174" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z174" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级1</t>
+          <t>议会随机议员-生物7003-评级4</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>3000070042</v>
+        <v>3000070035</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C175" s="0" t="n">
         <v>3</v>
@@ -8288,27 +8332,27 @@
       </c>
       <c r="O175" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P175" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q175" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W175" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z175" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级2</t>
+          <t>议会随机议员-生物7003-评级5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>3000070043</v>
+        <v>3000070041</v>
       </c>
       <c r="B176" s="0" t="n">
         <v>7004</v>
@@ -8324,27 +8368,27 @@
       </c>
       <c r="O176" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P176" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q176" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W176" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z176" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级3</t>
+          <t>议会随机议员-生物7004-评级1</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>3000070044</v>
+        <v>3000070042</v>
       </c>
       <c r="B177" s="0" t="n">
         <v>7004</v>
@@ -8360,27 +8404,27 @@
       </c>
       <c r="O177" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P177" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q177" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W177" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z177" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级4</t>
+          <t>议会随机议员-生物7004-评级2</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>3000070045</v>
+        <v>3000070043</v>
       </c>
       <c r="B178" s="0" t="n">
         <v>7004</v>
@@ -8396,19 +8440,91 @@
       </c>
       <c r="O178" s="0" t="inlineStr">
         <is>
+          <t>70000002,R</t>
+        </is>
+      </c>
+      <c r="P178" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z178" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级3</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="n">
+        <v>3000070044</v>
+      </c>
+      <c r="B179" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D179" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O179" s="0" t="inlineStr">
+        <is>
+          <t>70000002,R,SR</t>
+        </is>
+      </c>
+      <c r="P179" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z179" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级4</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="n">
+        <v>3000070045</v>
+      </c>
+      <c r="B180" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D180" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O180" s="0" t="inlineStr">
+        <is>
           <t>70000002,SR,SSR</t>
         </is>
       </c>
-      <c r="P178" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q178" s="0" t="n">
+      <c r="P180" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="W178" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z178" s="0" t="inlineStr">
+      <c r="W180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z180" s="0" t="inlineStr">
         <is>
           <t>议会随机议员-生物7004-评级5</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z186"/>
+  <dimension ref="A1:Z188"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.375" customWidth="1" style="3" min="1" max="2"/>
@@ -1625,11 +1625,9 @@
       <c r="K8" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="0" t="n">
-        <v>2010000</v>
-      </c>
+      <c r="L8" s="0" t="inlineStr"/>
       <c r="M8" s="0" t="n">
-        <v>0</v>
+        <v>2000001</v>
       </c>
       <c r="N8" s="0" t="inlineStr"/>
       <c r="O8" s="0" t="inlineStr"/>
@@ -1654,7 +1652,7 @@
       <c r="X8" s="0" t="inlineStr"/>
       <c r="Z8" s="0" t="inlineStr">
         <is>
-          <t>召唤物-骷髅召唤师-骷髅战士（HP=20）</t>
+          <t>召唤物-骷髅召唤师-骷髅战士（HP=20，随机外貌=骷髅通用池2000001）</t>
         </is>
       </c>
     </row>
@@ -1692,11 +1690,9 @@
       <c r="K9" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="0" t="n">
-        <v>2010001</v>
-      </c>
+      <c r="L9" s="0" t="inlineStr"/>
       <c r="M9" s="0" t="n">
-        <v>0</v>
+        <v>2000001</v>
       </c>
       <c r="N9" s="0" t="inlineStr"/>
       <c r="O9" s="0" t="inlineStr"/>
@@ -1721,7 +1717,7 @@
       <c r="X9" s="0" t="inlineStr"/>
       <c r="Z9" s="0" t="inlineStr">
         <is>
-          <t>召唤物-骷髅召唤师-骷髅投手（HP=20）</t>
+          <t>召唤物-骷髅召唤师-骷髅投手（HP=20，随机外貌=骷髅通用池2000001）</t>
         </is>
       </c>
     </row>
@@ -2798,144 +2794,175 @@
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="0" t="n">
-        <v>1040010001</v>
+        <v>1031080001</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>104001</v>
+        <v>103108</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="D27" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="F27" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>150</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H27" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="K27" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="M27" s="0" t="n">
         <v>1000001</v>
       </c>
       <c r="N27" s="0" t="inlineStr">
         <is>
-          <t>10100008&amp;10200008&amp;10300008&amp;11020014&amp;</t>
+          <t>10100012&amp;10200012&amp;10300012&amp;11000013</t>
         </is>
       </c>
       <c r="P27" s="0" t="n">
-        <v>1040010001</v>
-      </c>
-      <c r="S27" s="0" t="inlineStr">
+        <v>1031080001</v>
+      </c>
+      <c r="Q27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T27" s="0" t="inlineStr">
+        <is>
+          <t>100009,100010</t>
+        </is>
+      </c>
+      <c r="W27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="0" t="inlineStr">
+        <is>
+          <t>skill_update:100009:3&amp;skill_update:100010:10</t>
+        </is>
+      </c>
+      <c r="Z27" s="0" t="inlineStr">
+        <is>
+          <t>BOSS-神官</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="3">
+      <c r="A28" t="n">
+        <v>1031080002</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103108</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>10100012&amp;10200012&amp;10300012&amp;11000013</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1031080002</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>0.9,1.1</t>
         </is>
       </c>
-      <c r="Z27" s="0" t="inlineStr">
-        <is>
-          <t>盗贼</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="3">
-      <c r="A28" s="0" t="n">
-        <v>1041010001</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>104101</v>
-      </c>
-      <c r="C28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="0" t="n">
-        <v>500</v>
-      </c>
-      <c r="F28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="I28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="K28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="N28" s="0" t="inlineStr">
-        <is>
-          <t>10200009&amp;10300009&amp;11000012&amp;</t>
-        </is>
-      </c>
-      <c r="P28" s="0" t="n">
-        <v>1041010001</v>
-      </c>
-      <c r="S28" s="0" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T28" s="0" t="n">
-        <v>100004</v>
-      </c>
-      <c r="Z28" s="0" t="inlineStr">
-        <is>
-          <t>BOSS-大剑战士</t>
+      <c r="T28" t="n">
+        <v>100009</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>skill_update:100009:3</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>牧师</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>1041010002</v>
+        <v>1040010001</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>104101</v>
+        <v>104001</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>500</v>
-      </c>
-      <c r="F29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="0" t="n">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H29" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K29" s="0" t="n">
         <v>1</v>
@@ -2945,33 +2972,35 @@
       </c>
       <c r="N29" s="0" t="inlineStr">
         <is>
-          <t>10200009&amp;10300009&amp;11000012&amp;</t>
+          <t>10100008&amp;10200008&amp;10300008&amp;11020014&amp;</t>
         </is>
       </c>
       <c r="P29" s="0" t="n">
-        <v>1041010001</v>
-      </c>
-      <c r="S29" s="0" t="n">
-        <v>1.2</v>
+        <v>1040010001</v>
+      </c>
+      <c r="S29" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
       </c>
       <c r="Z29" s="0" t="inlineStr">
         <is>
-          <t>大剑战士</t>
+          <t>盗贼</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>1041020001</v>
+        <v>1041010001</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>104102</v>
+        <v>104101</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
@@ -2979,10 +3008,10 @@
         </is>
       </c>
       <c r="G30" s="0" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I30" s="0" t="n">
         <v>0</v>
@@ -2998,37 +3027,30 @@
       </c>
       <c r="N30" s="0" t="inlineStr">
         <is>
-          <t>10200009&amp;10300009&amp;11000015&amp;</t>
+          <t>10200009&amp;10300009&amp;11000012&amp;</t>
         </is>
       </c>
       <c r="P30" s="0" t="n">
-        <v>1041020001</v>
+        <v>1041010001</v>
       </c>
       <c r="S30" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="T30" s="0" t="inlineStr">
-        <is>
-          <t>100005</t>
-        </is>
-      </c>
-      <c r="Y30" s="0" t="inlineStr">
-        <is>
-          <t>skill_update:100005:10</t>
-        </is>
+      <c r="T30" s="0" t="n">
+        <v>100004</v>
       </c>
       <c r="Z30" s="0" t="inlineStr">
         <is>
-          <t>BOSS-大盾战士</t>
+          <t>BOSS-大剑战士</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="3">
       <c r="A31" s="0" t="n">
-        <v>1041020002</v>
+        <v>1041010002</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>104102</v>
+        <v>104101</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>1</v>
@@ -3040,10 +3062,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I31" s="0" t="n">
         <v>0</v>
@@ -3059,48 +3081,50 @@
       </c>
       <c r="N31" s="0" t="inlineStr">
         <is>
-          <t>10200009&amp;10300009&amp;11000015&amp;</t>
+          <t>10200009&amp;10300009&amp;11000012&amp;</t>
         </is>
       </c>
       <c r="P31" s="0" t="n">
-        <v>1041020001</v>
+        <v>1041010001</v>
       </c>
       <c r="S31" s="0" t="n">
         <v>1.2</v>
       </c>
       <c r="Z31" s="0" t="inlineStr">
         <is>
-          <t>大盾战士</t>
+          <t>大剑战士</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="3">
       <c r="A32" s="0" t="n">
-        <v>1041030001</v>
+        <v>1041020001</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>104103</v>
+        <v>104102</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>500</v>
-      </c>
-      <c r="F32" s="0" t="n">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G32" s="0" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="0" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K32" s="0" t="n">
         <v>1</v>
@@ -3110,460 +3134,500 @@
       </c>
       <c r="N32" s="0" t="inlineStr">
         <is>
-          <t>10200009&amp;10300009&amp;11000012&amp;</t>
+          <t>10200009&amp;10300009&amp;11000015&amp;</t>
         </is>
       </c>
       <c r="P32" s="0" t="n">
-        <v>1041030001</v>
+        <v>1041020001</v>
       </c>
       <c r="S32" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="T32" s="0" t="n">
+      <c r="T32" s="0" t="inlineStr">
+        <is>
+          <t>100005</t>
+        </is>
+      </c>
+      <c r="Y32" s="0" t="inlineStr">
+        <is>
+          <t>skill_update:100005:10</t>
+        </is>
+      </c>
+      <c r="Z32" s="0" t="inlineStr">
+        <is>
+          <t>BOSS-大盾战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="n">
+        <v>1041020002</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>104102</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N33" s="0" t="inlineStr">
+        <is>
+          <t>10200009&amp;10300009&amp;11000015&amp;</t>
+        </is>
+      </c>
+      <c r="P33" s="0" t="n">
+        <v>1041020001</v>
+      </c>
+      <c r="S33" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z33" s="0" t="inlineStr">
+        <is>
+          <t>大盾战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="n">
+        <v>1041030001</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>104103</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="K34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N34" s="0" t="inlineStr">
+        <is>
+          <t>10200009&amp;10300009&amp;11000012&amp;</t>
+        </is>
+      </c>
+      <c r="P34" s="0" t="n">
+        <v>1041030001</v>
+      </c>
+      <c r="S34" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T34" s="0" t="n">
         <v>100004</v>
       </c>
-      <c r="Z32" s="0" t="inlineStr">
+      <c r="Z34" s="0" t="inlineStr">
         <is>
           <t>BOSS-长枪骑士</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>10200016&amp;10300016&amp;</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n"/>
-      <c r="P33" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="Q33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>cn</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z33" s="2" t="inlineStr">
-        <is>
-          <t>白剑伟</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>2000000002</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>5050011&amp;5070005&amp;</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>2000000002</v>
-      </c>
-      <c r="Q34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>cn</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z34" s="2" t="inlineStr">
-        <is>
-          <t>宛家伟</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000001</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="0" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G35" s="0" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H35" s="0" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I35" s="0" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J35" s="0" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="0" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="0" t="inlineStr">
-        <is>
-          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
-        </is>
-      </c>
-      <c r="M35" s="0" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>40200006&amp;40300003&amp;41000004&amp;</t>
-        </is>
-      </c>
+          <t>10200016&amp;10300016&amp;</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000001</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
+        </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W35" s="0" t="n">
+      <c r="W35" s="2" t="n">
         <v>4</v>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>雷神天尊斩</t>
+          <t>白剑伟</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
+        <v>2000000002</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>5050011&amp;5070005&amp;</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>2000000002</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>宛家伟</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>2000000003</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="0" t="inlineStr">
+        <is>
+          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
+        </is>
+      </c>
+      <c r="M37" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>40200006&amp;40300003&amp;41000004&amp;</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>2000000003</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="W37" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>雷神天尊斩</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
         <v>2000000004</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="2" t="n">
+      <c r="C38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E36" s="0" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="0" t="inlineStr">
+      <c r="F38" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G36" s="0" t="inlineStr">
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H36" s="0" t="inlineStr">
+      <c r="H38" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I36" s="0" t="inlineStr">
+      <c r="I38" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J36" s="0" t="inlineStr">
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K36" s="0" t="inlineStr">
+      <c r="K38" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L36" s="0" t="inlineStr">
+      <c r="L38" s="0" t="inlineStr">
         <is>
           <t>1030006&amp;1040002&amp;1050012&amp;1060002&amp;</t>
         </is>
       </c>
-      <c r="M36" s="0" t="inlineStr">
+      <c r="M38" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>10300011&amp;10200011&amp;</t>
         </is>
       </c>
-      <c r="P36" s="2" t="n">
+      <c r="P38" s="2" t="n">
         <v>2000000004</v>
       </c>
-      <c r="Q36" s="2" t="n">
+      <c r="Q38" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R36" s="2" t="n"/>
-      <c r="U36" s="0" t="inlineStr">
+      <c r="R38" s="2" t="n"/>
+      <c r="U38" s="0" t="inlineStr">
         <is>
           <t>3,255,255,255,255&amp;6,178,38,38,255&amp;</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W36" s="0" t="n">
+      <c r="W38" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z38" s="2" t="inlineStr">
         <is>
           <t>卡米莉娅</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="n">
-        <v>3000010011</v>
-      </c>
-      <c r="B37" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C37" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O37" s="0" t="inlineStr">
-        <is>
-          <t>10000002,N</t>
-        </is>
-      </c>
-      <c r="P37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="n">
-        <v>3000010012</v>
-      </c>
-      <c r="B38" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C38" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O38" s="0" t="inlineStr">
-        <is>
-          <t>10000002,N,R</t>
-        </is>
-      </c>
-      <c r="P38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>3000010013</v>
+        <v>3000010011</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>1001</v>
@@ -3579,27 +3643,27 @@
       </c>
       <c r="O39" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W39" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z39" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级3</t>
+          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>3000010014</v>
+        <v>3000010012</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>1001</v>
@@ -3615,27 +3679,27 @@
       </c>
       <c r="O40" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P40" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W40" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z40" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级4</t>
+          <t>议会随机议员-生物1001-评级2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>3000010015</v>
+        <v>3000010013</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>1001</v>
@@ -3651,30 +3715,30 @@
       </c>
       <c r="O41" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W41" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z41" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级5</t>
+          <t>议会随机议员-生物1001-评级3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>3000010021</v>
+        <v>3000010014</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>3</v>
@@ -3687,30 +3751,30 @@
       </c>
       <c r="O42" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W42" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级1</t>
+          <t>议会随机议员-生物1001-评级4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>3000010022</v>
+        <v>3000010015</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>3</v>
@@ -3723,27 +3787,27 @@
       </c>
       <c r="O43" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P43" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W43" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z43" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级2</t>
+          <t>议会随机议员-生物1001-评级5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>3000010023</v>
+        <v>3000010021</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>1002</v>
@@ -3759,27 +3823,27 @@
       </c>
       <c r="O44" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P44" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W44" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z44" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级3</t>
+          <t>议会随机议员-生物1002-评级1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>3000010024</v>
+        <v>3000010022</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>1002</v>
@@ -3795,27 +3859,27 @@
       </c>
       <c r="O45" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P45" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W45" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z45" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级4</t>
+          <t>议会随机议员-生物1002-评级2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>3000010025</v>
+        <v>3000010023</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>1002</v>
@@ -3831,30 +3895,30 @@
       </c>
       <c r="O46" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P46" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W46" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z46" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级5</t>
+          <t>议会随机议员-生物1002-评级3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>3000010031</v>
+        <v>3000010024</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>3</v>
@@ -3867,30 +3931,30 @@
       </c>
       <c r="O47" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P47" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W47" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z47" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级1</t>
+          <t>议会随机议员-生物1002-评级4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>3000010032</v>
+        <v>3000010025</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>3</v>
@@ -3903,27 +3967,27 @@
       </c>
       <c r="O48" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P48" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W48" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z48" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级2</t>
+          <t>议会随机议员-生物1002-评级5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>3000010033</v>
+        <v>3000010031</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>1003</v>
@@ -3939,27 +4003,27 @@
       </c>
       <c r="O49" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P49" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W49" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级3</t>
+          <t>议会随机议员-生物1003-评级1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>3000010034</v>
+        <v>3000010032</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>1003</v>
@@ -3975,27 +4039,27 @@
       </c>
       <c r="O50" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P50" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W50" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z50" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级4</t>
+          <t>议会随机议员-生物1003-评级2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>3000010035</v>
+        <v>3000010033</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>1003</v>
@@ -4011,30 +4075,30 @@
       </c>
       <c r="O51" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P51" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W51" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z51" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级5</t>
+          <t>议会随机议员-生物1003-评级3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>3000010041</v>
+        <v>3000010034</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>3</v>
@@ -4047,30 +4111,30 @@
       </c>
       <c r="O52" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P52" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W52" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z52" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级1</t>
+          <t>议会随机议员-生物1003-评级4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>3000010042</v>
+        <v>3000010035</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>3</v>
@@ -4083,27 +4147,27 @@
       </c>
       <c r="O53" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z53" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级2</t>
+          <t>议会随机议员-生物1003-评级5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>3000010043</v>
+        <v>3000010041</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>1004</v>
@@ -4119,27 +4183,27 @@
       </c>
       <c r="O54" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P54" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z54" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级3</t>
+          <t>议会随机议员-生物1004-评级1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>3000010044</v>
+        <v>3000010042</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>1004</v>
@@ -4155,27 +4219,27 @@
       </c>
       <c r="O55" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P55" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z55" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级4</t>
+          <t>议会随机议员-生物1004-评级2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>3000010045</v>
+        <v>3000010043</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>1004</v>
@@ -4191,30 +4255,30 @@
       </c>
       <c r="O56" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P56" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W56" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z56" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级5</t>
+          <t>议会随机议员-生物1004-评级3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>3000020011</v>
+        <v>3000010044</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>3</v>
@@ -4227,30 +4291,30 @@
       </c>
       <c r="O57" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P57" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z57" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级1</t>
+          <t>议会随机议员-生物1004-评级4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>3000020012</v>
+        <v>3000010045</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>3</v>
@@ -4263,27 +4327,27 @@
       </c>
       <c r="O58" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P58" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W58" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z58" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级2</t>
+          <t>议会随机议员-生物1004-评级5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>3000020013</v>
+        <v>3000020011</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>2001</v>
@@ -4299,27 +4363,27 @@
       </c>
       <c r="O59" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P59" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W59" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z59" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级3</t>
+          <t>议会随机议员-生物2001-评级1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>3000020014</v>
+        <v>3000020012</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>2001</v>
@@ -4335,27 +4399,27 @@
       </c>
       <c r="O60" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P60" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W60" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z60" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级4</t>
+          <t>议会随机议员-生物2001-评级2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3000020015</v>
+        <v>3000020013</v>
       </c>
       <c r="B61" s="0" t="n">
         <v>2001</v>
@@ -4371,30 +4435,30 @@
       </c>
       <c r="O61" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P61" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W61" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z61" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级5</t>
+          <t>议会随机议员-生物2001-评级3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3000020021</v>
+        <v>3000020014</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C62" s="0" t="n">
         <v>3</v>
@@ -4407,30 +4471,30 @@
       </c>
       <c r="O62" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P62" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W62" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z62" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级1</t>
+          <t>议会随机议员-生物2001-评级4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>3000020022</v>
+        <v>3000020015</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>3</v>
@@ -4443,27 +4507,27 @@
       </c>
       <c r="O63" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P63" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z63" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级2</t>
+          <t>议会随机议员-生物2001-评级5</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="3">
       <c r="A64" s="0" t="n">
-        <v>3000020023</v>
+        <v>3000020021</v>
       </c>
       <c r="B64" s="0" t="n">
         <v>2002</v>
@@ -4479,27 +4543,27 @@
       </c>
       <c r="O64" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P64" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W64" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z64" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级3</t>
+          <t>议会随机议员-生物2002-评级1</t>
         </is>
       </c>
     </row>
     <row r="65" ht="12" customHeight="1" s="3">
       <c r="A65" s="0" t="n">
-        <v>3000020024</v>
+        <v>3000020022</v>
       </c>
       <c r="B65" s="0" t="n">
         <v>2002</v>
@@ -4515,27 +4579,27 @@
       </c>
       <c r="O65" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P65" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z65" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级4</t>
+          <t>议会随机议员-生物2002-评级2</t>
         </is>
       </c>
     </row>
     <row r="66" ht="12" customHeight="1" s="3">
       <c r="A66" s="0" t="n">
-        <v>3000020025</v>
+        <v>3000020023</v>
       </c>
       <c r="B66" s="0" t="n">
         <v>2002</v>
@@ -4551,30 +4615,30 @@
       </c>
       <c r="O66" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P66" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z66" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级5</t>
+          <t>议会随机议员-生物2002-评级3</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="3">
       <c r="A67" s="0" t="n">
-        <v>3000020031</v>
+        <v>3000020024</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>3</v>
@@ -4587,30 +4651,30 @@
       </c>
       <c r="O67" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P67" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z67" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级1</t>
+          <t>议会随机议员-生物2002-评级4</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="3">
       <c r="A68" s="0" t="n">
-        <v>3000020032</v>
+        <v>3000020025</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>3</v>
@@ -4623,27 +4687,27 @@
       </c>
       <c r="O68" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P68" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z68" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级2</t>
+          <t>议会随机议员-生物2002-评级5</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>3000020033</v>
+        <v>3000020031</v>
       </c>
       <c r="B69" s="0" t="n">
         <v>2003</v>
@@ -4659,27 +4723,27 @@
       </c>
       <c r="O69" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P69" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z69" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级3</t>
+          <t>议会随机议员-生物2003-评级1</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>3000020034</v>
+        <v>3000020032</v>
       </c>
       <c r="B70" s="0" t="n">
         <v>2003</v>
@@ -4695,27 +4759,27 @@
       </c>
       <c r="O70" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P70" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z70" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级4</t>
+          <t>议会随机议员-生物2003-评级2</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>3000020035</v>
+        <v>3000020033</v>
       </c>
       <c r="B71" s="0" t="n">
         <v>2003</v>
@@ -4731,30 +4795,30 @@
       </c>
       <c r="O71" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P71" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z71" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级5</t>
+          <t>议会随机议员-生物2003-评级3</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="3">
       <c r="A72" s="0" t="n">
-        <v>3000020041</v>
+        <v>3000020034</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>3</v>
@@ -4767,30 +4831,30 @@
       </c>
       <c r="O72" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P72" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z72" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级1</t>
+          <t>议会随机议员-生物2003-评级4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>3000020042</v>
+        <v>3000020035</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>3</v>
@@ -4803,27 +4867,27 @@
       </c>
       <c r="O73" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P73" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z73" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级2</t>
+          <t>议会随机议员-生物2003-评级5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>3000020043</v>
+        <v>3000020041</v>
       </c>
       <c r="B74" s="0" t="n">
         <v>2004</v>
@@ -4839,27 +4903,27 @@
       </c>
       <c r="O74" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P74" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z74" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级3</t>
+          <t>议会随机议员-生物2004-评级1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>3000020044</v>
+        <v>3000020042</v>
       </c>
       <c r="B75" s="0" t="n">
         <v>2004</v>
@@ -4875,27 +4939,27 @@
       </c>
       <c r="O75" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P75" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z75" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级4</t>
+          <t>议会随机议员-生物2004-评级2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>3000020045</v>
+        <v>3000020043</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>2004</v>
@@ -4911,30 +4975,30 @@
       </c>
       <c r="O76" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P76" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z76" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级5</t>
+          <t>议会随机议员-生物2004-评级3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>3000030011</v>
+        <v>3000020044</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>3</v>
@@ -4947,30 +5011,30 @@
       </c>
       <c r="O77" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P77" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z77" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级1</t>
+          <t>议会随机议员-生物2004-评级4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>3000030012</v>
+        <v>3000020045</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>3</v>
@@ -4983,27 +5047,27 @@
       </c>
       <c r="O78" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P78" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z78" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级2</t>
+          <t>议会随机议员-生物2004-评级5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>3000030013</v>
+        <v>3000030011</v>
       </c>
       <c r="B79" s="0" t="n">
         <v>3001</v>
@@ -5019,27 +5083,27 @@
       </c>
       <c r="O79" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P79" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z79" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级3</t>
+          <t>议会随机议员-生物3001-评级1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>3000030014</v>
+        <v>3000030012</v>
       </c>
       <c r="B80" s="0" t="n">
         <v>3001</v>
@@ -5055,27 +5119,27 @@
       </c>
       <c r="O80" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P80" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z80" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级4</t>
+          <t>议会随机议员-生物3001-评级2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>3000030015</v>
+        <v>3000030013</v>
       </c>
       <c r="B81" s="0" t="n">
         <v>3001</v>
@@ -5091,30 +5155,30 @@
       </c>
       <c r="O81" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P81" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q81" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z81" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级5</t>
+          <t>议会随机议员-生物3001-评级3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>3000030021</v>
+        <v>3000030014</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>3</v>
@@ -5127,30 +5191,30 @@
       </c>
       <c r="O82" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P82" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z82" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级1</t>
+          <t>议会随机议员-生物3001-评级4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>3000030022</v>
+        <v>3000030015</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>3</v>
@@ -5163,27 +5227,27 @@
       </c>
       <c r="O83" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P83" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z83" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级2</t>
+          <t>议会随机议员-生物3001-评级5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>3000030023</v>
+        <v>3000030021</v>
       </c>
       <c r="B84" s="0" t="n">
         <v>3002</v>
@@ -5199,27 +5263,27 @@
       </c>
       <c r="O84" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P84" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q84" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W84" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z84" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级3</t>
+          <t>议会随机议员-生物3002-评级1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>3000030024</v>
+        <v>3000030022</v>
       </c>
       <c r="B85" s="0" t="n">
         <v>3002</v>
@@ -5235,27 +5299,27 @@
       </c>
       <c r="O85" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P85" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q85" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z85" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级4</t>
+          <t>议会随机议员-生物3002-评级2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>3000030025</v>
+        <v>3000030023</v>
       </c>
       <c r="B86" s="0" t="n">
         <v>3002</v>
@@ -5271,30 +5335,30 @@
       </c>
       <c r="O86" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P86" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W86" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z86" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级5</t>
+          <t>议会随机议员-生物3002-评级3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>3000030031</v>
+        <v>3000030024</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>3</v>
@@ -5307,30 +5371,30 @@
       </c>
       <c r="O87" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P87" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z87" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级1</t>
+          <t>议会随机议员-生物3002-评级4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>3000030032</v>
+        <v>3000030025</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>3</v>
@@ -5343,27 +5407,27 @@
       </c>
       <c r="O88" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P88" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q88" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z88" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级2</t>
+          <t>议会随机议员-生物3002-评级5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>3000030033</v>
+        <v>3000030031</v>
       </c>
       <c r="B89" s="0" t="n">
         <v>3003</v>
@@ -5379,27 +5443,27 @@
       </c>
       <c r="O89" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P89" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q89" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W89" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z89" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级3</t>
+          <t>议会随机议员-生物3003-评级1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>3000030034</v>
+        <v>3000030032</v>
       </c>
       <c r="B90" s="0" t="n">
         <v>3003</v>
@@ -5415,27 +5479,27 @@
       </c>
       <c r="O90" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P90" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z90" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级4</t>
+          <t>议会随机议员-生物3003-评级2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>3000030035</v>
+        <v>3000030033</v>
       </c>
       <c r="B91" s="0" t="n">
         <v>3003</v>
@@ -5451,30 +5515,30 @@
       </c>
       <c r="O91" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P91" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q91" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W91" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z91" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级5</t>
+          <t>议会随机议员-生物3003-评级3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>3000030041</v>
+        <v>3000030034</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>3</v>
@@ -5487,30 +5551,30 @@
       </c>
       <c r="O92" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P92" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q92" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z92" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级1</t>
+          <t>议会随机议员-生物3003-评级4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>3000030042</v>
+        <v>3000030035</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>3</v>
@@ -5523,27 +5587,27 @@
       </c>
       <c r="O93" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P93" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q93" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z93" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级2</t>
+          <t>议会随机议员-生物3003-评级5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>3000030043</v>
+        <v>3000030041</v>
       </c>
       <c r="B94" s="0" t="n">
         <v>3004</v>
@@ -5559,27 +5623,27 @@
       </c>
       <c r="O94" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P94" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W94" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z94" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级3</t>
+          <t>议会随机议员-生物3004-评级1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>3000030044</v>
+        <v>3000030042</v>
       </c>
       <c r="B95" s="0" t="n">
         <v>3004</v>
@@ -5595,27 +5659,27 @@
       </c>
       <c r="O95" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P95" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q95" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W95" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z95" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级4</t>
+          <t>议会随机议员-生物3004-评级2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>3000030045</v>
+        <v>3000030043</v>
       </c>
       <c r="B96" s="0" t="n">
         <v>3004</v>
@@ -5631,30 +5695,30 @@
       </c>
       <c r="O96" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P96" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q96" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W96" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z96" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级5</t>
+          <t>议会随机议员-生物3004-评级3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>3000040011</v>
+        <v>3000030044</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>3</v>
@@ -5667,30 +5731,30 @@
       </c>
       <c r="O97" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P97" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q97" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W97" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z97" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级1</t>
+          <t>议会随机议员-生物3004-评级4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>3000040012</v>
+        <v>3000030045</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>3</v>
@@ -5703,27 +5767,27 @@
       </c>
       <c r="O98" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P98" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q98" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W98" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z98" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级2</t>
+          <t>议会随机议员-生物3004-评级5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>3000040013</v>
+        <v>3000040011</v>
       </c>
       <c r="B99" s="0" t="n">
         <v>4001</v>
@@ -5739,27 +5803,27 @@
       </c>
       <c r="O99" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P99" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q99" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W99" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z99" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级3</t>
+          <t>议会随机议员-生物4001-评级1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>3000040014</v>
+        <v>3000040012</v>
       </c>
       <c r="B100" s="0" t="n">
         <v>4001</v>
@@ -5775,27 +5839,27 @@
       </c>
       <c r="O100" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P100" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q100" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W100" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z100" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级4</t>
+          <t>议会随机议员-生物4001-评级2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>3000040015</v>
+        <v>3000040013</v>
       </c>
       <c r="B101" s="0" t="n">
         <v>4001</v>
@@ -5811,30 +5875,30 @@
       </c>
       <c r="O101" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P101" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q101" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W101" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z101" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级5</t>
+          <t>议会随机议员-生物4001-评级3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>3000040021</v>
+        <v>3000040014</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>3</v>
@@ -5847,30 +5911,30 @@
       </c>
       <c r="O102" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P102" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q102" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z102" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级1</t>
+          <t>议会随机议员-生物4001-评级4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>3000040022</v>
+        <v>3000040015</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>3</v>
@@ -5883,27 +5947,27 @@
       </c>
       <c r="O103" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P103" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q103" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z103" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级2</t>
+          <t>议会随机议员-生物4001-评级5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>3000040023</v>
+        <v>3000040021</v>
       </c>
       <c r="B104" s="0" t="n">
         <v>4002</v>
@@ -5919,27 +5983,27 @@
       </c>
       <c r="O104" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P104" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q104" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W104" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z104" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级3</t>
+          <t>议会随机议员-生物4002-评级1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>3000040024</v>
+        <v>3000040022</v>
       </c>
       <c r="B105" s="0" t="n">
         <v>4002</v>
@@ -5955,27 +6019,27 @@
       </c>
       <c r="O105" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P105" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q105" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z105" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级4</t>
+          <t>议会随机议员-生物4002-评级2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>3000040025</v>
+        <v>3000040023</v>
       </c>
       <c r="B106" s="0" t="n">
         <v>4002</v>
@@ -5991,30 +6055,30 @@
       </c>
       <c r="O106" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P106" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q106" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W106" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z106" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级5</t>
+          <t>议会随机议员-生物4002-评级3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>3000040031</v>
+        <v>3000040024</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>3</v>
@@ -6027,30 +6091,30 @@
       </c>
       <c r="O107" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P107" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q107" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z107" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级1</t>
+          <t>议会随机议员-生物4002-评级4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>3000040032</v>
+        <v>3000040025</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>3</v>
@@ -6063,27 +6127,27 @@
       </c>
       <c r="O108" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P108" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z108" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级2</t>
+          <t>议会随机议员-生物4002-评级5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>3000040033</v>
+        <v>3000040031</v>
       </c>
       <c r="B109" s="0" t="n">
         <v>4003</v>
@@ -6099,27 +6163,27 @@
       </c>
       <c r="O109" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P109" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q109" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W109" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z109" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级3</t>
+          <t>议会随机议员-生物4003-评级1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>3000040034</v>
+        <v>3000040032</v>
       </c>
       <c r="B110" s="0" t="n">
         <v>4003</v>
@@ -6135,27 +6199,27 @@
       </c>
       <c r="O110" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P110" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q110" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W110" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z110" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级4</t>
+          <t>议会随机议员-生物4003-评级2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>3000040035</v>
+        <v>3000040033</v>
       </c>
       <c r="B111" s="0" t="n">
         <v>4003</v>
@@ -6171,30 +6235,30 @@
       </c>
       <c r="O111" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P111" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q111" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W111" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z111" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级5</t>
+          <t>议会随机议员-生物4003-评级3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>3000040041</v>
+        <v>3000040034</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>3</v>
@@ -6207,30 +6271,30 @@
       </c>
       <c r="O112" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P112" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W112" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z112" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级1</t>
+          <t>议会随机议员-生物4003-评级4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>3000040042</v>
+        <v>3000040035</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>3</v>
@@ -6243,27 +6307,27 @@
       </c>
       <c r="O113" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P113" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q113" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z113" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级2</t>
+          <t>议会随机议员-生物4003-评级5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>3000040043</v>
+        <v>3000040041</v>
       </c>
       <c r="B114" s="0" t="n">
         <v>4004</v>
@@ -6279,27 +6343,27 @@
       </c>
       <c r="O114" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P114" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q114" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W114" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z114" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级3</t>
+          <t>议会随机议员-生物4004-评级1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>3000040044</v>
+        <v>3000040042</v>
       </c>
       <c r="B115" s="0" t="n">
         <v>4004</v>
@@ -6315,27 +6379,27 @@
       </c>
       <c r="O115" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P115" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W115" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z115" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级4</t>
+          <t>议会随机议员-生物4004-评级2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>3000040045</v>
+        <v>3000040043</v>
       </c>
       <c r="B116" s="0" t="n">
         <v>4004</v>
@@ -6351,30 +6415,30 @@
       </c>
       <c r="O116" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P116" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q116" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W116" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z116" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级5</t>
+          <t>议会随机议员-生物4004-评级3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>3000040051</v>
+        <v>3000040044</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>3</v>
@@ -6387,30 +6451,30 @@
       </c>
       <c r="O117" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P117" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q117" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W117" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z117" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级1</t>
+          <t>议会随机议员-生物4004-评级4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>3000040052</v>
+        <v>3000040045</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>3</v>
@@ -6423,27 +6487,27 @@
       </c>
       <c r="O118" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P118" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q118" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z118" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级2</t>
+          <t>议会随机议员-生物4004-评级5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>3000040053</v>
+        <v>3000040051</v>
       </c>
       <c r="B119" s="0" t="n">
         <v>4005</v>
@@ -6459,27 +6523,27 @@
       </c>
       <c r="O119" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P119" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q119" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W119" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z119" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级3</t>
+          <t>议会随机议员-生物4005-评级1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>3000040054</v>
+        <v>3000040052</v>
       </c>
       <c r="B120" s="0" t="n">
         <v>4005</v>
@@ -6495,27 +6559,27 @@
       </c>
       <c r="O120" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P120" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q120" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W120" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z120" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级4</t>
+          <t>议会随机议员-生物4005-评级2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>3000040055</v>
+        <v>3000040053</v>
       </c>
       <c r="B121" s="0" t="n">
         <v>4005</v>
@@ -6531,30 +6595,30 @@
       </c>
       <c r="O121" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P121" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W121" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z121" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级5</t>
+          <t>议会随机议员-生物4005-评级3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>3000050011</v>
+        <v>3000040054</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>3</v>
@@ -6567,30 +6631,30 @@
       </c>
       <c r="O122" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P122" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q122" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W122" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z122" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级1</t>
+          <t>议会随机议员-生物4005-评级4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>3000050012</v>
+        <v>3000040055</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>3</v>
@@ -6603,27 +6667,27 @@
       </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P123" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q123" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z123" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级2</t>
+          <t>议会随机议员-生物4005-评级5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>3000050013</v>
+        <v>3000050011</v>
       </c>
       <c r="B124" s="0" t="n">
         <v>5001</v>
@@ -6639,27 +6703,27 @@
       </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P124" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q124" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W124" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z124" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级3</t>
+          <t>议会随机议员-生物5001-评级1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>3000050014</v>
+        <v>3000050012</v>
       </c>
       <c r="B125" s="0" t="n">
         <v>5001</v>
@@ -6675,27 +6739,27 @@
       </c>
       <c r="O125" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P125" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q125" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z125" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级4</t>
+          <t>议会随机议员-生物5001-评级2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>3000050015</v>
+        <v>3000050013</v>
       </c>
       <c r="B126" s="0" t="n">
         <v>5001</v>
@@ -6711,30 +6775,30 @@
       </c>
       <c r="O126" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P126" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q126" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W126" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z126" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级5</t>
+          <t>议会随机议员-生物5001-评级3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>3000050021</v>
+        <v>3000050014</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>3</v>
@@ -6747,30 +6811,30 @@
       </c>
       <c r="O127" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P127" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q127" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W127" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z127" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级1</t>
+          <t>议会随机议员-生物5001-评级4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>3000050022</v>
+        <v>3000050015</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>3</v>
@@ -6783,27 +6847,27 @@
       </c>
       <c r="O128" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P128" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q128" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z128" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级2</t>
+          <t>议会随机议员-生物5001-评级5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000050023</v>
+        <v>3000050021</v>
       </c>
       <c r="B129" s="0" t="n">
         <v>5002</v>
@@ -6819,27 +6883,27 @@
       </c>
       <c r="O129" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P129" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q129" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W129" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z129" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级3</t>
+          <t>议会随机议员-生物5002-评级1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000050024</v>
+        <v>3000050022</v>
       </c>
       <c r="B130" s="0" t="n">
         <v>5002</v>
@@ -6855,27 +6919,27 @@
       </c>
       <c r="O130" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P130" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q130" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W130" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z130" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级4</t>
+          <t>议会随机议员-生物5002-评级2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000050025</v>
+        <v>3000050023</v>
       </c>
       <c r="B131" s="0" t="n">
         <v>5002</v>
@@ -6891,30 +6955,30 @@
       </c>
       <c r="O131" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P131" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q131" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W131" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z131" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级5</t>
+          <t>议会随机议员-生物5002-评级3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000050031</v>
+        <v>3000050024</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C132" s="0" t="n">
         <v>3</v>
@@ -6927,30 +6991,30 @@
       </c>
       <c r="O132" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P132" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q132" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W132" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z132" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级1</t>
+          <t>议会随机议员-生物5002-评级4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000050032</v>
+        <v>3000050025</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>3</v>
@@ -6963,27 +7027,27 @@
       </c>
       <c r="O133" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P133" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q133" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W133" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z133" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级2</t>
+          <t>议会随机议员-生物5002-评级5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000050033</v>
+        <v>3000050031</v>
       </c>
       <c r="B134" s="0" t="n">
         <v>5003</v>
@@ -6999,27 +7063,27 @@
       </c>
       <c r="O134" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P134" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q134" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W134" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z134" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级3</t>
+          <t>议会随机议员-生物5003-评级1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000050034</v>
+        <v>3000050032</v>
       </c>
       <c r="B135" s="0" t="n">
         <v>5003</v>
@@ -7035,27 +7099,27 @@
       </c>
       <c r="O135" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P135" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q135" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W135" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z135" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级4</t>
+          <t>议会随机议员-生物5003-评级2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000050035</v>
+        <v>3000050033</v>
       </c>
       <c r="B136" s="0" t="n">
         <v>5003</v>
@@ -7071,30 +7135,30 @@
       </c>
       <c r="O136" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P136" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q136" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W136" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z136" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级5</t>
+          <t>议会随机议员-生物5003-评级3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000050041</v>
+        <v>3000050034</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C137" s="0" t="n">
         <v>3</v>
@@ -7107,30 +7171,30 @@
       </c>
       <c r="O137" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P137" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q137" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W137" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z137" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级1</t>
+          <t>议会随机议员-生物5003-评级4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000050042</v>
+        <v>3000050035</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C138" s="0" t="n">
         <v>3</v>
@@ -7143,27 +7207,27 @@
       </c>
       <c r="O138" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P138" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q138" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W138" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z138" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级2</t>
+          <t>议会随机议员-生物5003-评级5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>3000050043</v>
+        <v>3000050041</v>
       </c>
       <c r="B139" s="0" t="n">
         <v>5004</v>
@@ -7179,27 +7243,27 @@
       </c>
       <c r="O139" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P139" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q139" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W139" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z139" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级3</t>
+          <t>议会随机议员-生物5004-评级1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>3000050044</v>
+        <v>3000050042</v>
       </c>
       <c r="B140" s="0" t="n">
         <v>5004</v>
@@ -7215,27 +7279,27 @@
       </c>
       <c r="O140" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P140" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q140" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W140" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z140" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级4</t>
+          <t>议会随机议员-生物5004-评级2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>3000050045</v>
+        <v>3000050043</v>
       </c>
       <c r="B141" s="0" t="n">
         <v>5004</v>
@@ -7251,30 +7315,30 @@
       </c>
       <c r="O141" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P141" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q141" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W141" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z141" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级5</t>
+          <t>议会随机议员-生物5004-评级3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>3000060011</v>
+        <v>3000050044</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C142" s="0" t="n">
         <v>3</v>
@@ -7287,30 +7351,30 @@
       </c>
       <c r="O142" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P142" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q142" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W142" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z142" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级1</t>
+          <t>议会随机议员-生物5004-评级4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>3000060012</v>
+        <v>3000050045</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>3</v>
@@ -7323,27 +7387,27 @@
       </c>
       <c r="O143" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P143" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q143" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W143" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z143" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级2</t>
+          <t>议会随机议员-生物5004-评级5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>3000060013</v>
+        <v>3000060011</v>
       </c>
       <c r="B144" s="0" t="n">
         <v>6001</v>
@@ -7359,27 +7423,27 @@
       </c>
       <c r="O144" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P144" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q144" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W144" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z144" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级3</t>
+          <t>议会随机议员-生物6001-评级1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>3000060014</v>
+        <v>3000060012</v>
       </c>
       <c r="B145" s="0" t="n">
         <v>6001</v>
@@ -7395,27 +7459,27 @@
       </c>
       <c r="O145" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P145" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q145" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W145" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z145" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级4</t>
+          <t>议会随机议员-生物6001-评级2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>3000060015</v>
+        <v>3000060013</v>
       </c>
       <c r="B146" s="0" t="n">
         <v>6001</v>
@@ -7431,30 +7495,30 @@
       </c>
       <c r="O146" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P146" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q146" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W146" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z146" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级5</t>
+          <t>议会随机议员-生物6001-评级3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>3000060021</v>
+        <v>3000060014</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C147" s="0" t="n">
         <v>3</v>
@@ -7467,30 +7531,30 @@
       </c>
       <c r="O147" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P147" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q147" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W147" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z147" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级1</t>
+          <t>议会随机议员-生物6001-评级4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>3000060022</v>
+        <v>3000060015</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C148" s="0" t="n">
         <v>3</v>
@@ -7503,27 +7567,27 @@
       </c>
       <c r="O148" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P148" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q148" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W148" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z148" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级2</t>
+          <t>议会随机议员-生物6001-评级5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>3000060023</v>
+        <v>3000060021</v>
       </c>
       <c r="B149" s="0" t="n">
         <v>6002</v>
@@ -7539,27 +7603,27 @@
       </c>
       <c r="O149" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P149" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q149" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W149" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z149" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级3</t>
+          <t>议会随机议员-生物6002-评级1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>3000060024</v>
+        <v>3000060022</v>
       </c>
       <c r="B150" s="0" t="n">
         <v>6002</v>
@@ -7575,27 +7639,27 @@
       </c>
       <c r="O150" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P150" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q150" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W150" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z150" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级4</t>
+          <t>议会随机议员-生物6002-评级2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>3000060025</v>
+        <v>3000060023</v>
       </c>
       <c r="B151" s="0" t="n">
         <v>6002</v>
@@ -7611,30 +7675,30 @@
       </c>
       <c r="O151" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P151" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q151" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W151" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z151" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级5</t>
+          <t>议会随机议员-生物6002-评级3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>3000060031</v>
+        <v>3000060024</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C152" s="0" t="n">
         <v>3</v>
@@ -7647,30 +7711,30 @@
       </c>
       <c r="O152" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P152" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q152" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W152" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z152" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级1</t>
+          <t>议会随机议员-生物6002-评级4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>3000060032</v>
+        <v>3000060025</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C153" s="0" t="n">
         <v>3</v>
@@ -7683,27 +7747,27 @@
       </c>
       <c r="O153" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P153" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q153" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W153" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z153" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级2</t>
+          <t>议会随机议员-生物6002-评级5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>3000060033</v>
+        <v>3000060031</v>
       </c>
       <c r="B154" s="0" t="n">
         <v>6003</v>
@@ -7719,27 +7783,27 @@
       </c>
       <c r="O154" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P154" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q154" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W154" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z154" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级3</t>
+          <t>议会随机议员-生物6003-评级1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>3000060034</v>
+        <v>3000060032</v>
       </c>
       <c r="B155" s="0" t="n">
         <v>6003</v>
@@ -7755,27 +7819,27 @@
       </c>
       <c r="O155" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P155" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q155" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W155" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z155" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级4</t>
+          <t>议会随机议员-生物6003-评级2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>3000060035</v>
+        <v>3000060033</v>
       </c>
       <c r="B156" s="0" t="n">
         <v>6003</v>
@@ -7791,30 +7855,30 @@
       </c>
       <c r="O156" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P156" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q156" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W156" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z156" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级5</t>
+          <t>议会随机议员-生物6003-评级3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>3000060041</v>
+        <v>3000060034</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C157" s="0" t="n">
         <v>3</v>
@@ -7827,30 +7891,30 @@
       </c>
       <c r="O157" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P157" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q157" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W157" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z157" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级1</t>
+          <t>议会随机议员-生物6003-评级4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>3000060042</v>
+        <v>3000060035</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C158" s="0" t="n">
         <v>3</v>
@@ -7863,27 +7927,27 @@
       </c>
       <c r="O158" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P158" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q158" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W158" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z158" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级2</t>
+          <t>议会随机议员-生物6003-评级5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>3000060043</v>
+        <v>3000060041</v>
       </c>
       <c r="B159" s="0" t="n">
         <v>6004</v>
@@ -7899,27 +7963,27 @@
       </c>
       <c r="O159" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P159" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q159" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W159" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z159" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级3</t>
+          <t>议会随机议员-生物6004-评级1</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>3000060044</v>
+        <v>3000060042</v>
       </c>
       <c r="B160" s="0" t="n">
         <v>6004</v>
@@ -7935,27 +7999,27 @@
       </c>
       <c r="O160" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P160" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q160" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W160" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z160" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级4</t>
+          <t>议会随机议员-生物6004-评级2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>3000060045</v>
+        <v>3000060043</v>
       </c>
       <c r="B161" s="0" t="n">
         <v>6004</v>
@@ -7971,30 +8035,30 @@
       </c>
       <c r="O161" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P161" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q161" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W161" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z161" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级5</t>
+          <t>议会随机议员-生物6004-评级3</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>3000060051</v>
+        <v>3000060044</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C162" s="0" t="n">
         <v>3</v>
@@ -8007,30 +8071,30 @@
       </c>
       <c r="O162" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P162" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q162" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W162" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z162" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级1</t>
+          <t>议会随机议员-生物6004-评级4</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>3000060052</v>
+        <v>3000060045</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C163" s="0" t="n">
         <v>3</v>
@@ -8043,27 +8107,27 @@
       </c>
       <c r="O163" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P163" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q163" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W163" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z163" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级2</t>
+          <t>议会随机议员-生物6004-评级5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000060053</v>
+        <v>3000060051</v>
       </c>
       <c r="B164" s="0" t="n">
         <v>6005</v>
@@ -8079,27 +8143,27 @@
       </c>
       <c r="O164" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P164" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q164" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W164" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z164" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级3</t>
+          <t>议会随机议员-生物6005-评级1</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000060054</v>
+        <v>3000060052</v>
       </c>
       <c r="B165" s="0" t="n">
         <v>6005</v>
@@ -8115,27 +8179,27 @@
       </c>
       <c r="O165" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P165" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q165" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W165" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z165" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级4</t>
+          <t>议会随机议员-生物6005-评级2</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000060055</v>
+        <v>3000060053</v>
       </c>
       <c r="B166" s="0" t="n">
         <v>6005</v>
@@ -8151,30 +8215,30 @@
       </c>
       <c r="O166" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P166" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q166" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W166" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z166" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级5</t>
+          <t>议会随机议员-生物6005-评级3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000070011</v>
+        <v>3000060054</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C167" s="0" t="n">
         <v>3</v>
@@ -8187,30 +8251,30 @@
       </c>
       <c r="O167" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P167" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q167" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W167" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z167" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级1</t>
+          <t>议会随机议员-生物6005-评级4</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000070012</v>
+        <v>3000060055</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C168" s="0" t="n">
         <v>3</v>
@@ -8223,27 +8287,27 @@
       </c>
       <c r="O168" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P168" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q168" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W168" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z168" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级2</t>
+          <t>议会随机议员-生物6005-评级5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000070013</v>
+        <v>3000070011</v>
       </c>
       <c r="B169" s="0" t="n">
         <v>7001</v>
@@ -8259,27 +8323,27 @@
       </c>
       <c r="O169" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P169" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q169" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W169" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z169" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级3</t>
+          <t>议会随机议员-生物7001-评级1</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>3000070014</v>
+        <v>3000070012</v>
       </c>
       <c r="B170" s="0" t="n">
         <v>7001</v>
@@ -8295,27 +8359,27 @@
       </c>
       <c r="O170" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P170" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q170" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W170" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z170" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级4</t>
+          <t>议会随机议员-生物7001-评级2</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000070015</v>
+        <v>3000070013</v>
       </c>
       <c r="B171" s="0" t="n">
         <v>7001</v>
@@ -8331,30 +8395,30 @@
       </c>
       <c r="O171" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P171" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q171" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W171" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z171" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级5</t>
+          <t>议会随机议员-生物7001-评级3</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>3000070021</v>
+        <v>3000070014</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C172" s="0" t="n">
         <v>3</v>
@@ -8367,30 +8431,30 @@
       </c>
       <c r="O172" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P172" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q172" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W172" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z172" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级1</t>
+          <t>议会随机议员-生物7001-评级4</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>3000070022</v>
+        <v>3000070015</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C173" s="0" t="n">
         <v>3</v>
@@ -8403,27 +8467,27 @@
       </c>
       <c r="O173" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P173" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q173" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W173" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z173" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级2</t>
+          <t>议会随机议员-生物7001-评级5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>3000070023</v>
+        <v>3000070021</v>
       </c>
       <c r="B174" s="0" t="n">
         <v>7002</v>
@@ -8439,27 +8503,27 @@
       </c>
       <c r="O174" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P174" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q174" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W174" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z174" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级3</t>
+          <t>议会随机议员-生物7002-评级1</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>3000070024</v>
+        <v>3000070022</v>
       </c>
       <c r="B175" s="0" t="n">
         <v>7002</v>
@@ -8475,27 +8539,27 @@
       </c>
       <c r="O175" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P175" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q175" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W175" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z175" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级4</t>
+          <t>议会随机议员-生物7002-评级2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>3000070025</v>
+        <v>3000070023</v>
       </c>
       <c r="B176" s="0" t="n">
         <v>7002</v>
@@ -8511,30 +8575,30 @@
       </c>
       <c r="O176" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P176" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q176" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W176" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z176" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级5</t>
+          <t>议会随机议员-生物7002-评级3</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>3000070031</v>
+        <v>3000070024</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C177" s="0" t="n">
         <v>3</v>
@@ -8547,30 +8611,30 @@
       </c>
       <c r="O177" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P177" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q177" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W177" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z177" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级1</t>
+          <t>议会随机议员-生物7002-评级4</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>3000070032</v>
+        <v>3000070025</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C178" s="0" t="n">
         <v>3</v>
@@ -8583,27 +8647,27 @@
       </c>
       <c r="O178" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P178" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q178" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W178" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z178" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级2</t>
+          <t>议会随机议员-生物7002-评级5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>3000070033</v>
+        <v>3000070031</v>
       </c>
       <c r="B179" s="0" t="n">
         <v>7003</v>
@@ -8619,27 +8683,27 @@
       </c>
       <c r="O179" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P179" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q179" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W179" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z179" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级3</t>
+          <t>议会随机议员-生物7003-评级1</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>3000070034</v>
+        <v>3000070032</v>
       </c>
       <c r="B180" s="0" t="n">
         <v>7003</v>
@@ -8655,27 +8719,27 @@
       </c>
       <c r="O180" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P180" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q180" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W180" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z180" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级4</t>
+          <t>议会随机议员-生物7003-评级2</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>3000070035</v>
+        <v>3000070033</v>
       </c>
       <c r="B181" s="0" t="n">
         <v>7003</v>
@@ -8691,30 +8755,30 @@
       </c>
       <c r="O181" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P181" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q181" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W181" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z181" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级5</t>
+          <t>议会随机议员-生物7003-评级3</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>3000070041</v>
+        <v>3000070034</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C182" s="0" t="n">
         <v>3</v>
@@ -8727,30 +8791,30 @@
       </c>
       <c r="O182" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P182" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q182" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W182" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z182" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级1</t>
+          <t>议会随机议员-生物7003-评级4</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>3000070042</v>
+        <v>3000070035</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C183" s="0" t="n">
         <v>3</v>
@@ -8763,27 +8827,27 @@
       </c>
       <c r="O183" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P183" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q183" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W183" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z183" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级2</t>
+          <t>议会随机议员-生物7003-评级5</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>3000070043</v>
+        <v>3000070041</v>
       </c>
       <c r="B184" s="0" t="n">
         <v>7004</v>
@@ -8799,27 +8863,27 @@
       </c>
       <c r="O184" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P184" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q184" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W184" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z184" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级3</t>
+          <t>议会随机议员-生物7004-评级1</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>3000070044</v>
+        <v>3000070042</v>
       </c>
       <c r="B185" s="0" t="n">
         <v>7004</v>
@@ -8835,27 +8899,27 @@
       </c>
       <c r="O185" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P185" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q185" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W185" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z185" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级4</t>
+          <t>议会随机议员-生物7004-评级2</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>3000070045</v>
+        <v>3000070043</v>
       </c>
       <c r="B186" s="0" t="n">
         <v>7004</v>
@@ -8871,19 +8935,91 @@
       </c>
       <c r="O186" s="0" t="inlineStr">
         <is>
+          <t>70000002,R</t>
+        </is>
+      </c>
+      <c r="P186" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z186" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级3</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0" t="n">
+        <v>3000070044</v>
+      </c>
+      <c r="B187" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C187" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O187" s="0" t="inlineStr">
+        <is>
+          <t>70000002,R,SR</t>
+        </is>
+      </c>
+      <c r="P187" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W187" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z187" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级4</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="n">
+        <v>3000070045</v>
+      </c>
+      <c r="B188" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C188" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O188" s="0" t="inlineStr">
+        <is>
           <t>70000002,SR,SSR</t>
         </is>
       </c>
-      <c r="P186" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q186" s="0" t="n">
+      <c r="P188" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="W186" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z186" s="0" t="inlineStr">
+      <c r="W188" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z188" s="0" t="inlineStr">
         <is>
           <t>议会随机议员-生物7004-评级5</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -3237,24 +3237,22 @@
         <v>1041010003</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>104101</v>
+        <v>104104</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>500</v>
-      </c>
-      <c r="F34" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>1000</v>
       </c>
       <c r="G34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I34" s="0" t="n">
         <v>0</v>
@@ -3277,7 +3275,7 @@
         <v>1041010003</v>
       </c>
       <c r="S34" s="0" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="T34" s="0" t="n">
         <v>100004</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -3431,12 +3431,17 @@
       <c r="K37" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1200001&amp;1210001&amp;1220001&amp;</t>
+        </is>
+      </c>
       <c r="M37" s="0" t="n">
         <v>1000001</v>
       </c>
       <c r="N37" s="0" t="inlineStr">
         <is>
-          <t>10200009&amp;10300009&amp;11000012&amp;</t>
+          <t>10200009&amp;10300009&amp;11020016&amp;</t>
         </is>
       </c>
       <c r="P37" s="0" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z191"/>
+  <dimension ref="A1:Z186"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.375" customWidth="1" style="3" min="1" max="2"/>
@@ -3431,7 +3431,7 @@
       <c r="K37" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="0" t="inlineStr">
         <is>
           <t>1200001&amp;1210001&amp;1220001&amp;</t>
         </is>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>3000040051</v>
+        <v>3000050011</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>4005</v>
+        <v>5001</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>3</v>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O122" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P122" s="0" t="n">
@@ -6732,16 +6732,16 @@
       </c>
       <c r="Z122" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级1</t>
+          <t>议会随机议员-生物5001-评级1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>3000040052</v>
+        <v>3000050012</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>4005</v>
+        <v>5001</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>3</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P123" s="0" t="n">
@@ -6768,16 +6768,16 @@
       </c>
       <c r="Z123" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级2</t>
+          <t>议会随机议员-生物5001-评级2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>3000040053</v>
+        <v>3000050013</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>4005</v>
+        <v>5001</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>3</v>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P124" s="0" t="n">
@@ -6804,16 +6804,16 @@
       </c>
       <c r="Z124" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级3</t>
+          <t>议会随机议员-生物5001-评级3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>3000040054</v>
+        <v>3000050014</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>4005</v>
+        <v>5001</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>3</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="O125" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P125" s="0" t="n">
@@ -6840,16 +6840,16 @@
       </c>
       <c r="Z125" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级4</t>
+          <t>议会随机议员-生物5001-评级4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>3000040055</v>
+        <v>3000050015</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>4005</v>
+        <v>5001</v>
       </c>
       <c r="C126" s="0" t="n">
         <v>3</v>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="O126" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P126" s="0" t="n">
@@ -6876,16 +6876,16 @@
       </c>
       <c r="Z126" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级5</t>
+          <t>议会随机议员-生物5001-评级5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>3000050011</v>
+        <v>3000050021</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>3</v>
@@ -6912,16 +6912,16 @@
       </c>
       <c r="Z127" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级1</t>
+          <t>议会随机议员-生物5002-评级1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>3000050012</v>
+        <v>3000050022</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>3</v>
@@ -6948,16 +6948,16 @@
       </c>
       <c r="Z128" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级2</t>
+          <t>议会随机议员-生物5002-评级2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000050013</v>
+        <v>3000050023</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="C129" s="0" t="n">
         <v>3</v>
@@ -6984,16 +6984,16 @@
       </c>
       <c r="Z129" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级3</t>
+          <t>议会随机议员-生物5002-评级3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000050014</v>
+        <v>3000050024</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="C130" s="0" t="n">
         <v>3</v>
@@ -7020,16 +7020,16 @@
       </c>
       <c r="Z130" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级4</t>
+          <t>议会随机议员-生物5002-评级4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000050015</v>
+        <v>3000050025</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="C131" s="0" t="n">
         <v>3</v>
@@ -7056,16 +7056,16 @@
       </c>
       <c r="Z131" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级5</t>
+          <t>议会随机议员-生物5002-评级5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000050021</v>
+        <v>3000050031</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="C132" s="0" t="n">
         <v>3</v>
@@ -7092,16 +7092,16 @@
       </c>
       <c r="Z132" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级1</t>
+          <t>议会随机议员-生物5003-评级1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000050022</v>
+        <v>3000050032</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>3</v>
@@ -7128,16 +7128,16 @@
       </c>
       <c r="Z133" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级2</t>
+          <t>议会随机议员-生物5003-评级2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000050023</v>
+        <v>3000050033</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="C134" s="0" t="n">
         <v>3</v>
@@ -7164,16 +7164,16 @@
       </c>
       <c r="Z134" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级3</t>
+          <t>议会随机议员-生物5003-评级3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000050024</v>
+        <v>3000050034</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="C135" s="0" t="n">
         <v>3</v>
@@ -7200,16 +7200,16 @@
       </c>
       <c r="Z135" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级4</t>
+          <t>议会随机议员-生物5003-评级4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000050025</v>
+        <v>3000050035</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="C136" s="0" t="n">
         <v>3</v>
@@ -7236,16 +7236,16 @@
       </c>
       <c r="Z136" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级5</t>
+          <t>议会随机议员-生物5003-评级5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000050031</v>
+        <v>3000050041</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="C137" s="0" t="n">
         <v>3</v>
@@ -7272,16 +7272,16 @@
       </c>
       <c r="Z137" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级1</t>
+          <t>议会随机议员-生物5004-评级1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000050032</v>
+        <v>3000050042</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="C138" s="0" t="n">
         <v>3</v>
@@ -7308,16 +7308,16 @@
       </c>
       <c r="Z138" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级2</t>
+          <t>议会随机议员-生物5004-评级2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>3000050033</v>
+        <v>3000050043</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="C139" s="0" t="n">
         <v>3</v>
@@ -7344,16 +7344,16 @@
       </c>
       <c r="Z139" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级3</t>
+          <t>议会随机议员-生物5004-评级3</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>3000050034</v>
+        <v>3000050044</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="C140" s="0" t="n">
         <v>3</v>
@@ -7380,16 +7380,16 @@
       </c>
       <c r="Z140" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级4</t>
+          <t>议会随机议员-生物5004-评级4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>3000050035</v>
+        <v>3000050045</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="C141" s="0" t="n">
         <v>3</v>
@@ -7416,16 +7416,16 @@
       </c>
       <c r="Z141" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级5</t>
+          <t>议会随机议员-生物5004-评级5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>3000050041</v>
+        <v>3000060011</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="C142" s="0" t="n">
         <v>3</v>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="O142" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P142" s="0" t="n">
@@ -7452,16 +7452,16 @@
       </c>
       <c r="Z142" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级1</t>
+          <t>议会随机议员-生物6001-评级1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>3000050042</v>
+        <v>3000060012</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>3</v>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="O143" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P143" s="0" t="n">
@@ -7488,16 +7488,16 @@
       </c>
       <c r="Z143" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级2</t>
+          <t>议会随机议员-生物6001-评级2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>3000050043</v>
+        <v>3000060013</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="C144" s="0" t="n">
         <v>3</v>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="O144" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P144" s="0" t="n">
@@ -7524,16 +7524,16 @@
       </c>
       <c r="Z144" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级3</t>
+          <t>议会随机议员-生物6001-评级3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>3000050044</v>
+        <v>3000060014</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="C145" s="0" t="n">
         <v>3</v>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="O145" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P145" s="0" t="n">
@@ -7560,16 +7560,16 @@
       </c>
       <c r="Z145" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级4</t>
+          <t>议会随机议员-生物6001-评级4</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>3000050045</v>
+        <v>3000060015</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="C146" s="0" t="n">
         <v>3</v>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="O146" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P146" s="0" t="n">
@@ -7596,16 +7596,16 @@
       </c>
       <c r="Z146" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级5</t>
+          <t>议会随机议员-生物6001-评级5</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>3000060011</v>
+        <v>3000060021</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="C147" s="0" t="n">
         <v>3</v>
@@ -7632,16 +7632,16 @@
       </c>
       <c r="Z147" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级1</t>
+          <t>议会随机议员-生物6002-评级1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>3000060012</v>
+        <v>3000060022</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="C148" s="0" t="n">
         <v>3</v>
@@ -7668,16 +7668,16 @@
       </c>
       <c r="Z148" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级2</t>
+          <t>议会随机议员-生物6002-评级2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>3000060013</v>
+        <v>3000060023</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="C149" s="0" t="n">
         <v>3</v>
@@ -7704,16 +7704,16 @@
       </c>
       <c r="Z149" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级3</t>
+          <t>议会随机议员-生物6002-评级3</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>3000060014</v>
+        <v>3000060024</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="C150" s="0" t="n">
         <v>3</v>
@@ -7740,16 +7740,16 @@
       </c>
       <c r="Z150" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级4</t>
+          <t>议会随机议员-生物6002-评级4</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>3000060015</v>
+        <v>3000060025</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="C151" s="0" t="n">
         <v>3</v>
@@ -7776,16 +7776,16 @@
       </c>
       <c r="Z151" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级5</t>
+          <t>议会随机议员-生物6002-评级5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>3000060021</v>
+        <v>3000060031</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="C152" s="0" t="n">
         <v>3</v>
@@ -7812,16 +7812,16 @@
       </c>
       <c r="Z152" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级1</t>
+          <t>议会随机议员-生物6003-评级1</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>3000060022</v>
+        <v>3000060032</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="C153" s="0" t="n">
         <v>3</v>
@@ -7848,16 +7848,16 @@
       </c>
       <c r="Z153" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级2</t>
+          <t>议会随机议员-生物6003-评级2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>3000060023</v>
+        <v>3000060033</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="C154" s="0" t="n">
         <v>3</v>
@@ -7884,16 +7884,16 @@
       </c>
       <c r="Z154" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级3</t>
+          <t>议会随机议员-生物6003-评级3</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>3000060024</v>
+        <v>3000060034</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="C155" s="0" t="n">
         <v>3</v>
@@ -7920,16 +7920,16 @@
       </c>
       <c r="Z155" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级4</t>
+          <t>议会随机议员-生物6003-评级4</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>3000060025</v>
+        <v>3000060035</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="C156" s="0" t="n">
         <v>3</v>
@@ -7956,16 +7956,16 @@
       </c>
       <c r="Z156" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级5</t>
+          <t>议会随机议员-生物6003-评级5</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>3000060031</v>
+        <v>3000060041</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="C157" s="0" t="n">
         <v>3</v>
@@ -7992,16 +7992,16 @@
       </c>
       <c r="Z157" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级1</t>
+          <t>议会随机议员-生物6004-评级1</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>3000060032</v>
+        <v>3000060042</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="C158" s="0" t="n">
         <v>3</v>
@@ -8028,16 +8028,16 @@
       </c>
       <c r="Z158" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级2</t>
+          <t>议会随机议员-生物6004-评级2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>3000060033</v>
+        <v>3000060043</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="C159" s="0" t="n">
         <v>3</v>
@@ -8064,16 +8064,16 @@
       </c>
       <c r="Z159" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级3</t>
+          <t>议会随机议员-生物6004-评级3</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>3000060034</v>
+        <v>3000060044</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="C160" s="0" t="n">
         <v>3</v>
@@ -8100,16 +8100,16 @@
       </c>
       <c r="Z160" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级4</t>
+          <t>议会随机议员-生物6004-评级4</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>3000060035</v>
+        <v>3000060045</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="C161" s="0" t="n">
         <v>3</v>
@@ -8136,16 +8136,16 @@
       </c>
       <c r="Z161" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级5</t>
+          <t>议会随机议员-生物6004-评级5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>3000060041</v>
+        <v>3000060051</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="C162" s="0" t="n">
         <v>3</v>
@@ -8172,16 +8172,16 @@
       </c>
       <c r="Z162" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级1</t>
+          <t>议会随机议员-生物6005-评级1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>3000060042</v>
+        <v>3000060052</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="C163" s="0" t="n">
         <v>3</v>
@@ -8208,16 +8208,16 @@
       </c>
       <c r="Z163" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级2</t>
+          <t>议会随机议员-生物6005-评级2</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000060043</v>
+        <v>3000060053</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="C164" s="0" t="n">
         <v>3</v>
@@ -8244,16 +8244,16 @@
       </c>
       <c r="Z164" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级3</t>
+          <t>议会随机议员-生物6005-评级3</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000060044</v>
+        <v>3000060054</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="C165" s="0" t="n">
         <v>3</v>
@@ -8280,16 +8280,16 @@
       </c>
       <c r="Z165" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级4</t>
+          <t>议会随机议员-生物6005-评级4</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000060045</v>
+        <v>3000060055</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="C166" s="0" t="n">
         <v>3</v>
@@ -8316,16 +8316,16 @@
       </c>
       <c r="Z166" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级5</t>
+          <t>议会随机议员-生物6005-评级5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000060051</v>
+        <v>3000070011</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>6005</v>
+        <v>7001</v>
       </c>
       <c r="C167" s="0" t="n">
         <v>3</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="O167" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P167" s="0" t="n">
@@ -8352,16 +8352,16 @@
       </c>
       <c r="Z167" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级1</t>
+          <t>议会随机议员-生物7001-评级1</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000060052</v>
+        <v>3000070012</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>6005</v>
+        <v>7001</v>
       </c>
       <c r="C168" s="0" t="n">
         <v>3</v>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="O168" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P168" s="0" t="n">
@@ -8388,16 +8388,16 @@
       </c>
       <c r="Z168" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级2</t>
+          <t>议会随机议员-生物7001-评级2</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000060053</v>
+        <v>3000070013</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>6005</v>
+        <v>7001</v>
       </c>
       <c r="C169" s="0" t="n">
         <v>3</v>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="O169" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P169" s="0" t="n">
@@ -8424,16 +8424,16 @@
       </c>
       <c r="Z169" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级3</t>
+          <t>议会随机议员-生物7001-评级3</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>3000060054</v>
+        <v>3000070014</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>6005</v>
+        <v>7001</v>
       </c>
       <c r="C170" s="0" t="n">
         <v>3</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="O170" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P170" s="0" t="n">
@@ -8460,16 +8460,16 @@
       </c>
       <c r="Z170" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级4</t>
+          <t>议会随机议员-生物7001-评级4</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000060055</v>
+        <v>3000070015</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>6005</v>
+        <v>7001</v>
       </c>
       <c r="C171" s="0" t="n">
         <v>3</v>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="O171" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P171" s="0" t="n">
@@ -8496,16 +8496,16 @@
       </c>
       <c r="Z171" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级5</t>
+          <t>议会随机议员-生物7001-评级5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>3000070011</v>
+        <v>3000070021</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="C172" s="0" t="n">
         <v>3</v>
@@ -8532,16 +8532,16 @@
       </c>
       <c r="Z172" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级1</t>
+          <t>议会随机议员-生物7002-评级1</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>3000070012</v>
+        <v>3000070022</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="C173" s="0" t="n">
         <v>3</v>
@@ -8568,16 +8568,16 @@
       </c>
       <c r="Z173" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级2</t>
+          <t>议会随机议员-生物7002-评级2</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>3000070013</v>
+        <v>3000070023</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="C174" s="0" t="n">
         <v>3</v>
@@ -8604,16 +8604,16 @@
       </c>
       <c r="Z174" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级3</t>
+          <t>议会随机议员-生物7002-评级3</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>3000070014</v>
+        <v>3000070024</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="C175" s="0" t="n">
         <v>3</v>
@@ -8640,16 +8640,16 @@
       </c>
       <c r="Z175" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级4</t>
+          <t>议会随机议员-生物7002-评级4</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>3000070015</v>
+        <v>3000070025</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="C176" s="0" t="n">
         <v>3</v>
@@ -8676,16 +8676,16 @@
       </c>
       <c r="Z176" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级5</t>
+          <t>议会随机议员-生物7002-评级5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>3000070021</v>
+        <v>3000070031</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="C177" s="0" t="n">
         <v>3</v>
@@ -8712,16 +8712,16 @@
       </c>
       <c r="Z177" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级1</t>
+          <t>议会随机议员-生物7003-评级1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>3000070022</v>
+        <v>3000070032</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="C178" s="0" t="n">
         <v>3</v>
@@ -8748,16 +8748,16 @@
       </c>
       <c r="Z178" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级2</t>
+          <t>议会随机议员-生物7003-评级2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>3000070023</v>
+        <v>3000070033</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="C179" s="0" t="n">
         <v>3</v>
@@ -8784,16 +8784,16 @@
       </c>
       <c r="Z179" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级3</t>
+          <t>议会随机议员-生物7003-评级3</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>3000070024</v>
+        <v>3000070034</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="C180" s="0" t="n">
         <v>3</v>
@@ -8820,16 +8820,16 @@
       </c>
       <c r="Z180" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级4</t>
+          <t>议会随机议员-生物7003-评级4</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>3000070025</v>
+        <v>3000070035</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="C181" s="0" t="n">
         <v>3</v>
@@ -8856,16 +8856,16 @@
       </c>
       <c r="Z181" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级5</t>
+          <t>议会随机议员-生物7003-评级5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>3000070031</v>
+        <v>3000070041</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="C182" s="0" t="n">
         <v>3</v>
@@ -8892,16 +8892,16 @@
       </c>
       <c r="Z182" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级1</t>
+          <t>议会随机议员-生物7004-评级1</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>3000070032</v>
+        <v>3000070042</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="C183" s="0" t="n">
         <v>3</v>
@@ -8928,16 +8928,16 @@
       </c>
       <c r="Z183" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级2</t>
+          <t>议会随机议员-生物7004-评级2</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>3000070033</v>
+        <v>3000070043</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="C184" s="0" t="n">
         <v>3</v>
@@ -8964,16 +8964,16 @@
       </c>
       <c r="Z184" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级3</t>
+          <t>议会随机议员-生物7004-评级3</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>3000070034</v>
+        <v>3000070044</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="C185" s="0" t="n">
         <v>3</v>
@@ -9000,16 +9000,16 @@
       </c>
       <c r="Z185" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级4</t>
+          <t>议会随机议员-生物7004-评级4</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>3000070035</v>
+        <v>3000070045</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="C186" s="0" t="n">
         <v>3</v>
@@ -9035,186 +9035,6 @@
         <v>3</v>
       </c>
       <c r="Z186" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7003-评级5</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="0" t="n">
-        <v>3000070041</v>
-      </c>
-      <c r="B187" s="0" t="n">
-        <v>7004</v>
-      </c>
-      <c r="C187" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D187" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M187" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O187" s="0" t="inlineStr">
-        <is>
-          <t>70000002,N</t>
-        </is>
-      </c>
-      <c r="P187" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q187" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W187" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z187" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7004-评级1</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="0" t="n">
-        <v>3000070042</v>
-      </c>
-      <c r="B188" s="0" t="n">
-        <v>7004</v>
-      </c>
-      <c r="C188" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D188" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M188" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O188" s="0" t="inlineStr">
-        <is>
-          <t>70000002,N,R</t>
-        </is>
-      </c>
-      <c r="P188" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q188" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W188" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z188" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7004-评级2</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="0" t="n">
-        <v>3000070043</v>
-      </c>
-      <c r="B189" s="0" t="n">
-        <v>7004</v>
-      </c>
-      <c r="C189" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D189" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M189" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O189" s="0" t="inlineStr">
-        <is>
-          <t>70000002,R</t>
-        </is>
-      </c>
-      <c r="P189" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q189" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W189" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z189" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7004-评级3</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="0" t="n">
-        <v>3000070044</v>
-      </c>
-      <c r="B190" s="0" t="n">
-        <v>7004</v>
-      </c>
-      <c r="C190" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D190" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M190" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O190" s="0" t="inlineStr">
-        <is>
-          <t>70000002,R,SR</t>
-        </is>
-      </c>
-      <c r="P190" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q190" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W190" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z190" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7004-评级4</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="0" t="n">
-        <v>3000070045</v>
-      </c>
-      <c r="B191" s="0" t="n">
-        <v>7004</v>
-      </c>
-      <c r="C191" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D191" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M191" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O191" s="0" t="inlineStr">
-        <is>
-          <t>70000002,SR,SSR</t>
-        </is>
-      </c>
-      <c r="P191" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q191" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W191" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z191" s="0" t="inlineStr">
         <is>
           <t>议会随机议员-生物7004-评级5</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G35" s="0" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="H35" s="0" t="n">
         <v>5</v>
@@ -3360,13 +3360,13 @@
         <v>1</v>
       </c>
       <c r="E36" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="0" t="n">
         <v>500</v>
-      </c>
-      <c r="F36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="0" t="n">
-        <v>5000</v>
       </c>
       <c r="H36" s="0" t="n">
         <v>5</v>
